--- a/savollar.xlsx
+++ b/savollar.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDA55D1-A3D5-42AF-8A43-33AD0DAFF6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Savollar" state="visible" r:id="rId4"/>
+    <sheet name="Savollar" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2549" uniqueCount="1514">
   <si>
     <t>category</t>
   </si>
@@ -2992,400 +3001,1606 @@
     <t>Ustozlar yo'riqnomasi</t>
   </si>
   <si>
-    <t>Dars maqsadi nimani belgilaydi?</t>
-  </si>
-  <si>
-    <t>Kutiladigan natija va yo'nalishni</t>
-  </si>
-  <si>
-    <t>Faqat sinf nomini</t>
-  </si>
-  <si>
-    <t>O'quvchining telefon modelini</t>
-  </si>
-  <si>
-    <t>Darslik rangini</t>
-  </si>
-  <si>
-    <t>Formativ baholashning asosiy maqsadi nima?</t>
-  </si>
-  <si>
-    <t>O'qish jarayonini kuzatib borish</t>
-  </si>
-  <si>
-    <t>Yil oxirida faqat raqam qo'yish</t>
-  </si>
-  <si>
-    <t>Sinfni bezash</t>
-  </si>
-  <si>
-    <t>Uy vazifasini o'chirish</t>
-  </si>
-  <si>
-    <t>Summativ baholash qachon qo'llanadi?</t>
-  </si>
-  <si>
-    <t>Mavzu yoki bo'lim yakunida</t>
-  </si>
-  <si>
-    <t>Dars boshida har daqiqa</t>
-  </si>
-  <si>
     <t>Faqat tanaffusda</t>
   </si>
   <si>
-    <t>Sinfga kirishda</t>
-  </si>
-  <si>
-    <t>Differensial yondashuv nimani anglatadi?</t>
-  </si>
-  <si>
-    <t>Turli o'quvchilar ehtiyojiga moslashtirishni</t>
-  </si>
-  <si>
-    <t>Faqat kuchli o'quvchiga dars berishni</t>
-  </si>
-  <si>
-    <t>Bir xil vazifani hamma uchun majburiy qilishni</t>
-  </si>
-  <si>
-    <t>Faqat test ishlatishni</t>
-  </si>
-  <si>
-    <t>Dars rejasida nimalar bo'lishi kerak?</t>
-  </si>
-  <si>
-    <t>Maqsad, metod, vaqt va baholash</t>
-  </si>
-  <si>
-    <t>Faqat daftar va ruchka</t>
-  </si>
-  <si>
-    <t>Faqat savol nomi</t>
-  </si>
-  <si>
-    <t>Sinf jurnali soni</t>
-  </si>
-  <si>
-    <t>Motivatsiya nimaga xizmat qiladi?</t>
-  </si>
-  <si>
-    <t>O'quvchini faollashtirishga</t>
-  </si>
-  <si>
-    <t>Sinf chirog'ini o'chirishga</t>
-  </si>
-  <si>
-    <t>Bahoni yashirishga</t>
-  </si>
-  <si>
-    <t>Uy vazifasini ko'paytirishga</t>
-  </si>
-  <si>
-    <t>Ochiq savolning foydasi nimada?</t>
-  </si>
-  <si>
-    <t>Fikrni kengroq ifodalashda</t>
-  </si>
-  <si>
-    <t>Faqat 'ha' yoki 'yo'q' javob olishda</t>
-  </si>
-  <si>
-    <t>Savolni yashirishda</t>
-  </si>
-  <si>
-    <t>O'qituvchini sukutga tushirishda</t>
-  </si>
-  <si>
-    <t>Guruhli ishning asosiy afzalligi nima?</t>
-  </si>
-  <si>
-    <t>Hamkorlik va fikr almashish</t>
-  </si>
-  <si>
-    <t>Faqat yakka ishlash</t>
-  </si>
-  <si>
-    <t>O'quvchini jim o'tirishga majburlash</t>
-  </si>
-  <si>
-    <t>Dars vaqtini bekor sarflash</t>
-  </si>
-  <si>
-    <t>Refleksiya nima?</t>
-  </si>
-  <si>
-    <t>O'z faoliyatini tahlil qilish</t>
-  </si>
-  <si>
-    <t>Faqat yozuvni ko'chirish</t>
-  </si>
-  <si>
-    <t>Sinfda yugurish</t>
-  </si>
-  <si>
-    <t>Darslikni almashtirish</t>
-  </si>
-  <si>
-    <t>Rubrika nima uchun ishlatiladi?</t>
-  </si>
-  <si>
-    <t>Baholash mezonini aniq ko'rsatish uchun</t>
-  </si>
-  <si>
-    <t>Sinf pardasini o'lchash uchun</t>
-  </si>
-  <si>
-    <t>Dars jadvalini o'chirish uchun</t>
-  </si>
-  <si>
-    <t>O'quvchini qayta ro'yxatga olish uchun</t>
-  </si>
-  <si>
-    <t>Aqliy hujum usuli nimaga xizmat qiladi?</t>
-  </si>
-  <si>
-    <t>Tez g'oyalar yig'ishga</t>
-  </si>
-  <si>
-    <t>Faqat sukut saqlashga</t>
-  </si>
-  <si>
-    <t>Bahoni o'chirishga</t>
-  </si>
-  <si>
-    <t>Uy vazifasini bekor qilishga</t>
-  </si>
-  <si>
-    <t>Dars yakunida nima qilish foydali?</t>
-  </si>
-  <si>
-    <t>Asosiy xulosani jamlash</t>
-  </si>
-  <si>
-    <t>Mavzuni butunlay tashlab ketish</t>
-  </si>
-  <si>
-    <t>Faqat yangi bo'limga o'tish</t>
-  </si>
-  <si>
-    <t>Daftarni yopib qo'yish</t>
-  </si>
-  <si>
-    <t>Classroom management nimani anglatadi?</t>
-  </si>
-  <si>
-    <t>Sinf tartibi va jarayonini boshqarishni</t>
-  </si>
-  <si>
-    <t>Kompyuter sotib olishni</t>
-  </si>
-  <si>
-    <t>Faqat baho qo'yishni</t>
-  </si>
-  <si>
-    <t>Darslik chop etishni</t>
-  </si>
-  <si>
-    <t>SMART maqsadning bir xususiyati qaysi?</t>
-  </si>
-  <si>
-    <t>Aniq va o'lchab bo'ladigan bo'lishi</t>
-  </si>
-  <si>
-    <t>Noaniq va uzun bo'lishi</t>
-  </si>
-  <si>
-    <t>Faqat og'zaki bo'lishi</t>
-  </si>
-  <si>
-    <t>Bahosiz bo'lishi</t>
-  </si>
-  <si>
-    <t>Scaffolding nimani bildiradi?</t>
-  </si>
-  <si>
-    <t>Yordamni bosqichma-bosqich berishni</t>
-  </si>
-  <si>
-    <t>O'quvchini yolg'iz qoldirishni</t>
-  </si>
-  <si>
-    <t>Faqat testni ko'paytirishni</t>
-  </si>
-  <si>
-    <t>Darsni bekor qilishni</t>
-  </si>
-  <si>
-    <t>Samarali feedback qanday bo'lishi kerak?</t>
-  </si>
-  <si>
-    <t>Aniq va yaxshilashga yo'naltirilgan</t>
-  </si>
-  <si>
-    <t>Qisqa va tushunarsiz</t>
-  </si>
-  <si>
-    <t>Faqat tanbeh shaklida</t>
-  </si>
-  <si>
-    <t>Hech qanday misolsiz</t>
-  </si>
-  <si>
-    <t>Cooperative learning nima?</t>
-  </si>
-  <si>
-    <t>Birgalikda o'rganish</t>
-  </si>
-  <si>
-    <t>Faqat mustaqil yozish</t>
-  </si>
-  <si>
-    <t>Uyda yolg'iz o'qish</t>
-  </si>
-  <si>
-    <t>Darsni to'xtatish</t>
-  </si>
-  <si>
-    <t>Inclusive education nimaga qaratilgan?</t>
-  </si>
-  <si>
-    <t>Hamma o'quvchi uchun mos muhit yaratishga</t>
-  </si>
-  <si>
-    <t>Faqat tanlangan o'quvchilarni o'qitishga</t>
-  </si>
-  <si>
-    <t>Faqat yuqori baho olishga</t>
-  </si>
-  <si>
-    <t>Sinfni kichraytirishga</t>
-  </si>
-  <si>
-    <t>Starter activity qachon foydali?</t>
-  </si>
-  <si>
-    <t>Dars boshida e'tiborni jamlashda</t>
-  </si>
-  <si>
     <t>Faqat dars oxirida</t>
   </si>
   <si>
-    <t>Uy vazifasi sifatida</t>
-  </si>
-  <si>
-    <t>Ta'til oldidan</t>
-  </si>
-  <si>
-    <t>Vaqtni boshqarishning foydasi nimada?</t>
-  </si>
-  <si>
-    <t>Darsni samarali o'tkazishda</t>
-  </si>
-  <si>
-    <t>Darslikni almashtirishda</t>
-  </si>
-  <si>
-    <t>Sinf nomini yozishda</t>
-  </si>
-  <si>
-    <t>Baho sonini kamaytirishda</t>
-  </si>
-  <si>
-    <t>Xavfsizlik qoidasi nimaga kerak?</t>
-  </si>
-  <si>
-    <t>Jarohat va xavfni kamaytirishga</t>
-  </si>
-  <si>
-    <t>Darsni cho'zishga</t>
-  </si>
-  <si>
-    <t>Sinfni bo'yashga</t>
-  </si>
-  <si>
-    <t>Peer assessment nimani anglatadi?</t>
-  </si>
-  <si>
-    <t>O'zaro baholashni</t>
-  </si>
-  <si>
-    <t>Faqat o'qituvchi bahosini</t>
-  </si>
-  <si>
-    <t>Bahoni o'chirishni</t>
-  </si>
-  <si>
-    <t>Jadvalni almashtirishni</t>
-  </si>
-  <si>
-    <t>Professional development nimaga yordam beradi?</t>
-  </si>
-  <si>
-    <t>Ustozning malakasini oshirishga</t>
-  </si>
-  <si>
-    <t>Sinf devorini qurishga</t>
-  </si>
-  <si>
-    <t>Daftar sonini ko'paytirishga</t>
-  </si>
-  <si>
-    <t>Telefonni almashtirishga</t>
-  </si>
-  <si>
-    <t>Savol berish texnikasining maqsadi nima?</t>
-  </si>
-  <si>
-    <t>Tushunishni tekshirish va fikrni ochish</t>
-  </si>
-  <si>
-    <t>Faqat jimlik yaratish</t>
-  </si>
-  <si>
-    <t>Daftarga yozuv qo'shish</t>
-  </si>
-  <si>
-    <t>Darslikni yopish</t>
-  </si>
-  <si>
-    <t>Diagnostik baholash nimaga yordam beradi?</t>
-  </si>
-  <si>
-    <t>Boshlang'ich bilim darajasini aniqlashga</t>
-  </si>
-  <si>
-    <t>Faqat yakuniy baho qo'yishga</t>
-  </si>
-  <si>
-    <t>Sinf derazasini ochishga</t>
-  </si>
-  <si>
-    <t>Kitob muqovasini almashtirishga</t>
+    <t>Vazifa umuman bajarilmagan holatda qaysi ball qo'yiladi?</t>
+  </si>
+  <si>
+    <t>1-20</t>
+  </si>
+  <si>
+    <t>21-59</t>
+  </si>
+  <si>
+    <t>60-70</t>
+  </si>
+  <si>
+    <t>Vazifa 90% dan ortiq bajarilmagan, faqat 5-10% qismi bor. Qaysi ball oralig'i mos?</t>
+  </si>
+  <si>
+    <t>Minimal talablarga javob bermagan, jiddiy xatolar ko'p va mavzuni faqat 10% tushungan. Qaysi ball oralig'i qo'yiladi?</t>
+  </si>
+  <si>
+    <t>71-85</t>
+  </si>
+  <si>
+    <t>Minimal talablarni qondiradi, lekin daraja past. Kamida 50% tushungan, jiddiy xatolar mavjud. Qancha ball oralig'i qo'yiladi?</t>
+  </si>
+  <si>
+    <t>86-94</t>
+  </si>
+  <si>
+    <t>Vazifa asosiy talablar asosida to'g'ri bajarilgan, xatolar kam. Qaysi ball oralig'i mos?</t>
+  </si>
+  <si>
+    <t>95-100</t>
+  </si>
+  <si>
+    <t>Mavzuni yuqori darajada tushungan, ijodiy va tahliliy yondashgan, mutlaqo xatosiz bajargan. Qaysi ball mos?</t>
+  </si>
+  <si>
+    <t>O'quvchi ustoz talab qilmagan qo'shimcha bilimlarni mustaqil o'rganib qo'llagan. Qaysi ball oralig'i mos?</t>
+  </si>
+  <si>
+    <t>O'quvchi loyihani ingliz tilida tasvirlab bera oladigan darajada bajargan. Qaysi ball oralig'i mos?</t>
+  </si>
+  <si>
+    <t>Ko'chirgan va ko'chirtirgan o'quvchilarga qanday ball qo'yiladi?</t>
+  </si>
+  <si>
+    <t>Ko'chirish holati aniqlansa, 0 ball qo'yish uchun nima kerak?</t>
+  </si>
+  <si>
+    <t>Dalillar bilan asoslash</t>
+  </si>
+  <si>
+    <t>Faqat gumon qilish</t>
+  </si>
+  <si>
+    <t>Ota-onadan so'rash</t>
+  </si>
+  <si>
+    <t>Guruh ovozi</t>
+  </si>
+  <si>
+    <t>Uy vazifasi o'quvchi yuklaganidan keyin maksimal qancha vaqtda tekshirilishi kerak?</t>
+  </si>
+  <si>
+    <t>6 soat</t>
+  </si>
+  <si>
+    <t>12 soat</t>
+  </si>
+  <si>
+    <t>24 soat</t>
+  </si>
+  <si>
+    <t>48 soat</t>
+  </si>
+  <si>
+    <t>12 soatdan keyin tekshirilgan vazifa tizimda qanday hisoblanadi?</t>
+  </si>
+  <si>
+    <t>O'z vaqtida</t>
+  </si>
+  <si>
+    <t>Kech tekshirilgan vazifa</t>
+  </si>
+  <si>
+    <t>Bekor qilingan vazifa</t>
+  </si>
+  <si>
+    <t>Qo'shimcha vazifa</t>
+  </si>
+  <si>
+    <t>Kech topshirilgan vazifaga qanday qoida qo'llanadi?</t>
+  </si>
+  <si>
+    <t>10% kam ball</t>
+  </si>
+  <si>
+    <t>20% kam ball</t>
+  </si>
+  <si>
+    <t>30% kam ball</t>
+  </si>
+  <si>
+    <t>Ball o'zgarmaydi</t>
+  </si>
+  <si>
+    <t>80 ballga loyiq vazifa kech topshirilsa, yakuniy ball nechchi bo'ladi?</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>90 ballga loyiq vazifa kech topshirilsa, yakuniy ball nechchi bo'ladi?</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>1 haftada 3 ta yo'nalish bo'lsa, uy vazifasini bajarish muddati qancha?</t>
+  </si>
+  <si>
+    <t>36 soat</t>
+  </si>
+  <si>
+    <t>7 kun</t>
+  </si>
+  <si>
+    <t>10 kun</t>
+  </si>
+  <si>
+    <t>2 haftada 2 ta yo'nalish bo'lsa, vazifa topshirish muddati qancha?</t>
+  </si>
+  <si>
+    <t>1 haftada 1 ta yo'nalish bo'lsa, vazifa topshirish muddati qancha?</t>
+  </si>
+  <si>
+    <t>Har bir darsda uy vazifasi berilishi shartmi?</t>
+  </si>
+  <si>
+    <t>Ha</t>
+  </si>
+  <si>
+    <t>Yo'q</t>
+  </si>
+  <si>
+    <t>Faqat nazariyada</t>
+  </si>
+  <si>
+    <t>Faqat robototexnikada</t>
+  </si>
+  <si>
+    <t>Qaysi kunda uy vazifasi berilmaydi?</t>
+  </si>
+  <si>
+    <t>Oddiy dars kuni</t>
+  </si>
+  <si>
+    <t>Imtihon kuni</t>
+  </si>
+  <si>
+    <t>Takrorlash kuni</t>
+  </si>
+  <si>
+    <t>Amaliyot kuni</t>
+  </si>
+  <si>
+    <t>Uy vazifasi muddati tugashidan qancha vaqt oldin guruhda ogohlantirish tavsiya etiladi?</t>
+  </si>
+  <si>
+    <t>2 soat</t>
+  </si>
+  <si>
+    <t>5 soat</t>
+  </si>
+  <si>
+    <t>15 o'quvchidan 13 tasi topshirgan bo'lsa, qolgan 2 tasi bilan nima qilish kerak?</t>
+  </si>
+  <si>
+    <t>Shaxsan bog'lanish</t>
+  </si>
+  <si>
+    <t>E'tibor bermaslik</t>
+  </si>
+  <si>
+    <t>Avtomatik 0 qo'yish</t>
+  </si>
+  <si>
+    <t>Guruhdan chiqarish</t>
+  </si>
+  <si>
+    <t>ERP bahosidan so'ng o'quvchiga nima qoldirilishi kerak?</t>
+  </si>
+  <si>
+    <t>Batafsil yozma fidbek</t>
+  </si>
+  <si>
+    <t>Faqat emoji</t>
+  </si>
+  <si>
+    <t>Faqat ball</t>
+  </si>
+  <si>
+    <t>Hech narsa</t>
+  </si>
+  <si>
+    <t>Guruhda hech kim 70 balldan yuqori olmasa, keyingi dars boshiga nima tayyorlanadi?</t>
+  </si>
+  <si>
+    <t>3-5 ta savol</t>
+  </si>
+  <si>
+    <t>Yangi imtihon</t>
+  </si>
+  <si>
+    <t>Jazo ro'yxati</t>
+  </si>
+  <si>
+    <t>Sport mashqi</t>
+  </si>
+  <si>
+    <t>Materiallar va uy vazifasi qachon taqdimotga biriktirilgan bo'lishi kerak?</t>
+  </si>
+  <si>
+    <t>Darsdan keyin</t>
+  </si>
+  <si>
+    <t>Dars boshlanishidan avval</t>
+  </si>
+  <si>
+    <t>Hafta oxirida</t>
+  </si>
+  <si>
+    <t>O'quvchi so'raganda</t>
+  </si>
+  <si>
+    <t>Yangi guruh ochilishidan oldin Telegram guruh kamida qachon tekshiriladi?</t>
+  </si>
+  <si>
+    <t>Dars kuni</t>
+  </si>
+  <si>
+    <t>1 kun oldin</t>
+  </si>
+  <si>
+    <t>2 kun oldin</t>
+  </si>
+  <si>
+    <t>1 hafta keyin</t>
+  </si>
+  <si>
+    <t>Telegram guruhda yangi a'zolar uchun qaysi sozlama yoqilishi kerak?</t>
+  </si>
+  <si>
+    <t>Oldingi xabarlarni ko'ra oladi</t>
+  </si>
+  <si>
+    <t>Faqat admin yozadi</t>
+  </si>
+  <si>
+    <t>Faqat rasm yuboradi</t>
+  </si>
+  <si>
+    <t>Xabarlar o'chadi</t>
+  </si>
+  <si>
+    <t>Guruh ma'lumotlarini kimlar o'zgartira olmasligi kerak?</t>
+  </si>
+  <si>
+    <t>Ota-onalar va o'quvchilar</t>
+  </si>
+  <si>
+    <t>Faqat adminlar</t>
+  </si>
+  <si>
+    <t>Faqat o'qituvchi</t>
+  </si>
+  <si>
+    <t>Hech kim</t>
+  </si>
+  <si>
+    <t>Telegram reaksiyalarida nimalar cheklanishi kerak?</t>
+  </si>
+  <si>
+    <t>Ortiqcha va behayo emojilar</t>
+  </si>
+  <si>
+    <t>Oddiy like</t>
+  </si>
+  <si>
+    <t>Matnli xabarlar</t>
+  </si>
+  <si>
+    <t>Dars materiallari</t>
+  </si>
+  <si>
+    <t>O'quvchilar ro'yxatida avvalo nimalar tekshiriladi?</t>
+  </si>
+  <si>
+    <t>Shartnoma, to'lov va guruhga qo'shilgani</t>
+  </si>
+  <si>
+    <t>Telefon modeli</t>
+  </si>
+  <si>
+    <t>Uy manzili</t>
+  </si>
+  <si>
+    <t>Baholari</t>
+  </si>
+  <si>
+    <t>Guruhga qo'shilmagan o'quvchilar bilan nima qilish kerak?</t>
+  </si>
+  <si>
+    <t>Shaxsan aloqaga chiqib qo'shilishini ta'minlash</t>
+  </si>
+  <si>
+    <t>Kutib turish</t>
+  </si>
+  <si>
+    <t>Bahosini pasaytirish</t>
+  </si>
+  <si>
+    <t>Guruhni o'chirish</t>
+  </si>
+  <si>
+    <t>Robototexnika dars jadvali nimaga to'g'ri kelmasligi kerak?</t>
+  </si>
+  <si>
+    <t>Boshqa guruhlarning LEGO mashg'ulot jadvaliga</t>
+  </si>
+  <si>
+    <t>Tanaffusga</t>
+  </si>
+  <si>
+    <t>ERPga</t>
+  </si>
+  <si>
+    <t>Uy vazifasiga</t>
+  </si>
+  <si>
+    <t>LEGO jadval moslashuvi deadline qachon?</t>
+  </si>
+  <si>
+    <t>Darsdan 2 kun oldin</t>
+  </si>
+  <si>
+    <t>Darsdan 1 oy oldin</t>
+  </si>
+  <si>
+    <t>Tanishtiruv video qachon yuboriladi?</t>
+  </si>
+  <si>
+    <t>Darsdan 1 kun oldin</t>
+  </si>
+  <si>
+    <t>Faqat ota-onaga</t>
+  </si>
+  <si>
+    <t>Tanishtiruv video davomiyligi qancha tavsiya etiladi?</t>
+  </si>
+  <si>
+    <t>30 soniya</t>
+  </si>
+  <si>
+    <t>1 daqiqa</t>
+  </si>
+  <si>
+    <t>3 daqiqa</t>
+  </si>
+  <si>
+    <t>10 daqiqa</t>
+  </si>
+  <si>
+    <t>Tanishtiruv videoda qaysi ma'lumot bo'lishi kerak?</t>
+  </si>
+  <si>
+    <t>Ism, mashg'ulot vaqti, jadval, xona</t>
+  </si>
+  <si>
+    <t>Oylik maosh</t>
+  </si>
+  <si>
+    <t>Shaxsiy sirlar</t>
+  </si>
+  <si>
+    <t>Rahbarlar haqida fikr</t>
+  </si>
+  <si>
+    <t>Videoni qayerdan boshlab olish tavsiya etiladi?</t>
+  </si>
+  <si>
+    <t>Reception yoki filial administratsiyasi yonidan</t>
+  </si>
+  <si>
+    <t>Uyda</t>
+  </si>
+  <si>
+    <t>Ko'chada</t>
+  </si>
+  <si>
+    <t>Avtobusda</t>
+  </si>
+  <si>
+    <t>Dars boshlanishidan necha daqiqa oldin sinfxonada bo'lish majburiy?</t>
+  </si>
+  <si>
+    <t>5 daqiqa</t>
+  </si>
+  <si>
+    <t>20 daqiqa</t>
+  </si>
+  <si>
+    <t>30 daqiqa</t>
+  </si>
+  <si>
+    <t>Markazga kirgach beyjik qanday bo'lishi kerak?</t>
+  </si>
+  <si>
+    <t>Ko'rinadigan qilib taqilgan</t>
+  </si>
+  <si>
+    <t>Sumkada</t>
+  </si>
+  <si>
+    <t>Cho'ntakda</t>
+  </si>
+  <si>
+    <t>Xona harorati qaysi oralig'iga olib kelinadi?</t>
+  </si>
+  <si>
+    <t>15-18°C</t>
+  </si>
+  <si>
+    <t>19-22°C</t>
+  </si>
+  <si>
+    <t>23-27°C</t>
+  </si>
+  <si>
+    <t>28-30°C</t>
+  </si>
+  <si>
+    <t>Xona qancha vaqtda shamollatiladi?</t>
+  </si>
+  <si>
+    <t>Har 10 daqiqada</t>
+  </si>
+  <si>
+    <t>Har 20 daqiqada</t>
+  </si>
+  <si>
+    <t>Har soatda</t>
+  </si>
+  <si>
+    <t>Darsdan oldin kompyuter/proyektor/elektron doska qanday holatda bo'lishi kerak?</t>
+  </si>
+  <si>
+    <t>Yoqilgan va tayyor</t>
+  </si>
+  <si>
+    <t>O'chiq</t>
+  </si>
+  <si>
+    <t>Ulanmagan</t>
+  </si>
+  <si>
+    <t>Faqat dars o'rtasida</t>
+  </si>
+  <si>
+    <t>Macbook bo'lsa, hub va adapterlar qachon ulanadi?</t>
+  </si>
+  <si>
+    <t>Oldindan</t>
+  </si>
+  <si>
+    <t>Dars tugagach</t>
+  </si>
+  <si>
+    <t>Kerak emas</t>
+  </si>
+  <si>
+    <t>Dars vaqtida slayd tayyorlash nimani anglatadi?</t>
+  </si>
+  <si>
+    <t>O'quvchilar vaqtini olish</t>
+  </si>
+  <si>
+    <t>Professional tayyorgarlik</t>
+  </si>
+  <si>
+    <t>Warm-up</t>
+  </si>
+  <si>
+    <t>CCQ</t>
+  </si>
+  <si>
+    <t>Davomat dars boshlanganidan keyin necha daqiqa ichida qilinadi?</t>
+  </si>
+  <si>
+    <t>15 daqiqa</t>
+  </si>
+  <si>
+    <t>Yo'q o'quvchini ERPda 'bor' deb belgilash mumkinmi?</t>
+  </si>
+  <si>
+    <t>Faqat ota-onasi aytsa</t>
+  </si>
+  <si>
+    <t>ERPda ismi chiqmagan o'quvchi nima qilinadi?</t>
+  </si>
+  <si>
+    <t>Administratsiyaga yo'naltiriladi</t>
+  </si>
+  <si>
+    <t>Darsga kiritiladi</t>
+  </si>
+  <si>
+    <t>Bor deb belgilanadi</t>
+  </si>
+  <si>
+    <t>Uyga jo'natiladi</t>
+  </si>
+  <si>
+    <t>Dars vaqtida telefon qanday holatda bo'lishi kerak?</t>
+  </si>
+  <si>
+    <t>Ovozsiz silent</t>
+  </si>
+  <si>
+    <t>Ovozli</t>
+  </si>
+  <si>
+    <t>Musiqa bilan</t>
+  </si>
+  <si>
+    <t>Doim qo'lda</t>
+  </si>
+  <si>
+    <t>Dars boshida avvalgi darsni eslash uchun qancha vaqt savol-javob o'tkaziladi?</t>
+  </si>
+  <si>
+    <t>2 daqiqa</t>
+  </si>
+  <si>
+    <t>O'quvchiga faqat 'vazifangiz a'lo' deyish o'rniga nima so'raladi?</t>
+  </si>
+  <si>
+    <t>Fikrini misol yoki dalillar bilan asoslash</t>
+  </si>
+  <si>
+    <t>Telefon raqami</t>
+  </si>
+  <si>
+    <t>CCQ usuli nima uchun ishlatiladi?</t>
+  </si>
+  <si>
+    <t>Mavzuni tushunganini tekshirish</t>
+  </si>
+  <si>
+    <t>Davomat olish</t>
+  </si>
+  <si>
+    <t>Wi-Fi ulash</t>
+  </si>
+  <si>
+    <t>Musobaqa e'loni</t>
+  </si>
+  <si>
+    <t>'Tushunarlimi?' kabi savol nima sababdan noqulay?</t>
+  </si>
+  <si>
+    <t>Ha/yo'q javobli</t>
+  </si>
+  <si>
+    <t>Juda uzun</t>
+  </si>
+  <si>
+    <t>Faqat inglizcha</t>
+  </si>
+  <si>
+    <t>Rasmiy emas</t>
+  </si>
+  <si>
+    <t>5 bosqichli savol berish sxemasida 1-bosqich nima?</t>
+  </si>
+  <si>
+    <t>Mavzu nomini so'rash</t>
+  </si>
+  <si>
+    <t>Sababini so'rash</t>
+  </si>
+  <si>
+    <t>Yangi misol berish</t>
+  </si>
+  <si>
+    <t>Javobni aytish</t>
+  </si>
+  <si>
+    <t>5 bosqichli savol berish sxemasida 2-bosqich nima?</t>
+  </si>
+  <si>
+    <t>Qanday ishlatilishini so'rash</t>
+  </si>
+  <si>
+    <t>Uy vazifa berish</t>
+  </si>
+  <si>
+    <t>Tanaffus qilish</t>
+  </si>
+  <si>
+    <t>5 bosqichli savol berish sxemasida 3-bosqich nima?</t>
+  </si>
+  <si>
+    <t>Nozik joyidan teskari savol berish</t>
+  </si>
+  <si>
+    <t>Bahoni aytish</t>
+  </si>
+  <si>
+    <t>Slayd yopish</t>
+  </si>
+  <si>
+    <t>5 bosqichli savol berish sxemasida 4-bosqich nima?</t>
+  </si>
+  <si>
+    <t>Mavzu nomi</t>
+  </si>
+  <si>
+    <t>Yangi misol</t>
+  </si>
+  <si>
+    <t>Uy vazifa</t>
+  </si>
+  <si>
+    <t>5 bosqichli savol berish sxemasida 5-bosqich nima?</t>
+  </si>
+  <si>
+    <t>Yangi misol berib yechimini aniqlash</t>
+  </si>
+  <si>
+    <t>Davomat</t>
+  </si>
+  <si>
+    <t>Baholash</t>
+  </si>
+  <si>
+    <t>Telegramga yozish</t>
+  </si>
+  <si>
+    <t>Warm-up faoliyati qancha vaqt davom etishi kerak?</t>
+  </si>
+  <si>
+    <t>2-3 daqiqa</t>
+  </si>
+  <si>
+    <t>Warm-up faoliyatiga qaysi biri mos?</t>
+  </si>
+  <si>
+    <t>Yangi mavzuga oid qiziqarli savol</t>
+  </si>
+  <si>
+    <t>Oylik maosh muhokamasi</t>
+  </si>
+  <si>
+    <t>Darsni tark etish</t>
+  </si>
+  <si>
+    <t>Jazo berish</t>
+  </si>
+  <si>
+    <t>Warm-up uchun amaliy keys nimaga xizmat qiladi?</t>
+  </si>
+  <si>
+    <t>E'tiborni darsga qaratishga</t>
+  </si>
+  <si>
+    <t>Davomatni yashirishga</t>
+  </si>
+  <si>
+    <t>Vaqt o'tkazishga</t>
+  </si>
+  <si>
+    <t>Uy vazifani bekor qilishga</t>
+  </si>
+  <si>
+    <t>Mavzuni boshlashdan avval o'quvchilarda nima shakllantiriladi?</t>
+  </si>
+  <si>
+    <t>Ehtiyoj</t>
+  </si>
+  <si>
+    <t>Qo'rquv</t>
+  </si>
+  <si>
+    <t>Charchoq</t>
+  </si>
+  <si>
+    <t>Jazo hissi</t>
+  </si>
+  <si>
+    <t>Nazariy ma'ruza vaqtida kompyuter qopqoqlari qanday bo'lishi so'raladi?</t>
+  </si>
+  <si>
+    <t>Butunlay yopiq</t>
+  </si>
+  <si>
+    <t>Ochiq</t>
+  </si>
+  <si>
+    <t>Yarim ochiq</t>
+  </si>
+  <si>
+    <t>Farqi yo'q</t>
+  </si>
+  <si>
+    <t>Yangi mavzu nechta asosiy qismda tushuntiriladi?</t>
+  </si>
+  <si>
+    <t>2 ta</t>
+  </si>
+  <si>
+    <t>3 ta</t>
+  </si>
+  <si>
+    <t>4 ta</t>
+  </si>
+  <si>
+    <t>5 ta</t>
+  </si>
+  <si>
+    <t>Yangi mavzu tushuntirishning 1-qismi nima?</t>
+  </si>
+  <si>
+    <t>Nazariya</t>
+  </si>
+  <si>
+    <t>Live coding</t>
+  </si>
+  <si>
+    <t>Natija tahlili</t>
+  </si>
+  <si>
+    <t>Yangi mavzu tushuntirishning 2-qismi nima?</t>
+  </si>
+  <si>
+    <t>Ekranda namuna ko'rsatish</t>
+  </si>
+  <si>
+    <t>Tanaffus</t>
+  </si>
+  <si>
+    <t>Musobaqa</t>
+  </si>
+  <si>
+    <t>Yangi mavzu tushuntirishning 3-qismi nima?</t>
+  </si>
+  <si>
+    <t>Natija va ko'rinishini tahlil qilish</t>
+  </si>
+  <si>
+    <t>Telegram yozish</t>
+  </si>
+  <si>
+    <t>Beyjik taqish</t>
+  </si>
+  <si>
+    <t>Mavzu bloklarga bo'lingach har bir blokdan so'ng nima o'tkaziladi?</t>
+  </si>
+  <si>
+    <t>Amaliy mashq va kviz</t>
+  </si>
+  <si>
+    <t>Oylik suhbat</t>
+  </si>
+  <si>
+    <t>Guruhlarda sinf ishi paytida ustoz nima qiladi?</t>
+  </si>
+  <si>
+    <t>Xona bo'ylab yurib nazorat qiladi</t>
+  </si>
+  <si>
+    <t>Telefon ishlatadi</t>
+  </si>
+  <si>
+    <t>Xonadan chiqadi</t>
+  </si>
+  <si>
+    <t>Faqat o'tiradi</t>
+  </si>
+  <si>
+    <t>Peer-review usuli nimani bildiradi?</t>
+  </si>
+  <si>
+    <t>O'quvchilar bir-birining ishiga fidbek beradi</t>
+  </si>
+  <si>
+    <t>Faqat ustoz baholaydi</t>
+  </si>
+  <si>
+    <t>Ota-ona baholaydi</t>
+  </si>
+  <si>
+    <t>ERP avtomatik tekshiradi</t>
+  </si>
+  <si>
+    <t>Darsni kimlarning xulosasi orqali yakunlash tavsiya etiladi?</t>
+  </si>
+  <si>
+    <t>3-4 o'quvchi</t>
+  </si>
+  <si>
+    <t>Faqat ustoz</t>
+  </si>
+  <si>
+    <t>Faqat administrator</t>
+  </si>
+  <si>
+    <t>Faqat ota-ona</t>
+  </si>
+  <si>
+    <t>Dars yakuni uchun maksimal qancha vaqt ajratiladi?</t>
+  </si>
+  <si>
+    <t>Dars yakunida mavzu maqsadlari yozilgan slaydga nima qilinadi?</t>
+  </si>
+  <si>
+    <t>Qaytiladi va bajarilgani tasdiqlatiladi</t>
+  </si>
+  <si>
+    <t>O'chiriladi</t>
+  </si>
+  <si>
+    <t>Yashiriladi</t>
+  </si>
+  <si>
+    <t>Uyga yuborilmaydi</t>
+  </si>
+  <si>
+    <t>Uy vazifasi qachon ERP tizimiga yuklanadi?</t>
+  </si>
+  <si>
+    <t>Dars ochiq bo'lgan vaqtda</t>
+  </si>
+  <si>
+    <t>Ertasi kuni</t>
+  </si>
+  <si>
+    <t>Ota-ona so'raganda</t>
+  </si>
+  <si>
+    <t>Uy vazifasi berilganda nimalar maydalab tushuntiriladi?</t>
+  </si>
+  <si>
+    <t>Bajarish tartibi, muhlat, manbalar</t>
+  </si>
+  <si>
+    <t>Rahbarlar ismi</t>
+  </si>
+  <si>
+    <t>Shaxsiy reja</t>
+  </si>
+  <si>
+    <t>Uy vazifasini tushuntirgach o'quvchilardan nima tasdiqlanadi?</t>
+  </si>
+  <si>
+    <t>Vazifa tushunarli bo'lgani</t>
+  </si>
+  <si>
+    <t>Bahosi</t>
+  </si>
+  <si>
+    <t>Markazda qanday rangdagi kiyimlar tavsiya etiladi?</t>
+  </si>
+  <si>
+    <t>Oq-qora, och havorang, och kulrang, qaymoq</t>
+  </si>
+  <si>
+    <t>Neon rang</t>
+  </si>
+  <si>
+    <t>Qizil-yashil naqshli</t>
+  </si>
+  <si>
+    <t>Faqat sport kiyimi</t>
+  </si>
+  <si>
+    <t>Kiyim qanday holatda bo'lishi kerak?</t>
+  </si>
+  <si>
+    <t>Pokiza va dazmollangan</t>
+  </si>
+  <si>
+    <t>Kir va g'ijim</t>
+  </si>
+  <si>
+    <t>Yirtiq</t>
+  </si>
+  <si>
+    <t>Shippak bilan</t>
+  </si>
+  <si>
+    <t>Qaysi kiyim taqiqlanadi?</t>
+  </si>
+  <si>
+    <t>Behayo yozuv va rasmlari bor kiyim</t>
+  </si>
+  <si>
+    <t>Klassik oq ko'ylak</t>
+  </si>
+  <si>
+    <t>Och kulrang shim</t>
+  </si>
+  <si>
+    <t>Dazmollangan kiyim</t>
+  </si>
+  <si>
+    <t>Qaysi kiyim bilan kelish mumkin emas?</t>
+  </si>
+  <si>
+    <t>Shortik</t>
+  </si>
+  <si>
+    <t>Klassik shim</t>
+  </si>
+  <si>
+    <t>Oq ko'ylak</t>
+  </si>
+  <si>
+    <t>Qaymoq rang kiyim</t>
+  </si>
+  <si>
+    <t>Oyoq kiyim qanday bo'lishi kerak?</t>
+  </si>
+  <si>
+    <t>Loy, chang va yirtilmagan</t>
+  </si>
+  <si>
+    <t>Loy va chang</t>
+  </si>
+  <si>
+    <t>Orqasi ezilgan</t>
+  </si>
+  <si>
+    <t>Qaysi oyoq kiyim taqiqlanadi?</t>
+  </si>
+  <si>
+    <t>Trippak/shippak</t>
+  </si>
+  <si>
+    <t>Toza tufli</t>
+  </si>
+  <si>
+    <t>Klassik oyoq kiyim</t>
+  </si>
+  <si>
+    <t>Chang bo'lmagan poyabzal</t>
+  </si>
+  <si>
+    <t>Oyoq kiyimni qanday kiyish taqiqlanadi?</t>
+  </si>
+  <si>
+    <t>Orqasini ezgan holatda</t>
+  </si>
+  <si>
+    <t>To'liq kiyilgan</t>
+  </si>
+  <si>
+    <t>Toza kiyilgan</t>
+  </si>
+  <si>
+    <t>Bog'ichi bog'langan</t>
+  </si>
+  <si>
+    <t>O'quvchilar bilan ko'z orqali muloqot nima uchun kerak?</t>
+  </si>
+  <si>
+    <t>Diqqatini ushlab turish uchun</t>
+  </si>
+  <si>
+    <t>Bahoni yashirish uchun</t>
+  </si>
+  <si>
+    <t>Telefon ishlatish uchun</t>
+  </si>
+  <si>
+    <t>Vaqtni cho'zish uchun</t>
+  </si>
+  <si>
+    <t>Nutqda nimalarga rioya qilish kerak?</t>
+  </si>
+  <si>
+    <t>Diksiya va artikulyatsiya</t>
+  </si>
+  <si>
+    <t>Monoton ohang</t>
+  </si>
+  <si>
+    <t>Juda murakkab iboralar</t>
+  </si>
+  <si>
+    <t>Jim turish</t>
+  </si>
+  <si>
+    <t>Monoton bir xil ohangda gapirish nimaga olib keladi?</t>
+  </si>
+  <si>
+    <t>Dars zerikarli bo'lishiga</t>
+  </si>
+  <si>
+    <t>Dars qiziq bo'lishiga</t>
+  </si>
+  <si>
+    <t>Davomat oshishiga</t>
+  </si>
+  <si>
+    <t>Baholar yaxshilanishiga</t>
+  </si>
+  <si>
+    <t>Darsda tana tili bo'yicha qaysi holat xunuk ko'rinadi?</t>
+  </si>
+  <si>
+    <t>Qo'lni cho'ntakka solish</t>
+  </si>
+  <si>
+    <t>Xona bo'ylab harakatlanish</t>
+  </si>
+  <si>
+    <t>Ko'z bilan muloqot</t>
+  </si>
+  <si>
+    <t>Sergak turish</t>
+  </si>
+  <si>
+    <t>8-15 yoshli bolalar bilan qanday til ishlatiladi?</t>
+  </si>
+  <si>
+    <t>Oson tushuniladigan til</t>
+  </si>
+  <si>
+    <t>Juda murakkab texnik til</t>
+  </si>
+  <si>
+    <t>Faqat rasmiy til</t>
+  </si>
+  <si>
+    <t>Darsda uxlab qolgan yoki o'yin o'ynayotgan bola bo'lsa, birinchi yondashuv nima?</t>
+  </si>
+  <si>
+    <t>Toza havo kiritish va darsga qaytarish</t>
+  </si>
+  <si>
+    <t>Jismoniy jazo</t>
+  </si>
+  <si>
+    <t>Guruh oldida kamsitish</t>
+  </si>
+  <si>
+    <t>Uyiga jo'natish</t>
+  </si>
+  <si>
+    <t>Chalg'igan bolani qo'pol urishmasdan qanday qaytarish tavsiya etiladi?</t>
+  </si>
+  <si>
+    <t>Ismi bilan savol berish</t>
+  </si>
+  <si>
+    <t>Baqirish</t>
+  </si>
+  <si>
+    <t>Sinfdan chiqarish</t>
+  </si>
+  <si>
+    <t>O'quvchilarga nisbatan jismoniy yoki ruhiy jazo qo'llash mumkinmi?</t>
+  </si>
+  <si>
+    <t>Ba'zida</t>
+  </si>
+  <si>
+    <t>Faqat kichiklarga</t>
+  </si>
+  <si>
+    <t>Atjimaniya qildirish qanday holat?</t>
+  </si>
+  <si>
+    <t>Qat'iyan taqiqlangan</t>
+  </si>
+  <si>
+    <t>Tavsiya etilgan</t>
+  </si>
+  <si>
+    <t>Sport darsi</t>
+  </si>
+  <si>
+    <t>Surunkali vazifa qilmaydigan o'quvchi bilan qanday suhbatlashiladi?</t>
+  </si>
+  <si>
+    <t>Ketma-ket 'nega' savoli bilan</t>
+  </si>
+  <si>
+    <t>Darhol 0 qo'yib</t>
+  </si>
+  <si>
+    <t>Guruhdan chiqarib</t>
+  </si>
+  <si>
+    <t>E'tiborsiz qoldirib</t>
+  </si>
+  <si>
+    <t>'Nega' savoli kamida nechanchi savolgacha davom etishi tavsiya etiladi?</t>
+  </si>
+  <si>
+    <t>2-savolgacha</t>
+  </si>
+  <si>
+    <t>4-savolgacha</t>
+  </si>
+  <si>
+    <t>7-savolgacha</t>
+  </si>
+  <si>
+    <t>10-savolgacha</t>
+  </si>
+  <si>
+    <t>Tanaffus vaqti qancha bo'lishi kerak?</t>
+  </si>
+  <si>
+    <t>5-10 daqiqa</t>
+  </si>
+  <si>
+    <t>15-20 daqiqa</t>
+  </si>
+  <si>
+    <t>Tanaffusdan darsga qaytish vaqtini nima qilish mumkin emas?</t>
+  </si>
+  <si>
+    <t>O'g'irlash</t>
+  </si>
+  <si>
+    <t>Aniq belgilash</t>
+  </si>
+  <si>
+    <t>Eslatish</t>
+  </si>
+  <si>
+    <t>Nazorat qilish</t>
+  </si>
+  <si>
+    <t>Katta musobaqalar qanday yosh toifalari asosida o'tkaziladi?</t>
+  </si>
+  <si>
+    <t>9-11 va 9-15</t>
+  </si>
+  <si>
+    <t>5-7 va 8-9</t>
+  </si>
+  <si>
+    <t>16-18 va 19-20</t>
+  </si>
+  <si>
+    <t>Faqat 9-15</t>
+  </si>
+  <si>
+    <t>Katta musobaqa qanchada bir marta o'tkaziladi?</t>
+  </si>
+  <si>
+    <t>Har oy</t>
+  </si>
+  <si>
+    <t>Har 2 oyda</t>
+  </si>
+  <si>
+    <t>Har 6 oyda</t>
+  </si>
+  <si>
+    <t>Har hafta</t>
+  </si>
+  <si>
+    <t>Musobaqaga qo'shimcha event sifatida nimalar navbatma-navbat keladi?</t>
+  </si>
+  <si>
+    <t>Typing va loyihalar taqdimoti</t>
+  </si>
+  <si>
+    <t>Futbol va shaxmat</t>
+  </si>
+  <si>
+    <t>Rasm va musiqa</t>
+  </si>
+  <si>
+    <t>Faqat imtihon</t>
+  </si>
+  <si>
+    <t>Musobaqa haqida qachon oldindan e'lon qilinadi?</t>
+  </si>
+  <si>
+    <t>2 oy oldin</t>
+  </si>
+  <si>
+    <t>1 hafta oldin</t>
+  </si>
+  <si>
+    <t>Musobaqa kuni</t>
+  </si>
+  <si>
+    <t>Musobaqa e'lonida nimalar aks etishi kerak?</t>
+  </si>
+  <si>
+    <t>Taxminiy sana, qat'iy shartlar, yo'nalishlar</t>
+  </si>
+  <si>
+    <t>Ustoz maoshi</t>
+  </si>
+  <si>
+    <t>Ichki shartnoma bahslari</t>
+  </si>
+  <si>
+    <t>Faqat sovg'a rasmi</t>
+  </si>
+  <si>
+    <t>Saralash jarayoni qachon yakunlanishi kerak?</t>
+  </si>
+  <si>
+    <t>Musobaqadan 1 hafta oldin</t>
+  </si>
+  <si>
+    <t>Saralashdan olingan foto/video materiallar kimga taqdim etiladi?</t>
+  </si>
+  <si>
+    <t>Marketing bo'limiga</t>
+  </si>
+  <si>
+    <t>Ota-onaga yashirincha</t>
+  </si>
+  <si>
+    <t>O'quvchiga</t>
+  </si>
+  <si>
+    <t>Wi-Fi adminiga</t>
+  </si>
+  <si>
+    <t>Musobaqadan 3 kun oldin ota-onalar guruhiga nima yuboriladi?</t>
+  </si>
+  <si>
+    <t>Saralashdan o'tganlar ro'yxati va aniq jadval</t>
+  </si>
+  <si>
+    <t>Ustoz oyligi</t>
+  </si>
+  <si>
+    <t>Wi-Fi paroli</t>
+  </si>
+  <si>
+    <t>Musobaqadan 1 kun oldin nima yuboriladi?</t>
+  </si>
+  <si>
+    <t>Oxirgi eslatma xabari</t>
+  </si>
+  <si>
+    <t>Yangi shartnoma</t>
+  </si>
+  <si>
+    <t>Baholar</t>
+  </si>
+  <si>
+    <t>Dars jadvali bekori</t>
+  </si>
+  <si>
+    <t>Musobaqadan 1 kun oldin filialda nimalar tayyor bo'lishi kerak?</t>
+  </si>
+  <si>
+    <t>Kovorking hududi, sovg'alar, sertifikatlar</t>
+  </si>
+  <si>
+    <t>Faqat Wi-Fi</t>
+  </si>
+  <si>
+    <t>Faqat telefon</t>
+  </si>
+  <si>
+    <t>Faqat dars xonasi</t>
+  </si>
+  <si>
+    <t>Event davomida ota-onalar bilan kimlar ochiq suhbat o'tkazadi?</t>
+  </si>
+  <si>
+    <t>Team Lead va filial menejeri</t>
+  </si>
+  <si>
+    <t>Faqat o'quvchilar</t>
+  </si>
+  <si>
+    <t>Faqat support teacher</t>
+  </si>
+  <si>
+    <t>O'qituvchi bir oyda nechta favqulodda sababsiz dars qoldirishi mumkin emas?</t>
+  </si>
+  <si>
+    <t>1 martadan ortiq</t>
+  </si>
+  <si>
+    <t>2 martadan ortiq</t>
+  </si>
+  <si>
+    <t>3 martadan ortiq</t>
+  </si>
+  <si>
+    <t>Cheklov yo'q</t>
+  </si>
+  <si>
+    <t>Dars qoldirish zarur bo'lsa, kamida qachon rasmiy guruhda ogohlantirish kerak?</t>
+  </si>
+  <si>
+    <t>1 soat oldin</t>
+  </si>
+  <si>
+    <t>Dars qoldirganda o'rniga kim topilishi kerak?</t>
+  </si>
+  <si>
+    <t>Ustoz</t>
+  </si>
+  <si>
+    <t>O'quvchi</t>
+  </si>
+  <si>
+    <t>Ota-ona</t>
+  </si>
+  <si>
+    <t>Reception</t>
+  </si>
+  <si>
+    <t>Support teacher ruxsatsiz darsda qoldirilishi mumkinmi?</t>
+  </si>
+  <si>
+    <t>Faqat kichik guruhda</t>
+  </si>
+  <si>
+    <t>Dars 08:30 da boshlansa, ustoz qachon xonada bo'lishi kerak?</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>1 daqiqa kechikish ham hisobga olinadimi?</t>
+  </si>
+  <si>
+    <t>Faqat imtihonda</t>
+  </si>
+  <si>
+    <t>Faqat ota-ona ko'rsa</t>
+  </si>
+  <si>
+    <t>1-5 daqiqa kechikish qanday hisoblanadi?</t>
+  </si>
+  <si>
+    <t>Kichik kechikish</t>
+  </si>
+  <si>
+    <t>Katta kechikish</t>
+  </si>
+  <si>
+    <t>Hisoblanmaydi</t>
+  </si>
+  <si>
+    <t>Mukofot</t>
+  </si>
+  <si>
+    <t>5 daqiqadan ortiq kechikish qanday hisoblanadi?</t>
+  </si>
+  <si>
+    <t>Ogohlantirish emas</t>
+  </si>
+  <si>
+    <t>3 ta kichik kechikish nimaga teng?</t>
+  </si>
+  <si>
+    <t>1 ta katta kechikish</t>
+  </si>
+  <si>
+    <t>2 ta katta kechikish</t>
+  </si>
+  <si>
+    <t>Yarim kechikish</t>
+  </si>
+  <si>
+    <t>O'quvchilarning darsda uxlab qolishi qaysi ro'yxatga kiradi?</t>
+  </si>
+  <si>
+    <t>Taqiqlangan holatlar</t>
+  </si>
+  <si>
+    <t>Mukofotlar</t>
+  </si>
+  <si>
+    <t>O'quvchilarga ustozning haqiqiy yoshi haqida gapirish mumkinmi?</t>
+  </si>
+  <si>
+    <t>Faqat 15 yoshdan kattalarga</t>
+  </si>
+  <si>
+    <t>O'quvchilarga ustozning shaxsiy oylik maoshi haqida gapirish mumkinmi?</t>
+  </si>
+  <si>
+    <t>Faqat yakka tartibda</t>
+  </si>
+  <si>
+    <t>O'quvchilar bilan tizim, rahbarlar yoki shartnoma bandlarini muhokama qilish mumkinmi?</t>
+  </si>
+  <si>
+    <t>Faqat norasmiy</t>
+  </si>
+  <si>
+    <t>Qo'pol so'zlashish qanday hisoblanadi?</t>
+  </si>
+  <si>
+    <t>Jiddiy intizomiy holat</t>
+  </si>
+  <si>
+    <t>Oddiy holat</t>
+  </si>
+  <si>
+    <t>Tavsiya</t>
+  </si>
+  <si>
+    <t>Bolalarni guruh oldida kamsitish mumkinmi?</t>
+  </si>
+  <si>
+    <t>Faqat ogohlantirish sifatida</t>
+  </si>
+  <si>
+    <t>Dars vaqtida telefonda chalg'ib o'tirish mumkinmi?</t>
+  </si>
+  <si>
+    <t>Faqat 5 daqiqa</t>
+  </si>
+  <si>
+    <t>Faqat xabar yozish</t>
+  </si>
+  <si>
+    <t>Darsni tekshiruvlar tufayli sababsiz tark etish mumkinmi?</t>
+  </si>
+  <si>
+    <t>Faqat charchasa</t>
+  </si>
+  <si>
+    <t>Faqat tanaffusdan oldin</t>
+  </si>
+  <si>
+    <t>Wi-Fi vaucher tarmog'iga ulanishda qaysi tarmoq tanlanadi?</t>
+  </si>
+  <si>
+    <t>Wi-Fi vaucher</t>
+  </si>
+  <si>
+    <t>Home Wi-Fi</t>
+  </si>
+  <si>
+    <t>Guest random</t>
+  </si>
+  <si>
+    <t>Admin only</t>
+  </si>
+  <si>
+    <t>Wi-Fi ID qanday yoziladi?</t>
+  </si>
+  <si>
+    <t>ID1234</t>
+  </si>
+  <si>
+    <t>id1234</t>
+  </si>
+  <si>
+    <t>Id 1234</t>
+  </si>
+  <si>
+    <t>ID 1234</t>
+  </si>
+  <si>
+    <t>Wi-Fi parolida telefon raqami qanday yoziladi?</t>
+  </si>
+  <si>
+    <t>+ belgisisiz</t>
+  </si>
+  <si>
+    <t>Plus belgisi bilan</t>
+  </si>
+  <si>
+    <t>Bo'shliqlar bilan</t>
+  </si>
+  <si>
+    <t>Harflar bilan</t>
+  </si>
+  <si>
+    <t>Wi-Fi boshqa qurilmaga ulanmayotgan bo'lsa, avval nima qilish mumkin?</t>
+  </si>
+  <si>
+    <t>Forget qilib qayta ulash</t>
+  </si>
+  <si>
+    <t>Kompyuterni sindirish</t>
+  </si>
+  <si>
+    <t>Parolni o'zgartirish</t>
+  </si>
+  <si>
+    <t>Ustozlik mahorati video-darslari qayerda berilgan?</t>
+  </si>
+  <si>
+    <t>Telegram havolasida</t>
+  </si>
+  <si>
+    <t>ERP bahosida</t>
+  </si>
+  <si>
+    <t>Wi-Fi parolida</t>
+  </si>
+  <si>
+    <t>Dress code ro'yxatida</t>
+  </si>
+  <si>
+    <t>Head teacher bilan bog'lanish uchun kim ko'rsatilgan?</t>
+  </si>
+  <si>
+    <t>Ibrohim Qodirov</t>
+  </si>
+  <si>
+    <t>Hasanboy Majidov</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>O'quv bo'limi Timlideri sifatida kim ko'rsatilgan?</t>
+  </si>
+  <si>
+    <t>Support teacher</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -3393,15 +4608,72 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{ADC10834-717D-46AE-A129-B1902B1B36B6}"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3737,16 +5009,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H226"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H338"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="8" width="30" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="56.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3772,7 +5049,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3798,7 +5075,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -3824,7 +5101,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3850,7 +5127,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3876,7 +5153,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3902,7 +5179,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -3928,7 +5205,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -3954,7 +5231,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3980,7 +5257,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -4006,7 +5283,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -4032,7 +5309,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -4058,7 +5335,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -4084,7 +5361,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -4110,7 +5387,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -4136,7 +5413,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -4162,7 +5439,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -4188,7 +5465,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -4214,7 +5491,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -4240,7 +5517,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -4266,7 +5543,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -4292,7 +5569,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -4318,7 +5595,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -4344,7 +5621,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -4370,7 +5647,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -4396,7 +5673,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -4422,7 +5699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>136</v>
       </c>
@@ -4448,7 +5725,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>136</v>
       </c>
@@ -4474,7 +5751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>136</v>
       </c>
@@ -4500,7 +5777,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>136</v>
       </c>
@@ -4526,7 +5803,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
         <v>136</v>
       </c>
@@ -4552,7 +5829,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>136</v>
       </c>
@@ -4578,7 +5855,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
         <v>136</v>
       </c>
@@ -4604,7 +5881,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>136</v>
       </c>
@@ -4630,7 +5907,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
         <v>136</v>
       </c>
@@ -4656,7 +5933,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>136</v>
       </c>
@@ -4682,7 +5959,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
         <v>136</v>
       </c>
@@ -4708,7 +5985,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
         <v>136</v>
       </c>
@@ -4734,7 +6011,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
         <v>136</v>
       </c>
@@ -4760,7 +6037,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
         <v>136</v>
       </c>
@@ -4786,7 +6063,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
         <v>136</v>
       </c>
@@ -4812,7 +6089,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
         <v>136</v>
       </c>
@@ -4838,7 +6115,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
         <v>136</v>
       </c>
@@ -4864,7 +6141,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
         <v>136</v>
       </c>
@@ -4890,7 +6167,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
         <v>136</v>
       </c>
@@ -4916,7 +6193,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" t="s">
         <v>136</v>
       </c>
@@ -4942,7 +6219,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8">
       <c r="A47" t="s">
         <v>136</v>
       </c>
@@ -4968,7 +6245,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" t="s">
         <v>136</v>
       </c>
@@ -4994,7 +6271,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
         <v>136</v>
       </c>
@@ -5020,7 +6297,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
         <v>136</v>
       </c>
@@ -5046,7 +6323,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
         <v>136</v>
       </c>
@@ -5072,7 +6349,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
         <v>259</v>
       </c>
@@ -5098,7 +6375,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
         <v>259</v>
       </c>
@@ -5124,7 +6401,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
         <v>259</v>
       </c>
@@ -5150,7 +6427,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
         <v>259</v>
       </c>
@@ -5176,7 +6453,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
         <v>259</v>
       </c>
@@ -5202,7 +6479,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
         <v>259</v>
       </c>
@@ -5228,7 +6505,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
         <v>259</v>
       </c>
@@ -5254,7 +6531,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
         <v>259</v>
       </c>
@@ -5280,7 +6557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
         <v>259</v>
       </c>
@@ -5306,7 +6583,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
         <v>259</v>
       </c>
@@ -5332,7 +6609,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
         <v>259</v>
       </c>
@@ -5358,7 +6635,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
         <v>259</v>
       </c>
@@ -5384,7 +6661,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
         <v>259</v>
       </c>
@@ -5410,7 +6687,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
         <v>259</v>
       </c>
@@ -5436,7 +6713,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
         <v>259</v>
       </c>
@@ -5462,7 +6739,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
         <v>259</v>
       </c>
@@ -5488,7 +6765,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
         <v>259</v>
       </c>
@@ -5514,7 +6791,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
         <v>259</v>
       </c>
@@ -5540,7 +6817,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
         <v>259</v>
       </c>
@@ -5566,7 +6843,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
         <v>259</v>
       </c>
@@ -5592,7 +6869,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
         <v>259</v>
       </c>
@@ -5618,7 +6895,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
         <v>259</v>
       </c>
@@ -5644,7 +6921,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
         <v>259</v>
       </c>
@@ -5670,7 +6947,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
         <v>259</v>
       </c>
@@ -5696,7 +6973,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
         <v>259</v>
       </c>
@@ -5722,7 +6999,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
         <v>381</v>
       </c>
@@ -5748,7 +7025,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8">
       <c r="A78" t="s">
         <v>381</v>
       </c>
@@ -5774,7 +7051,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8">
       <c r="A79" t="s">
         <v>381</v>
       </c>
@@ -5800,7 +7077,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8">
       <c r="A80" t="s">
         <v>381</v>
       </c>
@@ -5826,7 +7103,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8">
       <c r="A81" t="s">
         <v>381</v>
       </c>
@@ -5852,7 +7129,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8">
       <c r="A82" t="s">
         <v>381</v>
       </c>
@@ -5878,7 +7155,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8">
       <c r="A83" t="s">
         <v>381</v>
       </c>
@@ -5904,7 +7181,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8">
       <c r="A84" t="s">
         <v>381</v>
       </c>
@@ -5930,7 +7207,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8">
       <c r="A85" t="s">
         <v>381</v>
       </c>
@@ -5956,7 +7233,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8">
       <c r="A86" t="s">
         <v>381</v>
       </c>
@@ -5982,7 +7259,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8">
       <c r="A87" t="s">
         <v>381</v>
       </c>
@@ -6008,7 +7285,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8">
       <c r="A88" t="s">
         <v>381</v>
       </c>
@@ -6034,7 +7311,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8">
       <c r="A89" t="s">
         <v>381</v>
       </c>
@@ -6060,7 +7337,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8">
       <c r="A90" t="s">
         <v>381</v>
       </c>
@@ -6086,7 +7363,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8">
       <c r="A91" t="s">
         <v>381</v>
       </c>
@@ -6112,7 +7389,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8">
       <c r="A92" t="s">
         <v>381</v>
       </c>
@@ -6138,7 +7415,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8">
       <c r="A93" t="s">
         <v>381</v>
       </c>
@@ -6164,7 +7441,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8">
       <c r="A94" t="s">
         <v>381</v>
       </c>
@@ -6190,7 +7467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8">
       <c r="A95" t="s">
         <v>381</v>
       </c>
@@ -6216,7 +7493,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8">
       <c r="A96" t="s">
         <v>381</v>
       </c>
@@ -6242,7 +7519,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
         <v>381</v>
       </c>
@@ -6268,7 +7545,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8">
       <c r="A98" t="s">
         <v>381</v>
       </c>
@@ -6294,7 +7571,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8">
       <c r="A99" t="s">
         <v>381</v>
       </c>
@@ -6320,7 +7597,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8">
       <c r="A100" t="s">
         <v>381</v>
       </c>
@@ -6346,7 +7623,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8">
       <c r="A101" t="s">
         <v>381</v>
       </c>
@@ -6372,7 +7649,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8">
       <c r="A102" t="s">
         <v>504</v>
       </c>
@@ -6398,7 +7675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8">
       <c r="A103" t="s">
         <v>504</v>
       </c>
@@ -6424,7 +7701,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8">
       <c r="A104" t="s">
         <v>504</v>
       </c>
@@ -6450,7 +7727,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8">
       <c r="A105" t="s">
         <v>504</v>
       </c>
@@ -6476,7 +7753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8">
       <c r="A106" t="s">
         <v>504</v>
       </c>
@@ -6502,7 +7779,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8">
       <c r="A107" t="s">
         <v>504</v>
       </c>
@@ -6528,7 +7805,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8">
       <c r="A108" t="s">
         <v>504</v>
       </c>
@@ -6554,7 +7831,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8">
       <c r="A109" t="s">
         <v>504</v>
       </c>
@@ -6580,7 +7857,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8">
       <c r="A110" t="s">
         <v>504</v>
       </c>
@@ -6606,7 +7883,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8">
       <c r="A111" t="s">
         <v>504</v>
       </c>
@@ -6632,7 +7909,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8">
       <c r="A112" t="s">
         <v>504</v>
       </c>
@@ -6658,7 +7935,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8">
       <c r="A113" t="s">
         <v>504</v>
       </c>
@@ -6684,7 +7961,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8">
       <c r="A114" t="s">
         <v>504</v>
       </c>
@@ -6710,7 +7987,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8">
       <c r="A115" t="s">
         <v>504</v>
       </c>
@@ -6736,7 +8013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8">
       <c r="A116" t="s">
         <v>504</v>
       </c>
@@ -6762,7 +8039,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8">
       <c r="A117" t="s">
         <v>504</v>
       </c>
@@ -6788,7 +8065,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8">
       <c r="A118" t="s">
         <v>504</v>
       </c>
@@ -6814,7 +8091,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8">
       <c r="A119" t="s">
         <v>504</v>
       </c>
@@ -6840,7 +8117,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8">
       <c r="A120" t="s">
         <v>504</v>
       </c>
@@ -6866,7 +8143,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8">
       <c r="A121" t="s">
         <v>504</v>
       </c>
@@ -6892,7 +8169,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8">
       <c r="A122" t="s">
         <v>504</v>
       </c>
@@ -6918,7 +8195,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8">
       <c r="A123" t="s">
         <v>504</v>
       </c>
@@ -6944,7 +8221,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8">
       <c r="A124" t="s">
         <v>504</v>
       </c>
@@ -6970,7 +8247,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8">
       <c r="A125" t="s">
         <v>504</v>
       </c>
@@ -6996,7 +8273,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8">
       <c r="A126" t="s">
         <v>504</v>
       </c>
@@ -7022,7 +8299,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8">
       <c r="A127" t="s">
         <v>626</v>
       </c>
@@ -7048,7 +8325,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8">
       <c r="A128" t="s">
         <v>626</v>
       </c>
@@ -7074,7 +8351,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8">
       <c r="A129" t="s">
         <v>626</v>
       </c>
@@ -7100,7 +8377,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8">
       <c r="A130" t="s">
         <v>626</v>
       </c>
@@ -7126,7 +8403,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8">
       <c r="A131" t="s">
         <v>626</v>
       </c>
@@ -7152,7 +8429,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8">
       <c r="A132" t="s">
         <v>626</v>
       </c>
@@ -7178,7 +8455,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8">
       <c r="A133" t="s">
         <v>626</v>
       </c>
@@ -7204,7 +8481,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8">
       <c r="A134" t="s">
         <v>626</v>
       </c>
@@ -7230,7 +8507,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8">
       <c r="A135" t="s">
         <v>626</v>
       </c>
@@ -7256,7 +8533,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8">
       <c r="A136" t="s">
         <v>626</v>
       </c>
@@ -7282,7 +8559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8">
       <c r="A137" t="s">
         <v>626</v>
       </c>
@@ -7308,7 +8585,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8">
       <c r="A138" t="s">
         <v>626</v>
       </c>
@@ -7334,7 +8611,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8">
       <c r="A139" t="s">
         <v>626</v>
       </c>
@@ -7360,7 +8637,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8">
       <c r="A140" t="s">
         <v>626</v>
       </c>
@@ -7386,7 +8663,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8">
       <c r="A141" t="s">
         <v>626</v>
       </c>
@@ -7412,7 +8689,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8">
       <c r="A142" t="s">
         <v>626</v>
       </c>
@@ -7438,7 +8715,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8">
       <c r="A143" t="s">
         <v>626</v>
       </c>
@@ -7464,7 +8741,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8">
       <c r="A144" t="s">
         <v>626</v>
       </c>
@@ -7490,7 +8767,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8">
       <c r="A145" t="s">
         <v>626</v>
       </c>
@@ -7516,7 +8793,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8">
       <c r="A146" t="s">
         <v>626</v>
       </c>
@@ -7542,7 +8819,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8">
       <c r="A147" t="s">
         <v>626</v>
       </c>
@@ -7568,7 +8845,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8">
       <c r="A148" t="s">
         <v>626</v>
       </c>
@@ -7594,7 +8871,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8">
       <c r="A149" t="s">
         <v>626</v>
       </c>
@@ -7620,7 +8897,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8">
       <c r="A150" t="s">
         <v>626</v>
       </c>
@@ -7646,7 +8923,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8">
       <c r="A151" t="s">
         <v>626</v>
       </c>
@@ -7672,7 +8949,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8">
       <c r="A152" t="s">
         <v>747</v>
       </c>
@@ -7698,7 +8975,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8">
       <c r="A153" t="s">
         <v>747</v>
       </c>
@@ -7724,7 +9001,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8">
       <c r="A154" t="s">
         <v>747</v>
       </c>
@@ -7750,7 +9027,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8">
       <c r="A155" t="s">
         <v>747</v>
       </c>
@@ -7776,7 +9053,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8">
       <c r="A156" t="s">
         <v>747</v>
       </c>
@@ -7802,7 +9079,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8">
       <c r="A157" t="s">
         <v>747</v>
       </c>
@@ -7828,7 +9105,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8">
       <c r="A158" t="s">
         <v>747</v>
       </c>
@@ -7854,7 +9131,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8">
       <c r="A159" t="s">
         <v>747</v>
       </c>
@@ -7880,7 +9157,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8">
       <c r="A160" t="s">
         <v>747</v>
       </c>
@@ -7906,7 +9183,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8">
       <c r="A161" t="s">
         <v>747</v>
       </c>
@@ -7932,7 +9209,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8">
       <c r="A162" t="s">
         <v>747</v>
       </c>
@@ -7958,7 +9235,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8">
       <c r="A163" t="s">
         <v>747</v>
       </c>
@@ -7984,7 +9261,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8">
       <c r="A164" t="s">
         <v>747</v>
       </c>
@@ -8010,7 +9287,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8">
       <c r="A165" t="s">
         <v>747</v>
       </c>
@@ -8036,7 +9313,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8">
       <c r="A166" t="s">
         <v>747</v>
       </c>
@@ -8062,7 +9339,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8">
       <c r="A167" t="s">
         <v>747</v>
       </c>
@@ -8088,7 +9365,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8">
       <c r="A168" t="s">
         <v>747</v>
       </c>
@@ -8114,7 +9391,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8">
       <c r="A169" t="s">
         <v>747</v>
       </c>
@@ -8140,7 +9417,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8">
       <c r="A170" t="s">
         <v>747</v>
       </c>
@@ -8166,7 +9443,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8">
       <c r="A171" t="s">
         <v>747</v>
       </c>
@@ -8192,7 +9469,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8">
       <c r="A172" t="s">
         <v>747</v>
       </c>
@@ -8218,7 +9495,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8">
       <c r="A173" t="s">
         <v>747</v>
       </c>
@@ -8244,7 +9521,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8">
       <c r="A174" t="s">
         <v>747</v>
       </c>
@@ -8270,7 +9547,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8">
       <c r="A175" t="s">
         <v>747</v>
       </c>
@@ -8296,7 +9573,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8">
       <c r="A176" t="s">
         <v>747</v>
       </c>
@@ -8322,7 +9599,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8">
       <c r="A177" t="s">
         <v>868</v>
       </c>
@@ -8348,7 +9625,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8">
       <c r="A178" t="s">
         <v>868</v>
       </c>
@@ -8374,7 +9651,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8">
       <c r="A179" t="s">
         <v>868</v>
       </c>
@@ -8400,7 +9677,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8">
       <c r="A180" t="s">
         <v>868</v>
       </c>
@@ -8426,7 +9703,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8">
       <c r="A181" t="s">
         <v>868</v>
       </c>
@@ -8452,7 +9729,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8">
       <c r="A182" t="s">
         <v>868</v>
       </c>
@@ -8478,7 +9755,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8">
       <c r="A183" t="s">
         <v>868</v>
       </c>
@@ -8504,7 +9781,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8">
       <c r="A184" t="s">
         <v>868</v>
       </c>
@@ -8530,7 +9807,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8">
       <c r="A185" t="s">
         <v>868</v>
       </c>
@@ -8556,7 +9833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8">
       <c r="A186" t="s">
         <v>868</v>
       </c>
@@ -8582,7 +9859,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8">
       <c r="A187" t="s">
         <v>868</v>
       </c>
@@ -8608,7 +9885,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8">
       <c r="A188" t="s">
         <v>868</v>
       </c>
@@ -8634,7 +9911,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8">
       <c r="A189" t="s">
         <v>868</v>
       </c>
@@ -8660,7 +9937,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8">
       <c r="A190" t="s">
         <v>868</v>
       </c>
@@ -8686,7 +9963,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8">
       <c r="A191" t="s">
         <v>868</v>
       </c>
@@ -8712,7 +9989,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8">
       <c r="A192" t="s">
         <v>868</v>
       </c>
@@ -8738,7 +10015,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8">
       <c r="A193" t="s">
         <v>868</v>
       </c>
@@ -8764,7 +10041,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8">
       <c r="A194" t="s">
         <v>868</v>
       </c>
@@ -8790,7 +10067,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8">
       <c r="A195" t="s">
         <v>868</v>
       </c>
@@ -8816,7 +10093,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8">
       <c r="A196" t="s">
         <v>868</v>
       </c>
@@ -8842,7 +10119,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8">
       <c r="A197" t="s">
         <v>868</v>
       </c>
@@ -8868,7 +10145,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8">
       <c r="A198" t="s">
         <v>868</v>
       </c>
@@ -8894,7 +10171,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8">
       <c r="A199" t="s">
         <v>868</v>
       </c>
@@ -8920,7 +10197,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8">
       <c r="A200" t="s">
         <v>868</v>
       </c>
@@ -8946,7 +10223,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8">
       <c r="A201" t="s">
         <v>868</v>
       </c>
@@ -8972,658 +10249,3103 @@
         <v>40</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8">
       <c r="A202" t="s">
         <v>992</v>
       </c>
-      <c r="B202" t="s">
-        <v>993</v>
-      </c>
-      <c r="C202" t="s">
-        <v>994</v>
-      </c>
-      <c r="D202" t="s">
+      <c r="B202" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="E202" t="s">
+      <c r="C202" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D202" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="F202" t="s">
+      <c r="E202" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="G202" t="s">
-        <v>994</v>
+      <c r="F202" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>690</v>
       </c>
       <c r="H202" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" ht="27.6">
       <c r="A203" t="s">
         <v>992</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>996</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>997</v>
+      </c>
+      <c r="F203" s="5" t="s">
         <v>998</v>
       </c>
-      <c r="C203" t="s">
-        <v>999</v>
-      </c>
-      <c r="D203" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E203" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F203" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G203" t="s">
-        <v>999</v>
+      <c r="G203" s="6" t="s">
+        <v>996</v>
       </c>
       <c r="H203" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" ht="27.6">
       <c r="A204" t="s">
         <v>992</v>
       </c>
-      <c r="B204" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C204" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D204" t="s">
-        <v>1005</v>
-      </c>
-      <c r="E204" t="s">
-        <v>1006</v>
-      </c>
-      <c r="F204" t="s">
-        <v>1007</v>
-      </c>
-      <c r="G204" t="s">
-        <v>1004</v>
+      <c r="B204" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>997</v>
       </c>
       <c r="H204" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" ht="27.6">
       <c r="A205" t="s">
         <v>992</v>
       </c>
-      <c r="B205" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C205" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D205" t="s">
-        <v>1010</v>
-      </c>
-      <c r="E205" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F205" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G205" t="s">
-        <v>1009</v>
+      <c r="B205" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>997</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="E205" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G205" s="6" t="s">
+        <v>998</v>
       </c>
       <c r="H205" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" ht="27.6">
       <c r="A206" t="s">
         <v>992</v>
       </c>
-      <c r="B206" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C206" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D206" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E206" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F206" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G206" t="s">
-        <v>1014</v>
+      <c r="B206" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>1001</v>
       </c>
       <c r="H206" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" ht="27.6">
       <c r="A207" t="s">
         <v>992</v>
       </c>
-      <c r="B207" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C207" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D207" t="s">
-        <v>1020</v>
-      </c>
-      <c r="E207" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F207" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G207" t="s">
-        <v>1019</v>
+      <c r="B207" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E207" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="G207" s="6" t="s">
+        <v>1003</v>
       </c>
       <c r="H207" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" ht="27.6">
       <c r="A208" t="s">
         <v>992</v>
       </c>
-      <c r="B208" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C208" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D208" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E208" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F208" t="s">
-        <v>1027</v>
-      </c>
-      <c r="G208" t="s">
-        <v>1024</v>
+      <c r="B208" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>1005</v>
       </c>
       <c r="H208" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" ht="27.6">
       <c r="A209" t="s">
         <v>992</v>
       </c>
-      <c r="B209" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C209" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D209" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E209" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F209" t="s">
-        <v>1032</v>
-      </c>
-      <c r="G209" t="s">
-        <v>1029</v>
+      <c r="B209" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G209" s="6" t="s">
+        <v>1005</v>
       </c>
       <c r="H209" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8">
       <c r="A210" t="s">
         <v>992</v>
       </c>
-      <c r="B210" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C210" t="s">
-        <v>1034</v>
-      </c>
-      <c r="D210" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E210" t="s">
-        <v>1036</v>
-      </c>
-      <c r="F210" t="s">
-        <v>1037</v>
-      </c>
-      <c r="G210" t="s">
-        <v>1034</v>
+      <c r="B210" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>690</v>
       </c>
       <c r="H210" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8">
       <c r="A211" t="s">
         <v>992</v>
       </c>
-      <c r="B211" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C211" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D211" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E211" t="s">
-        <v>1041</v>
-      </c>
-      <c r="F211" t="s">
-        <v>1042</v>
-      </c>
-      <c r="G211" t="s">
-        <v>1039</v>
+      <c r="B211" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E211" s="5" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G211" s="6" t="s">
+        <v>1011</v>
       </c>
       <c r="H211" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" ht="27.6">
       <c r="A212" t="s">
         <v>992</v>
       </c>
-      <c r="B212" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C212" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D212" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E212" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F212" t="s">
-        <v>1047</v>
-      </c>
-      <c r="G212" t="s">
-        <v>1044</v>
+      <c r="B212" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>1017</v>
       </c>
       <c r="H212" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" ht="27.6">
       <c r="A213" t="s">
         <v>992</v>
       </c>
-      <c r="B213" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C213" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D213" t="s">
-        <v>1050</v>
-      </c>
-      <c r="E213" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F213" t="s">
-        <v>1052</v>
-      </c>
-      <c r="G213" t="s">
-        <v>1049</v>
+      <c r="B213" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D213" s="5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E213" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G213" s="6" t="s">
+        <v>1022</v>
       </c>
       <c r="H213" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8">
       <c r="A214" t="s">
         <v>992</v>
       </c>
-      <c r="B214" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C214" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D214" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E214" t="s">
-        <v>1056</v>
-      </c>
-      <c r="F214" t="s">
-        <v>1057</v>
-      </c>
-      <c r="G214" t="s">
-        <v>1054</v>
+      <c r="B214" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>1027</v>
       </c>
       <c r="H214" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" ht="27.6">
       <c r="A215" t="s">
         <v>992</v>
       </c>
-      <c r="B215" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C215" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D215" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E215" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F215" t="s">
-        <v>1062</v>
-      </c>
-      <c r="G215" t="s">
-        <v>1059</v>
+      <c r="B215" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D215" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E215" s="5" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G215" s="6" t="s">
+        <v>1031</v>
       </c>
       <c r="H215" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" ht="27.6">
       <c r="A216" t="s">
         <v>992</v>
       </c>
-      <c r="B216" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C216" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D216" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E216" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F216" t="s">
-        <v>1067</v>
-      </c>
-      <c r="G216" t="s">
-        <v>1064</v>
+      <c r="B216" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>1034</v>
       </c>
       <c r="H216" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" ht="27.6">
       <c r="A217" t="s">
         <v>992</v>
       </c>
-      <c r="B217" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C217" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D217" t="s">
-        <v>1070</v>
-      </c>
-      <c r="E217" t="s">
-        <v>1071</v>
-      </c>
-      <c r="F217" t="s">
-        <v>1072</v>
-      </c>
-      <c r="G217" t="s">
-        <v>1069</v>
+      <c r="B217" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D217" s="5" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E217" s="5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G217" s="6" t="s">
+        <v>1040</v>
       </c>
       <c r="H217" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" ht="27.6">
       <c r="A218" t="s">
         <v>992</v>
       </c>
-      <c r="B218" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C218" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D218" t="s">
-        <v>1075</v>
-      </c>
-      <c r="E218" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F218" t="s">
-        <v>1077</v>
-      </c>
-      <c r="G218" t="s">
-        <v>1074</v>
+      <c r="B218" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>1019</v>
       </c>
       <c r="H218" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" ht="27.6">
       <c r="A219" t="s">
         <v>992</v>
       </c>
-      <c r="B219" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C219" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D219" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E219" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F219" t="s">
-        <v>1082</v>
-      </c>
-      <c r="G219" t="s">
-        <v>1079</v>
+      <c r="B219" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D219" s="5" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E219" s="5" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F219" s="5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G219" s="6" t="s">
+        <v>1039</v>
       </c>
       <c r="H219" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8">
       <c r="A220" t="s">
         <v>992</v>
       </c>
-      <c r="B220" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C220" t="s">
-        <v>1084</v>
-      </c>
-      <c r="D220" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E220" t="s">
-        <v>1086</v>
-      </c>
-      <c r="F220" t="s">
-        <v>1087</v>
-      </c>
-      <c r="G220" t="s">
-        <v>1084</v>
+      <c r="B220" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>1045</v>
       </c>
       <c r="H220" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8">
       <c r="A221" t="s">
         <v>992</v>
       </c>
-      <c r="B221" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C221" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D221" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E221" t="s">
-        <v>1091</v>
-      </c>
-      <c r="F221" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G221" t="s">
-        <v>1089</v>
+      <c r="B221" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F221" s="5" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G221" s="6" t="s">
+        <v>1051</v>
       </c>
       <c r="H221" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" ht="27.6">
       <c r="A222" t="s">
         <v>992</v>
       </c>
-      <c r="B222" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C222" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D222" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E222" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F222" t="s">
-        <v>1096</v>
-      </c>
-      <c r="G222" t="s">
-        <v>1094</v>
+      <c r="B222" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>1056</v>
       </c>
       <c r="H222" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" ht="27.6">
       <c r="A223" t="s">
         <v>992</v>
       </c>
-      <c r="B223" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C223" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D223" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E223" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F223" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G223" t="s">
-        <v>1098</v>
+      <c r="B223" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D223" s="5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E223" s="5" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G223" s="6" t="s">
+        <v>1058</v>
       </c>
       <c r="H223" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8">
       <c r="A224" t="s">
         <v>992</v>
       </c>
-      <c r="B224" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C224" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D224" t="s">
-        <v>1104</v>
-      </c>
-      <c r="E224" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F224" t="s">
-        <v>1106</v>
-      </c>
-      <c r="G224" t="s">
-        <v>1103</v>
+      <c r="B224" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>1063</v>
       </c>
       <c r="H224" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" ht="27.6">
       <c r="A225" t="s">
         <v>992</v>
       </c>
-      <c r="B225" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C225" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D225" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E225" t="s">
-        <v>1110</v>
-      </c>
-      <c r="F225" t="s">
-        <v>1111</v>
-      </c>
-      <c r="G225" t="s">
-        <v>1108</v>
+      <c r="B225" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D225" s="5" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E225" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G225" s="6" t="s">
+        <v>1068</v>
       </c>
       <c r="H225" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" ht="27.6">
       <c r="A226" t="s">
         <v>992</v>
       </c>
-      <c r="B226" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C226" t="s">
-        <v>1113</v>
-      </c>
-      <c r="D226" t="s">
-        <v>1114</v>
-      </c>
-      <c r="E226" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F226" t="s">
-        <v>1116</v>
-      </c>
-      <c r="G226" t="s">
-        <v>1113</v>
+      <c r="B226" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>1074</v>
       </c>
       <c r="H226" t="s">
         <v>40</v>
       </c>
     </row>
+    <row r="227" spans="1:8" ht="27.6">
+      <c r="A227" t="s">
+        <v>992</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E227" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G227" s="6" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="27.6">
+      <c r="A228" t="s">
+        <v>992</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229" t="s">
+        <v>992</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D229" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E229" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F229" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G229" s="6" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230" t="s">
+        <v>992</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="27.6">
+      <c r="A231" t="s">
+        <v>992</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G231" s="6" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="27.6">
+      <c r="A232" t="s">
+        <v>992</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="27.6">
+      <c r="A233" t="s">
+        <v>992</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D233" s="5" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E233" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F233" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G233" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" t="s">
+        <v>992</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235" t="s">
+        <v>992</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D235" s="5" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E235" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F235" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G235" s="6" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236" t="s">
+        <v>992</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" ht="27.6">
+      <c r="A237" t="s">
+        <v>992</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D237" s="5" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E237" s="5" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G237" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" ht="27.6">
+      <c r="A238" t="s">
+        <v>992</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="27.6">
+      <c r="A239" t="s">
+        <v>992</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D239" s="5" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E239" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G239" s="6" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" t="s">
+        <v>992</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" t="s">
+        <v>992</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D241" s="5" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E241" s="5" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G241" s="6" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" t="s">
+        <v>992</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="27.6">
+      <c r="A243" t="s">
+        <v>992</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D243" s="5" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E243" s="5" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F243" s="5" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G243" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" t="s">
+        <v>992</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" t="s">
+        <v>992</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D245" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E245" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G245" s="6" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" ht="27.6">
+      <c r="A246" t="s">
+        <v>992</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" t="s">
+        <v>992</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E247" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="G247" s="6" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" t="s">
+        <v>992</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" t="s">
+        <v>992</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D249" s="5" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E249" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G249" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" ht="27.6">
+      <c r="A250" t="s">
+        <v>992</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" ht="27.6">
+      <c r="A251" t="s">
+        <v>992</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E251" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G251" s="6" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" ht="27.6">
+      <c r="A252" t="s">
+        <v>992</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" t="s">
+        <v>992</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D253" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E253" s="5" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G253" s="6" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" t="s">
+        <v>992</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" t="s">
+        <v>992</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D255" s="5" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E255" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F255" s="5" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G255" s="6" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" ht="27.6">
+      <c r="A256" t="s">
+        <v>992</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" t="s">
+        <v>992</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D257" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E257" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F257" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G257" s="6" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" ht="27.6">
+      <c r="A258" t="s">
+        <v>992</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" t="s">
+        <v>992</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D259" s="5" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E259" s="5" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F259" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G259" s="6" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" ht="27.6">
+      <c r="A260" t="s">
+        <v>992</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" t="s">
+        <v>992</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D261" s="5" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E261" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F261" s="5" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G261" s="6" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" t="s">
+        <v>992</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" ht="27.6">
+      <c r="A263" t="s">
+        <v>992</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D263" s="5" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E263" s="5" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F263" s="5" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G263" s="6" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" t="s">
+        <v>992</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" t="s">
+        <v>992</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D265" s="5" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E265" s="5" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F265" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G265" s="6" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" t="s">
+        <v>992</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F266" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G266" s="3" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" t="s">
+        <v>992</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D267" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E267" s="5" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F267" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G267" s="6" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" ht="27.6">
+      <c r="A268" t="s">
+        <v>992</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" ht="27.6">
+      <c r="A269" t="s">
+        <v>992</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D269" s="5" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E269" s="5" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F269" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G269" s="6" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" ht="27.6">
+      <c r="A270" t="s">
+        <v>992</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F270" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" t="s">
+        <v>992</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D271" s="5" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E271" s="5" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F271" s="5" t="s">
+        <v>1271</v>
+      </c>
+      <c r="G271" s="6" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" t="s">
+        <v>992</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F272" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" ht="27.6">
+      <c r="A273" t="s">
+        <v>992</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D273" s="5" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E273" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F273" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G273" s="6" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" t="s">
+        <v>992</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F274" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" ht="27.6">
+      <c r="A275" t="s">
+        <v>992</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D275" s="5" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E275" s="5" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F275" s="5" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G275" s="6" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" t="s">
+        <v>992</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F276" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="27.6">
+      <c r="A277" t="s">
+        <v>992</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D277" s="5" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E277" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F277" s="5" t="s">
+        <v>1293</v>
+      </c>
+      <c r="G277" s="6" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" t="s">
+        <v>992</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F278" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" ht="27.6">
+      <c r="A279" t="s">
+        <v>992</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D279" s="5" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E279" s="5" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F279" s="5" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G279" s="6" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" t="s">
+        <v>992</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F280" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" t="s">
+        <v>992</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D281" s="5" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E281" s="5" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F281" s="5" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G281" s="6" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" t="s">
+        <v>992</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F282" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" t="s">
+        <v>992</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D283" s="5" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E283" s="5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F283" s="5" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G283" s="6" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" t="s">
+        <v>992</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F284" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" t="s">
+        <v>992</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D285" s="5" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E285" s="5" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F285" s="5" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G285" s="6" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" t="s">
+        <v>992</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F286" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G286" s="3" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" t="s">
+        <v>992</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D287" s="5" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E287" s="5" t="s">
+        <v>1341</v>
+      </c>
+      <c r="F287" s="5" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G287" s="6" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" t="s">
+        <v>992</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F288" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" ht="27.6">
+      <c r="A289" t="s">
+        <v>992</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D289" s="5" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E289" s="5" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F289" s="5" t="s">
+        <v>1351</v>
+      </c>
+      <c r="G289" s="6" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" ht="27.6">
+      <c r="A290" t="s">
+        <v>992</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F290" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="G290" s="3" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" ht="27.6">
+      <c r="A291" t="s">
+        <v>992</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D291" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E291" s="5" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F291" s="5" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G291" s="6" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" t="s">
+        <v>992</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F292" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="27.6">
+      <c r="A293" t="s">
+        <v>992</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D293" s="5" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E293" s="5" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F293" s="5" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G293" s="6" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" ht="27.6">
+      <c r="A294" t="s">
+        <v>992</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E294" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F294" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G294" s="3" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" t="s">
+        <v>992</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D295" s="5" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E295" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F295" s="5" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G295" s="6" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" t="s">
+        <v>992</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F296" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G296" s="3" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" t="s">
+        <v>992</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D297" s="5" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E297" s="5" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F297" s="5" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G297" s="6" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" t="s">
+        <v>992</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F298" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G298" s="3" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" ht="27.6">
+      <c r="A299" t="s">
+        <v>992</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D299" s="5" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E299" s="5" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F299" s="5" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G299" s="6" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" t="s">
+        <v>992</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E300" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F300" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G300" s="3" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" ht="27.6">
+      <c r="A301" t="s">
+        <v>992</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D301" s="5" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E301" s="5" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F301" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="G301" s="6" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" t="s">
+        <v>992</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E302" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F302" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G302" s="3" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" t="s">
+        <v>992</v>
+      </c>
+      <c r="B303" s="4" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D303" s="5" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E303" s="5" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F303" s="5" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G303" s="6" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" ht="27.6">
+      <c r="A304" t="s">
+        <v>992</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E304" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="F304" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="G304" s="3" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" t="s">
+        <v>992</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D305" s="5" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E305" s="5" t="s">
+        <v>1419</v>
+      </c>
+      <c r="F305" s="5" t="s">
+        <v>1420</v>
+      </c>
+      <c r="G305" s="6" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" ht="27.6">
+      <c r="A306" t="s">
+        <v>992</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E306" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F306" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G306" s="3" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" t="s">
+        <v>992</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D307" s="5" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E307" s="5" t="s">
+        <v>1429</v>
+      </c>
+      <c r="F307" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G307" s="6" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" ht="27.6">
+      <c r="A308" t="s">
+        <v>992</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="E308" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="F308" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="G308" s="3" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" ht="27.6">
+      <c r="A309" t="s">
+        <v>992</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D309" s="5" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E309" s="5" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F309" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G309" s="6" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" t="s">
+        <v>992</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E310" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F310" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G310" s="3" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" t="s">
+        <v>992</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D311" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E311" s="5" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F311" s="5" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G311" s="6" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" t="s">
+        <v>992</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F312" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G312" s="3" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" t="s">
+        <v>992</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D313" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E313" s="5" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F313" s="5" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G313" s="6" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" t="s">
+        <v>992</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E314" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F314" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G314" s="3" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" t="s">
+        <v>992</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D315" s="5" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E315" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F315" s="5" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G315" s="6" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" t="s">
+        <v>992</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F316" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G316" s="3" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" t="s">
+        <v>992</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D317" s="5" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E317" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F317" s="5" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G317" s="6" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" ht="27.6">
+      <c r="A318" t="s">
+        <v>992</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F318" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G318" s="3" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" ht="27.6">
+      <c r="A319" t="s">
+        <v>992</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D319" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E319" s="5" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F319" s="5" t="s">
+        <v>994</v>
+      </c>
+      <c r="G319" s="6" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" ht="27.6">
+      <c r="A320" t="s">
+        <v>992</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F320" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="G320" s="3" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" t="s">
+        <v>992</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D321" s="5" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E321" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F321" s="5" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G321" s="6" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" t="s">
+        <v>992</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F322" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G322" s="3" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" t="s">
+        <v>992</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D323" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E323" s="5" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F323" s="5" t="s">
+        <v>1480</v>
+      </c>
+      <c r="G323" s="6" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" t="s">
+        <v>992</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E324" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F324" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G324" s="3" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7">
+      <c r="A325" t="s">
+        <v>992</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D325" s="5" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E325" s="5" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F325" s="5" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G325" s="6" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
+      <c r="A326" t="s">
+        <v>992</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F326" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G326" s="3" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327" t="s">
+        <v>992</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D327" s="5" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E327" s="5" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F327" s="5" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G327" s="6" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" ht="27.6">
+      <c r="A328" t="s">
+        <v>992</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F328" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="G328" s="3" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329" t="s">
+        <v>992</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D329" s="5" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E329" s="5" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F329" s="5" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G329" s="6" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="A330" t="s">
+        <v>992</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E330" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F330" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G330" s="3" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="A331" t="s">
+        <v>992</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C331" s="5" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D331" s="5" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E331" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F331" s="5" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G331" s="6" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7">
+      <c r="A333" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7">
+      <c r="A334" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7">
+      <c r="A335" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" t="s">
+        <v>992</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/savollar.xlsx
+++ b/savollar.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDA55D1-A3D5-42AF-8A43-33AD0DAFF6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E88FA8-8406-4669-AFD9-7E8BCC9226EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2549" uniqueCount="1514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="992">
   <si>
     <t>category</t>
   </si>
@@ -2996,1572 +2996,6 @@
   </si>
   <si>
     <t>Faqat bir martalik natija</t>
-  </si>
-  <si>
-    <t>Ustozlar yo'riqnomasi</t>
-  </si>
-  <si>
-    <t>Faqat tanaffusda</t>
-  </si>
-  <si>
-    <t>Faqat dars oxirida</t>
-  </si>
-  <si>
-    <t>Vazifa umuman bajarilmagan holatda qaysi ball qo'yiladi?</t>
-  </si>
-  <si>
-    <t>1-20</t>
-  </si>
-  <si>
-    <t>21-59</t>
-  </si>
-  <si>
-    <t>60-70</t>
-  </si>
-  <si>
-    <t>Vazifa 90% dan ortiq bajarilmagan, faqat 5-10% qismi bor. Qaysi ball oralig'i mos?</t>
-  </si>
-  <si>
-    <t>Minimal talablarga javob bermagan, jiddiy xatolar ko'p va mavzuni faqat 10% tushungan. Qaysi ball oralig'i qo'yiladi?</t>
-  </si>
-  <si>
-    <t>71-85</t>
-  </si>
-  <si>
-    <t>Minimal talablarni qondiradi, lekin daraja past. Kamida 50% tushungan, jiddiy xatolar mavjud. Qancha ball oralig'i qo'yiladi?</t>
-  </si>
-  <si>
-    <t>86-94</t>
-  </si>
-  <si>
-    <t>Vazifa asosiy talablar asosida to'g'ri bajarilgan, xatolar kam. Qaysi ball oralig'i mos?</t>
-  </si>
-  <si>
-    <t>95-100</t>
-  </si>
-  <si>
-    <t>Mavzuni yuqori darajada tushungan, ijodiy va tahliliy yondashgan, mutlaqo xatosiz bajargan. Qaysi ball mos?</t>
-  </si>
-  <si>
-    <t>O'quvchi ustoz talab qilmagan qo'shimcha bilimlarni mustaqil o'rganib qo'llagan. Qaysi ball oralig'i mos?</t>
-  </si>
-  <si>
-    <t>O'quvchi loyihani ingliz tilida tasvirlab bera oladigan darajada bajargan. Qaysi ball oralig'i mos?</t>
-  </si>
-  <si>
-    <t>Ko'chirgan va ko'chirtirgan o'quvchilarga qanday ball qo'yiladi?</t>
-  </si>
-  <si>
-    <t>Ko'chirish holati aniqlansa, 0 ball qo'yish uchun nima kerak?</t>
-  </si>
-  <si>
-    <t>Dalillar bilan asoslash</t>
-  </si>
-  <si>
-    <t>Faqat gumon qilish</t>
-  </si>
-  <si>
-    <t>Ota-onadan so'rash</t>
-  </si>
-  <si>
-    <t>Guruh ovozi</t>
-  </si>
-  <si>
-    <t>Uy vazifasi o'quvchi yuklaganidan keyin maksimal qancha vaqtda tekshirilishi kerak?</t>
-  </si>
-  <si>
-    <t>6 soat</t>
-  </si>
-  <si>
-    <t>12 soat</t>
-  </si>
-  <si>
-    <t>24 soat</t>
-  </si>
-  <si>
-    <t>48 soat</t>
-  </si>
-  <si>
-    <t>12 soatdan keyin tekshirilgan vazifa tizimda qanday hisoblanadi?</t>
-  </si>
-  <si>
-    <t>O'z vaqtida</t>
-  </si>
-  <si>
-    <t>Kech tekshirilgan vazifa</t>
-  </si>
-  <si>
-    <t>Bekor qilingan vazifa</t>
-  </si>
-  <si>
-    <t>Qo'shimcha vazifa</t>
-  </si>
-  <si>
-    <t>Kech topshirilgan vazifaga qanday qoida qo'llanadi?</t>
-  </si>
-  <si>
-    <t>10% kam ball</t>
-  </si>
-  <si>
-    <t>20% kam ball</t>
-  </si>
-  <si>
-    <t>30% kam ball</t>
-  </si>
-  <si>
-    <t>Ball o'zgarmaydi</t>
-  </si>
-  <si>
-    <t>80 ballga loyiq vazifa kech topshirilsa, yakuniy ball nechchi bo'ladi?</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>90 ballga loyiq vazifa kech topshirilsa, yakuniy ball nechchi bo'ladi?</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>1 haftada 3 ta yo'nalish bo'lsa, uy vazifasini bajarish muddati qancha?</t>
-  </si>
-  <si>
-    <t>36 soat</t>
-  </si>
-  <si>
-    <t>7 kun</t>
-  </si>
-  <si>
-    <t>10 kun</t>
-  </si>
-  <si>
-    <t>2 haftada 2 ta yo'nalish bo'lsa, vazifa topshirish muddati qancha?</t>
-  </si>
-  <si>
-    <t>1 haftada 1 ta yo'nalish bo'lsa, vazifa topshirish muddati qancha?</t>
-  </si>
-  <si>
-    <t>Har bir darsda uy vazifasi berilishi shartmi?</t>
-  </si>
-  <si>
-    <t>Ha</t>
-  </si>
-  <si>
-    <t>Yo'q</t>
-  </si>
-  <si>
-    <t>Faqat nazariyada</t>
-  </si>
-  <si>
-    <t>Faqat robototexnikada</t>
-  </si>
-  <si>
-    <t>Qaysi kunda uy vazifasi berilmaydi?</t>
-  </si>
-  <si>
-    <t>Oddiy dars kuni</t>
-  </si>
-  <si>
-    <t>Imtihon kuni</t>
-  </si>
-  <si>
-    <t>Takrorlash kuni</t>
-  </si>
-  <si>
-    <t>Amaliyot kuni</t>
-  </si>
-  <si>
-    <t>Uy vazifasi muddati tugashidan qancha vaqt oldin guruhda ogohlantirish tavsiya etiladi?</t>
-  </si>
-  <si>
-    <t>2 soat</t>
-  </si>
-  <si>
-    <t>5 soat</t>
-  </si>
-  <si>
-    <t>15 o'quvchidan 13 tasi topshirgan bo'lsa, qolgan 2 tasi bilan nima qilish kerak?</t>
-  </si>
-  <si>
-    <t>Shaxsan bog'lanish</t>
-  </si>
-  <si>
-    <t>E'tibor bermaslik</t>
-  </si>
-  <si>
-    <t>Avtomatik 0 qo'yish</t>
-  </si>
-  <si>
-    <t>Guruhdan chiqarish</t>
-  </si>
-  <si>
-    <t>ERP bahosidan so'ng o'quvchiga nima qoldirilishi kerak?</t>
-  </si>
-  <si>
-    <t>Batafsil yozma fidbek</t>
-  </si>
-  <si>
-    <t>Faqat emoji</t>
-  </si>
-  <si>
-    <t>Faqat ball</t>
-  </si>
-  <si>
-    <t>Hech narsa</t>
-  </si>
-  <si>
-    <t>Guruhda hech kim 70 balldan yuqori olmasa, keyingi dars boshiga nima tayyorlanadi?</t>
-  </si>
-  <si>
-    <t>3-5 ta savol</t>
-  </si>
-  <si>
-    <t>Yangi imtihon</t>
-  </si>
-  <si>
-    <t>Jazo ro'yxati</t>
-  </si>
-  <si>
-    <t>Sport mashqi</t>
-  </si>
-  <si>
-    <t>Materiallar va uy vazifasi qachon taqdimotga biriktirilgan bo'lishi kerak?</t>
-  </si>
-  <si>
-    <t>Darsdan keyin</t>
-  </si>
-  <si>
-    <t>Dars boshlanishidan avval</t>
-  </si>
-  <si>
-    <t>Hafta oxirida</t>
-  </si>
-  <si>
-    <t>O'quvchi so'raganda</t>
-  </si>
-  <si>
-    <t>Yangi guruh ochilishidan oldin Telegram guruh kamida qachon tekshiriladi?</t>
-  </si>
-  <si>
-    <t>Dars kuni</t>
-  </si>
-  <si>
-    <t>1 kun oldin</t>
-  </si>
-  <si>
-    <t>2 kun oldin</t>
-  </si>
-  <si>
-    <t>1 hafta keyin</t>
-  </si>
-  <si>
-    <t>Telegram guruhda yangi a'zolar uchun qaysi sozlama yoqilishi kerak?</t>
-  </si>
-  <si>
-    <t>Oldingi xabarlarni ko'ra oladi</t>
-  </si>
-  <si>
-    <t>Faqat admin yozadi</t>
-  </si>
-  <si>
-    <t>Faqat rasm yuboradi</t>
-  </si>
-  <si>
-    <t>Xabarlar o'chadi</t>
-  </si>
-  <si>
-    <t>Guruh ma'lumotlarini kimlar o'zgartira olmasligi kerak?</t>
-  </si>
-  <si>
-    <t>Ota-onalar va o'quvchilar</t>
-  </si>
-  <si>
-    <t>Faqat adminlar</t>
-  </si>
-  <si>
-    <t>Faqat o'qituvchi</t>
-  </si>
-  <si>
-    <t>Hech kim</t>
-  </si>
-  <si>
-    <t>Telegram reaksiyalarida nimalar cheklanishi kerak?</t>
-  </si>
-  <si>
-    <t>Ortiqcha va behayo emojilar</t>
-  </si>
-  <si>
-    <t>Oddiy like</t>
-  </si>
-  <si>
-    <t>Matnli xabarlar</t>
-  </si>
-  <si>
-    <t>Dars materiallari</t>
-  </si>
-  <si>
-    <t>O'quvchilar ro'yxatida avvalo nimalar tekshiriladi?</t>
-  </si>
-  <si>
-    <t>Shartnoma, to'lov va guruhga qo'shilgani</t>
-  </si>
-  <si>
-    <t>Telefon modeli</t>
-  </si>
-  <si>
-    <t>Uy manzili</t>
-  </si>
-  <si>
-    <t>Baholari</t>
-  </si>
-  <si>
-    <t>Guruhga qo'shilmagan o'quvchilar bilan nima qilish kerak?</t>
-  </si>
-  <si>
-    <t>Shaxsan aloqaga chiqib qo'shilishini ta'minlash</t>
-  </si>
-  <si>
-    <t>Kutib turish</t>
-  </si>
-  <si>
-    <t>Bahosini pasaytirish</t>
-  </si>
-  <si>
-    <t>Guruhni o'chirish</t>
-  </si>
-  <si>
-    <t>Robototexnika dars jadvali nimaga to'g'ri kelmasligi kerak?</t>
-  </si>
-  <si>
-    <t>Boshqa guruhlarning LEGO mashg'ulot jadvaliga</t>
-  </si>
-  <si>
-    <t>Tanaffusga</t>
-  </si>
-  <si>
-    <t>ERPga</t>
-  </si>
-  <si>
-    <t>Uy vazifasiga</t>
-  </si>
-  <si>
-    <t>LEGO jadval moslashuvi deadline qachon?</t>
-  </si>
-  <si>
-    <t>Darsdan 2 kun oldin</t>
-  </si>
-  <si>
-    <t>Darsdan 1 oy oldin</t>
-  </si>
-  <si>
-    <t>Tanishtiruv video qachon yuboriladi?</t>
-  </si>
-  <si>
-    <t>Darsdan 1 kun oldin</t>
-  </si>
-  <si>
-    <t>Faqat ota-onaga</t>
-  </si>
-  <si>
-    <t>Tanishtiruv video davomiyligi qancha tavsiya etiladi?</t>
-  </si>
-  <si>
-    <t>30 soniya</t>
-  </si>
-  <si>
-    <t>1 daqiqa</t>
-  </si>
-  <si>
-    <t>3 daqiqa</t>
-  </si>
-  <si>
-    <t>10 daqiqa</t>
-  </si>
-  <si>
-    <t>Tanishtiruv videoda qaysi ma'lumot bo'lishi kerak?</t>
-  </si>
-  <si>
-    <t>Ism, mashg'ulot vaqti, jadval, xona</t>
-  </si>
-  <si>
-    <t>Oylik maosh</t>
-  </si>
-  <si>
-    <t>Shaxsiy sirlar</t>
-  </si>
-  <si>
-    <t>Rahbarlar haqida fikr</t>
-  </si>
-  <si>
-    <t>Videoni qayerdan boshlab olish tavsiya etiladi?</t>
-  </si>
-  <si>
-    <t>Reception yoki filial administratsiyasi yonidan</t>
-  </si>
-  <si>
-    <t>Uyda</t>
-  </si>
-  <si>
-    <t>Ko'chada</t>
-  </si>
-  <si>
-    <t>Avtobusda</t>
-  </si>
-  <si>
-    <t>Dars boshlanishidan necha daqiqa oldin sinfxonada bo'lish majburiy?</t>
-  </si>
-  <si>
-    <t>5 daqiqa</t>
-  </si>
-  <si>
-    <t>20 daqiqa</t>
-  </si>
-  <si>
-    <t>30 daqiqa</t>
-  </si>
-  <si>
-    <t>Markazga kirgach beyjik qanday bo'lishi kerak?</t>
-  </si>
-  <si>
-    <t>Ko'rinadigan qilib taqilgan</t>
-  </si>
-  <si>
-    <t>Sumkada</t>
-  </si>
-  <si>
-    <t>Cho'ntakda</t>
-  </si>
-  <si>
-    <t>Xona harorati qaysi oralig'iga olib kelinadi?</t>
-  </si>
-  <si>
-    <t>15-18°C</t>
-  </si>
-  <si>
-    <t>19-22°C</t>
-  </si>
-  <si>
-    <t>23-27°C</t>
-  </si>
-  <si>
-    <t>28-30°C</t>
-  </si>
-  <si>
-    <t>Xona qancha vaqtda shamollatiladi?</t>
-  </si>
-  <si>
-    <t>Har 10 daqiqada</t>
-  </si>
-  <si>
-    <t>Har 20 daqiqada</t>
-  </si>
-  <si>
-    <t>Har soatda</t>
-  </si>
-  <si>
-    <t>Darsdan oldin kompyuter/proyektor/elektron doska qanday holatda bo'lishi kerak?</t>
-  </si>
-  <si>
-    <t>Yoqilgan va tayyor</t>
-  </si>
-  <si>
-    <t>O'chiq</t>
-  </si>
-  <si>
-    <t>Ulanmagan</t>
-  </si>
-  <si>
-    <t>Faqat dars o'rtasida</t>
-  </si>
-  <si>
-    <t>Macbook bo'lsa, hub va adapterlar qachon ulanadi?</t>
-  </si>
-  <si>
-    <t>Oldindan</t>
-  </si>
-  <si>
-    <t>Dars tugagach</t>
-  </si>
-  <si>
-    <t>Kerak emas</t>
-  </si>
-  <si>
-    <t>Dars vaqtida slayd tayyorlash nimani anglatadi?</t>
-  </si>
-  <si>
-    <t>O'quvchilar vaqtini olish</t>
-  </si>
-  <si>
-    <t>Professional tayyorgarlik</t>
-  </si>
-  <si>
-    <t>Warm-up</t>
-  </si>
-  <si>
-    <t>CCQ</t>
-  </si>
-  <si>
-    <t>Davomat dars boshlanganidan keyin necha daqiqa ichida qilinadi?</t>
-  </si>
-  <si>
-    <t>15 daqiqa</t>
-  </si>
-  <si>
-    <t>Yo'q o'quvchini ERPda 'bor' deb belgilash mumkinmi?</t>
-  </si>
-  <si>
-    <t>Faqat ota-onasi aytsa</t>
-  </si>
-  <si>
-    <t>ERPda ismi chiqmagan o'quvchi nima qilinadi?</t>
-  </si>
-  <si>
-    <t>Administratsiyaga yo'naltiriladi</t>
-  </si>
-  <si>
-    <t>Darsga kiritiladi</t>
-  </si>
-  <si>
-    <t>Bor deb belgilanadi</t>
-  </si>
-  <si>
-    <t>Uyga jo'natiladi</t>
-  </si>
-  <si>
-    <t>Dars vaqtida telefon qanday holatda bo'lishi kerak?</t>
-  </si>
-  <si>
-    <t>Ovozsiz silent</t>
-  </si>
-  <si>
-    <t>Ovozli</t>
-  </si>
-  <si>
-    <t>Musiqa bilan</t>
-  </si>
-  <si>
-    <t>Doim qo'lda</t>
-  </si>
-  <si>
-    <t>Dars boshida avvalgi darsni eslash uchun qancha vaqt savol-javob o'tkaziladi?</t>
-  </si>
-  <si>
-    <t>2 daqiqa</t>
-  </si>
-  <si>
-    <t>O'quvchiga faqat 'vazifangiz a'lo' deyish o'rniga nima so'raladi?</t>
-  </si>
-  <si>
-    <t>Fikrini misol yoki dalillar bilan asoslash</t>
-  </si>
-  <si>
-    <t>Telefon raqami</t>
-  </si>
-  <si>
-    <t>CCQ usuli nima uchun ishlatiladi?</t>
-  </si>
-  <si>
-    <t>Mavzuni tushunganini tekshirish</t>
-  </si>
-  <si>
-    <t>Davomat olish</t>
-  </si>
-  <si>
-    <t>Wi-Fi ulash</t>
-  </si>
-  <si>
-    <t>Musobaqa e'loni</t>
-  </si>
-  <si>
-    <t>'Tushunarlimi?' kabi savol nima sababdan noqulay?</t>
-  </si>
-  <si>
-    <t>Ha/yo'q javobli</t>
-  </si>
-  <si>
-    <t>Juda uzun</t>
-  </si>
-  <si>
-    <t>Faqat inglizcha</t>
-  </si>
-  <si>
-    <t>Rasmiy emas</t>
-  </si>
-  <si>
-    <t>5 bosqichli savol berish sxemasida 1-bosqich nima?</t>
-  </si>
-  <si>
-    <t>Mavzu nomini so'rash</t>
-  </si>
-  <si>
-    <t>Sababini so'rash</t>
-  </si>
-  <si>
-    <t>Yangi misol berish</t>
-  </si>
-  <si>
-    <t>Javobni aytish</t>
-  </si>
-  <si>
-    <t>5 bosqichli savol berish sxemasida 2-bosqich nima?</t>
-  </si>
-  <si>
-    <t>Qanday ishlatilishini so'rash</t>
-  </si>
-  <si>
-    <t>Uy vazifa berish</t>
-  </si>
-  <si>
-    <t>Tanaffus qilish</t>
-  </si>
-  <si>
-    <t>5 bosqichli savol berish sxemasida 3-bosqich nima?</t>
-  </si>
-  <si>
-    <t>Nozik joyidan teskari savol berish</t>
-  </si>
-  <si>
-    <t>Bahoni aytish</t>
-  </si>
-  <si>
-    <t>Slayd yopish</t>
-  </si>
-  <si>
-    <t>5 bosqichli savol berish sxemasida 4-bosqich nima?</t>
-  </si>
-  <si>
-    <t>Mavzu nomi</t>
-  </si>
-  <si>
-    <t>Yangi misol</t>
-  </si>
-  <si>
-    <t>Uy vazifa</t>
-  </si>
-  <si>
-    <t>5 bosqichli savol berish sxemasida 5-bosqich nima?</t>
-  </si>
-  <si>
-    <t>Yangi misol berib yechimini aniqlash</t>
-  </si>
-  <si>
-    <t>Davomat</t>
-  </si>
-  <si>
-    <t>Baholash</t>
-  </si>
-  <si>
-    <t>Telegramga yozish</t>
-  </si>
-  <si>
-    <t>Warm-up faoliyati qancha vaqt davom etishi kerak?</t>
-  </si>
-  <si>
-    <t>2-3 daqiqa</t>
-  </si>
-  <si>
-    <t>Warm-up faoliyatiga qaysi biri mos?</t>
-  </si>
-  <si>
-    <t>Yangi mavzuga oid qiziqarli savol</t>
-  </si>
-  <si>
-    <t>Oylik maosh muhokamasi</t>
-  </si>
-  <si>
-    <t>Darsni tark etish</t>
-  </si>
-  <si>
-    <t>Jazo berish</t>
-  </si>
-  <si>
-    <t>Warm-up uchun amaliy keys nimaga xizmat qiladi?</t>
-  </si>
-  <si>
-    <t>E'tiborni darsga qaratishga</t>
-  </si>
-  <si>
-    <t>Davomatni yashirishga</t>
-  </si>
-  <si>
-    <t>Vaqt o'tkazishga</t>
-  </si>
-  <si>
-    <t>Uy vazifani bekor qilishga</t>
-  </si>
-  <si>
-    <t>Mavzuni boshlashdan avval o'quvchilarda nima shakllantiriladi?</t>
-  </si>
-  <si>
-    <t>Ehtiyoj</t>
-  </si>
-  <si>
-    <t>Qo'rquv</t>
-  </si>
-  <si>
-    <t>Charchoq</t>
-  </si>
-  <si>
-    <t>Jazo hissi</t>
-  </si>
-  <si>
-    <t>Nazariy ma'ruza vaqtida kompyuter qopqoqlari qanday bo'lishi so'raladi?</t>
-  </si>
-  <si>
-    <t>Butunlay yopiq</t>
-  </si>
-  <si>
-    <t>Ochiq</t>
-  </si>
-  <si>
-    <t>Yarim ochiq</t>
-  </si>
-  <si>
-    <t>Farqi yo'q</t>
-  </si>
-  <si>
-    <t>Yangi mavzu nechta asosiy qismda tushuntiriladi?</t>
-  </si>
-  <si>
-    <t>2 ta</t>
-  </si>
-  <si>
-    <t>3 ta</t>
-  </si>
-  <si>
-    <t>4 ta</t>
-  </si>
-  <si>
-    <t>5 ta</t>
-  </si>
-  <si>
-    <t>Yangi mavzu tushuntirishning 1-qismi nima?</t>
-  </si>
-  <si>
-    <t>Nazariya</t>
-  </si>
-  <si>
-    <t>Live coding</t>
-  </si>
-  <si>
-    <t>Natija tahlili</t>
-  </si>
-  <si>
-    <t>Yangi mavzu tushuntirishning 2-qismi nima?</t>
-  </si>
-  <si>
-    <t>Ekranda namuna ko'rsatish</t>
-  </si>
-  <si>
-    <t>Tanaffus</t>
-  </si>
-  <si>
-    <t>Musobaqa</t>
-  </si>
-  <si>
-    <t>Yangi mavzu tushuntirishning 3-qismi nima?</t>
-  </si>
-  <si>
-    <t>Natija va ko'rinishini tahlil qilish</t>
-  </si>
-  <si>
-    <t>Telegram yozish</t>
-  </si>
-  <si>
-    <t>Beyjik taqish</t>
-  </si>
-  <si>
-    <t>Mavzu bloklarga bo'lingach har bir blokdan so'ng nima o'tkaziladi?</t>
-  </si>
-  <si>
-    <t>Amaliy mashq va kviz</t>
-  </si>
-  <si>
-    <t>Oylik suhbat</t>
-  </si>
-  <si>
-    <t>Guruhlarda sinf ishi paytida ustoz nima qiladi?</t>
-  </si>
-  <si>
-    <t>Xona bo'ylab yurib nazorat qiladi</t>
-  </si>
-  <si>
-    <t>Telefon ishlatadi</t>
-  </si>
-  <si>
-    <t>Xonadan chiqadi</t>
-  </si>
-  <si>
-    <t>Faqat o'tiradi</t>
-  </si>
-  <si>
-    <t>Peer-review usuli nimani bildiradi?</t>
-  </si>
-  <si>
-    <t>O'quvchilar bir-birining ishiga fidbek beradi</t>
-  </si>
-  <si>
-    <t>Faqat ustoz baholaydi</t>
-  </si>
-  <si>
-    <t>Ota-ona baholaydi</t>
-  </si>
-  <si>
-    <t>ERP avtomatik tekshiradi</t>
-  </si>
-  <si>
-    <t>Darsni kimlarning xulosasi orqali yakunlash tavsiya etiladi?</t>
-  </si>
-  <si>
-    <t>3-4 o'quvchi</t>
-  </si>
-  <si>
-    <t>Faqat ustoz</t>
-  </si>
-  <si>
-    <t>Faqat administrator</t>
-  </si>
-  <si>
-    <t>Faqat ota-ona</t>
-  </si>
-  <si>
-    <t>Dars yakuni uchun maksimal qancha vaqt ajratiladi?</t>
-  </si>
-  <si>
-    <t>Dars yakunida mavzu maqsadlari yozilgan slaydga nima qilinadi?</t>
-  </si>
-  <si>
-    <t>Qaytiladi va bajarilgani tasdiqlatiladi</t>
-  </si>
-  <si>
-    <t>O'chiriladi</t>
-  </si>
-  <si>
-    <t>Yashiriladi</t>
-  </si>
-  <si>
-    <t>Uyga yuborilmaydi</t>
-  </si>
-  <si>
-    <t>Uy vazifasi qachon ERP tizimiga yuklanadi?</t>
-  </si>
-  <si>
-    <t>Dars ochiq bo'lgan vaqtda</t>
-  </si>
-  <si>
-    <t>Ertasi kuni</t>
-  </si>
-  <si>
-    <t>Ota-ona so'raganda</t>
-  </si>
-  <si>
-    <t>Uy vazifasi berilganda nimalar maydalab tushuntiriladi?</t>
-  </si>
-  <si>
-    <t>Bajarish tartibi, muhlat, manbalar</t>
-  </si>
-  <si>
-    <t>Rahbarlar ismi</t>
-  </si>
-  <si>
-    <t>Shaxsiy reja</t>
-  </si>
-  <si>
-    <t>Uy vazifasini tushuntirgach o'quvchilardan nima tasdiqlanadi?</t>
-  </si>
-  <si>
-    <t>Vazifa tushunarli bo'lgani</t>
-  </si>
-  <si>
-    <t>Bahosi</t>
-  </si>
-  <si>
-    <t>Markazda qanday rangdagi kiyimlar tavsiya etiladi?</t>
-  </si>
-  <si>
-    <t>Oq-qora, och havorang, och kulrang, qaymoq</t>
-  </si>
-  <si>
-    <t>Neon rang</t>
-  </si>
-  <si>
-    <t>Qizil-yashil naqshli</t>
-  </si>
-  <si>
-    <t>Faqat sport kiyimi</t>
-  </si>
-  <si>
-    <t>Kiyim qanday holatda bo'lishi kerak?</t>
-  </si>
-  <si>
-    <t>Pokiza va dazmollangan</t>
-  </si>
-  <si>
-    <t>Kir va g'ijim</t>
-  </si>
-  <si>
-    <t>Yirtiq</t>
-  </si>
-  <si>
-    <t>Shippak bilan</t>
-  </si>
-  <si>
-    <t>Qaysi kiyim taqiqlanadi?</t>
-  </si>
-  <si>
-    <t>Behayo yozuv va rasmlari bor kiyim</t>
-  </si>
-  <si>
-    <t>Klassik oq ko'ylak</t>
-  </si>
-  <si>
-    <t>Och kulrang shim</t>
-  </si>
-  <si>
-    <t>Dazmollangan kiyim</t>
-  </si>
-  <si>
-    <t>Qaysi kiyim bilan kelish mumkin emas?</t>
-  </si>
-  <si>
-    <t>Shortik</t>
-  </si>
-  <si>
-    <t>Klassik shim</t>
-  </si>
-  <si>
-    <t>Oq ko'ylak</t>
-  </si>
-  <si>
-    <t>Qaymoq rang kiyim</t>
-  </si>
-  <si>
-    <t>Oyoq kiyim qanday bo'lishi kerak?</t>
-  </si>
-  <si>
-    <t>Loy, chang va yirtilmagan</t>
-  </si>
-  <si>
-    <t>Loy va chang</t>
-  </si>
-  <si>
-    <t>Orqasi ezilgan</t>
-  </si>
-  <si>
-    <t>Qaysi oyoq kiyim taqiqlanadi?</t>
-  </si>
-  <si>
-    <t>Trippak/shippak</t>
-  </si>
-  <si>
-    <t>Toza tufli</t>
-  </si>
-  <si>
-    <t>Klassik oyoq kiyim</t>
-  </si>
-  <si>
-    <t>Chang bo'lmagan poyabzal</t>
-  </si>
-  <si>
-    <t>Oyoq kiyimni qanday kiyish taqiqlanadi?</t>
-  </si>
-  <si>
-    <t>Orqasini ezgan holatda</t>
-  </si>
-  <si>
-    <t>To'liq kiyilgan</t>
-  </si>
-  <si>
-    <t>Toza kiyilgan</t>
-  </si>
-  <si>
-    <t>Bog'ichi bog'langan</t>
-  </si>
-  <si>
-    <t>O'quvchilar bilan ko'z orqali muloqot nima uchun kerak?</t>
-  </si>
-  <si>
-    <t>Diqqatini ushlab turish uchun</t>
-  </si>
-  <si>
-    <t>Bahoni yashirish uchun</t>
-  </si>
-  <si>
-    <t>Telefon ishlatish uchun</t>
-  </si>
-  <si>
-    <t>Vaqtni cho'zish uchun</t>
-  </si>
-  <si>
-    <t>Nutqda nimalarga rioya qilish kerak?</t>
-  </si>
-  <si>
-    <t>Diksiya va artikulyatsiya</t>
-  </si>
-  <si>
-    <t>Monoton ohang</t>
-  </si>
-  <si>
-    <t>Juda murakkab iboralar</t>
-  </si>
-  <si>
-    <t>Jim turish</t>
-  </si>
-  <si>
-    <t>Monoton bir xil ohangda gapirish nimaga olib keladi?</t>
-  </si>
-  <si>
-    <t>Dars zerikarli bo'lishiga</t>
-  </si>
-  <si>
-    <t>Dars qiziq bo'lishiga</t>
-  </si>
-  <si>
-    <t>Davomat oshishiga</t>
-  </si>
-  <si>
-    <t>Baholar yaxshilanishiga</t>
-  </si>
-  <si>
-    <t>Darsda tana tili bo'yicha qaysi holat xunuk ko'rinadi?</t>
-  </si>
-  <si>
-    <t>Qo'lni cho'ntakka solish</t>
-  </si>
-  <si>
-    <t>Xona bo'ylab harakatlanish</t>
-  </si>
-  <si>
-    <t>Ko'z bilan muloqot</t>
-  </si>
-  <si>
-    <t>Sergak turish</t>
-  </si>
-  <si>
-    <t>8-15 yoshli bolalar bilan qanday til ishlatiladi?</t>
-  </si>
-  <si>
-    <t>Oson tushuniladigan til</t>
-  </si>
-  <si>
-    <t>Juda murakkab texnik til</t>
-  </si>
-  <si>
-    <t>Faqat rasmiy til</t>
-  </si>
-  <si>
-    <t>Darsda uxlab qolgan yoki o'yin o'ynayotgan bola bo'lsa, birinchi yondashuv nima?</t>
-  </si>
-  <si>
-    <t>Toza havo kiritish va darsga qaytarish</t>
-  </si>
-  <si>
-    <t>Jismoniy jazo</t>
-  </si>
-  <si>
-    <t>Guruh oldida kamsitish</t>
-  </si>
-  <si>
-    <t>Uyiga jo'natish</t>
-  </si>
-  <si>
-    <t>Chalg'igan bolani qo'pol urishmasdan qanday qaytarish tavsiya etiladi?</t>
-  </si>
-  <si>
-    <t>Ismi bilan savol berish</t>
-  </si>
-  <si>
-    <t>Baqirish</t>
-  </si>
-  <si>
-    <t>Sinfdan chiqarish</t>
-  </si>
-  <si>
-    <t>O'quvchilarga nisbatan jismoniy yoki ruhiy jazo qo'llash mumkinmi?</t>
-  </si>
-  <si>
-    <t>Ba'zida</t>
-  </si>
-  <si>
-    <t>Faqat kichiklarga</t>
-  </si>
-  <si>
-    <t>Atjimaniya qildirish qanday holat?</t>
-  </si>
-  <si>
-    <t>Qat'iyan taqiqlangan</t>
-  </si>
-  <si>
-    <t>Tavsiya etilgan</t>
-  </si>
-  <si>
-    <t>Sport darsi</t>
-  </si>
-  <si>
-    <t>Surunkali vazifa qilmaydigan o'quvchi bilan qanday suhbatlashiladi?</t>
-  </si>
-  <si>
-    <t>Ketma-ket 'nega' savoli bilan</t>
-  </si>
-  <si>
-    <t>Darhol 0 qo'yib</t>
-  </si>
-  <si>
-    <t>Guruhdan chiqarib</t>
-  </si>
-  <si>
-    <t>E'tiborsiz qoldirib</t>
-  </si>
-  <si>
-    <t>'Nega' savoli kamida nechanchi savolgacha davom etishi tavsiya etiladi?</t>
-  </si>
-  <si>
-    <t>2-savolgacha</t>
-  </si>
-  <si>
-    <t>4-savolgacha</t>
-  </si>
-  <si>
-    <t>7-savolgacha</t>
-  </si>
-  <si>
-    <t>10-savolgacha</t>
-  </si>
-  <si>
-    <t>Tanaffus vaqti qancha bo'lishi kerak?</t>
-  </si>
-  <si>
-    <t>5-10 daqiqa</t>
-  </si>
-  <si>
-    <t>15-20 daqiqa</t>
-  </si>
-  <si>
-    <t>Tanaffusdan darsga qaytish vaqtini nima qilish mumkin emas?</t>
-  </si>
-  <si>
-    <t>O'g'irlash</t>
-  </si>
-  <si>
-    <t>Aniq belgilash</t>
-  </si>
-  <si>
-    <t>Eslatish</t>
-  </si>
-  <si>
-    <t>Nazorat qilish</t>
-  </si>
-  <si>
-    <t>Katta musobaqalar qanday yosh toifalari asosida o'tkaziladi?</t>
-  </si>
-  <si>
-    <t>9-11 va 9-15</t>
-  </si>
-  <si>
-    <t>5-7 va 8-9</t>
-  </si>
-  <si>
-    <t>16-18 va 19-20</t>
-  </si>
-  <si>
-    <t>Faqat 9-15</t>
-  </si>
-  <si>
-    <t>Katta musobaqa qanchada bir marta o'tkaziladi?</t>
-  </si>
-  <si>
-    <t>Har oy</t>
-  </si>
-  <si>
-    <t>Har 2 oyda</t>
-  </si>
-  <si>
-    <t>Har 6 oyda</t>
-  </si>
-  <si>
-    <t>Har hafta</t>
-  </si>
-  <si>
-    <t>Musobaqaga qo'shimcha event sifatida nimalar navbatma-navbat keladi?</t>
-  </si>
-  <si>
-    <t>Typing va loyihalar taqdimoti</t>
-  </si>
-  <si>
-    <t>Futbol va shaxmat</t>
-  </si>
-  <si>
-    <t>Rasm va musiqa</t>
-  </si>
-  <si>
-    <t>Faqat imtihon</t>
-  </si>
-  <si>
-    <t>Musobaqa haqida qachon oldindan e'lon qilinadi?</t>
-  </si>
-  <si>
-    <t>2 oy oldin</t>
-  </si>
-  <si>
-    <t>1 hafta oldin</t>
-  </si>
-  <si>
-    <t>Musobaqa kuni</t>
-  </si>
-  <si>
-    <t>Musobaqa e'lonida nimalar aks etishi kerak?</t>
-  </si>
-  <si>
-    <t>Taxminiy sana, qat'iy shartlar, yo'nalishlar</t>
-  </si>
-  <si>
-    <t>Ustoz maoshi</t>
-  </si>
-  <si>
-    <t>Ichki shartnoma bahslari</t>
-  </si>
-  <si>
-    <t>Faqat sovg'a rasmi</t>
-  </si>
-  <si>
-    <t>Saralash jarayoni qachon yakunlanishi kerak?</t>
-  </si>
-  <si>
-    <t>Musobaqadan 1 hafta oldin</t>
-  </si>
-  <si>
-    <t>Saralashdan olingan foto/video materiallar kimga taqdim etiladi?</t>
-  </si>
-  <si>
-    <t>Marketing bo'limiga</t>
-  </si>
-  <si>
-    <t>Ota-onaga yashirincha</t>
-  </si>
-  <si>
-    <t>O'quvchiga</t>
-  </si>
-  <si>
-    <t>Wi-Fi adminiga</t>
-  </si>
-  <si>
-    <t>Musobaqadan 3 kun oldin ota-onalar guruhiga nima yuboriladi?</t>
-  </si>
-  <si>
-    <t>Saralashdan o'tganlar ro'yxati va aniq jadval</t>
-  </si>
-  <si>
-    <t>Ustoz oyligi</t>
-  </si>
-  <si>
-    <t>Wi-Fi paroli</t>
-  </si>
-  <si>
-    <t>Musobaqadan 1 kun oldin nima yuboriladi?</t>
-  </si>
-  <si>
-    <t>Oxirgi eslatma xabari</t>
-  </si>
-  <si>
-    <t>Yangi shartnoma</t>
-  </si>
-  <si>
-    <t>Baholar</t>
-  </si>
-  <si>
-    <t>Dars jadvali bekori</t>
-  </si>
-  <si>
-    <t>Musobaqadan 1 kun oldin filialda nimalar tayyor bo'lishi kerak?</t>
-  </si>
-  <si>
-    <t>Kovorking hududi, sovg'alar, sertifikatlar</t>
-  </si>
-  <si>
-    <t>Faqat Wi-Fi</t>
-  </si>
-  <si>
-    <t>Faqat telefon</t>
-  </si>
-  <si>
-    <t>Faqat dars xonasi</t>
-  </si>
-  <si>
-    <t>Event davomida ota-onalar bilan kimlar ochiq suhbat o'tkazadi?</t>
-  </si>
-  <si>
-    <t>Team Lead va filial menejeri</t>
-  </si>
-  <si>
-    <t>Faqat o'quvchilar</t>
-  </si>
-  <si>
-    <t>Faqat support teacher</t>
-  </si>
-  <si>
-    <t>O'qituvchi bir oyda nechta favqulodda sababsiz dars qoldirishi mumkin emas?</t>
-  </si>
-  <si>
-    <t>1 martadan ortiq</t>
-  </si>
-  <si>
-    <t>2 martadan ortiq</t>
-  </si>
-  <si>
-    <t>3 martadan ortiq</t>
-  </si>
-  <si>
-    <t>Cheklov yo'q</t>
-  </si>
-  <si>
-    <t>Dars qoldirish zarur bo'lsa, kamida qachon rasmiy guruhda ogohlantirish kerak?</t>
-  </si>
-  <si>
-    <t>1 soat oldin</t>
-  </si>
-  <si>
-    <t>Dars qoldirganda o'rniga kim topilishi kerak?</t>
-  </si>
-  <si>
-    <t>Ustoz</t>
-  </si>
-  <si>
-    <t>O'quvchi</t>
-  </si>
-  <si>
-    <t>Ota-ona</t>
-  </si>
-  <si>
-    <t>Reception</t>
-  </si>
-  <si>
-    <t>Support teacher ruxsatsiz darsda qoldirilishi mumkinmi?</t>
-  </si>
-  <si>
-    <t>Faqat kichik guruhda</t>
-  </si>
-  <si>
-    <t>Dars 08:30 da boshlansa, ustoz qachon xonada bo'lishi kerak?</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>1 daqiqa kechikish ham hisobga olinadimi?</t>
-  </si>
-  <si>
-    <t>Faqat imtihonda</t>
-  </si>
-  <si>
-    <t>Faqat ota-ona ko'rsa</t>
-  </si>
-  <si>
-    <t>1-5 daqiqa kechikish qanday hisoblanadi?</t>
-  </si>
-  <si>
-    <t>Kichik kechikish</t>
-  </si>
-  <si>
-    <t>Katta kechikish</t>
-  </si>
-  <si>
-    <t>Hisoblanmaydi</t>
-  </si>
-  <si>
-    <t>Mukofot</t>
-  </si>
-  <si>
-    <t>5 daqiqadan ortiq kechikish qanday hisoblanadi?</t>
-  </si>
-  <si>
-    <t>Ogohlantirish emas</t>
-  </si>
-  <si>
-    <t>3 ta kichik kechikish nimaga teng?</t>
-  </si>
-  <si>
-    <t>1 ta katta kechikish</t>
-  </si>
-  <si>
-    <t>2 ta katta kechikish</t>
-  </si>
-  <si>
-    <t>Yarim kechikish</t>
-  </si>
-  <si>
-    <t>O'quvchilarning darsda uxlab qolishi qaysi ro'yxatga kiradi?</t>
-  </si>
-  <si>
-    <t>Taqiqlangan holatlar</t>
-  </si>
-  <si>
-    <t>Mukofotlar</t>
-  </si>
-  <si>
-    <t>O'quvchilarga ustozning haqiqiy yoshi haqida gapirish mumkinmi?</t>
-  </si>
-  <si>
-    <t>Faqat 15 yoshdan kattalarga</t>
-  </si>
-  <si>
-    <t>O'quvchilarga ustozning shaxsiy oylik maoshi haqida gapirish mumkinmi?</t>
-  </si>
-  <si>
-    <t>Faqat yakka tartibda</t>
-  </si>
-  <si>
-    <t>O'quvchilar bilan tizim, rahbarlar yoki shartnoma bandlarini muhokama qilish mumkinmi?</t>
-  </si>
-  <si>
-    <t>Faqat norasmiy</t>
-  </si>
-  <si>
-    <t>Qo'pol so'zlashish qanday hisoblanadi?</t>
-  </si>
-  <si>
-    <t>Jiddiy intizomiy holat</t>
-  </si>
-  <si>
-    <t>Oddiy holat</t>
-  </si>
-  <si>
-    <t>Tavsiya</t>
-  </si>
-  <si>
-    <t>Bolalarni guruh oldida kamsitish mumkinmi?</t>
-  </si>
-  <si>
-    <t>Faqat ogohlantirish sifatida</t>
-  </si>
-  <si>
-    <t>Dars vaqtida telefonda chalg'ib o'tirish mumkinmi?</t>
-  </si>
-  <si>
-    <t>Faqat 5 daqiqa</t>
-  </si>
-  <si>
-    <t>Faqat xabar yozish</t>
-  </si>
-  <si>
-    <t>Darsni tekshiruvlar tufayli sababsiz tark etish mumkinmi?</t>
-  </si>
-  <si>
-    <t>Faqat charchasa</t>
-  </si>
-  <si>
-    <t>Faqat tanaffusdan oldin</t>
-  </si>
-  <si>
-    <t>Wi-Fi vaucher tarmog'iga ulanishda qaysi tarmoq tanlanadi?</t>
-  </si>
-  <si>
-    <t>Wi-Fi vaucher</t>
-  </si>
-  <si>
-    <t>Home Wi-Fi</t>
-  </si>
-  <si>
-    <t>Guest random</t>
-  </si>
-  <si>
-    <t>Admin only</t>
-  </si>
-  <si>
-    <t>Wi-Fi ID qanday yoziladi?</t>
-  </si>
-  <si>
-    <t>ID1234</t>
-  </si>
-  <si>
-    <t>id1234</t>
-  </si>
-  <si>
-    <t>Id 1234</t>
-  </si>
-  <si>
-    <t>ID 1234</t>
-  </si>
-  <si>
-    <t>Wi-Fi parolida telefon raqami qanday yoziladi?</t>
-  </si>
-  <si>
-    <t>+ belgisisiz</t>
-  </si>
-  <si>
-    <t>Plus belgisi bilan</t>
-  </si>
-  <si>
-    <t>Bo'shliqlar bilan</t>
-  </si>
-  <si>
-    <t>Harflar bilan</t>
-  </si>
-  <si>
-    <t>Wi-Fi boshqa qurilmaga ulanmayotgan bo'lsa, avval nima qilish mumkin?</t>
-  </si>
-  <si>
-    <t>Forget qilib qayta ulash</t>
-  </si>
-  <si>
-    <t>Kompyuterni sindirish</t>
-  </si>
-  <si>
-    <t>Parolni o'zgartirish</t>
-  </si>
-  <si>
-    <t>Ustozlik mahorati video-darslari qayerda berilgan?</t>
-  </si>
-  <si>
-    <t>Telegram havolasida</t>
-  </si>
-  <si>
-    <t>ERP bahosida</t>
-  </si>
-  <si>
-    <t>Wi-Fi parolida</t>
-  </si>
-  <si>
-    <t>Dress code ro'yxatida</t>
-  </si>
-  <si>
-    <t>Head teacher bilan bog'lanish uchun kim ko'rsatilgan?</t>
-  </si>
-  <si>
-    <t>Ibrohim Qodirov</t>
-  </si>
-  <si>
-    <t>Hasanboy Majidov</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>O'quv bo'limi Timlideri sifatida kim ko'rsatilgan?</t>
-  </si>
-  <si>
-    <t>Support teacher</t>
   </si>
 </sst>
 </file>
@@ -5010,7 +3444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H338"/>
+  <dimension ref="A1:H331"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
@@ -10250,3099 +8684,1044 @@
       </c>
     </row>
     <row r="202" spans="1:8">
-      <c r="A202" t="s">
-        <v>992</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>995</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="G202" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="H202" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" ht="27.6">
-      <c r="A203" t="s">
-        <v>992</v>
-      </c>
-      <c r="B203" s="4" t="s">
-        <v>999</v>
-      </c>
-      <c r="C203" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="D203" s="5" t="s">
-        <v>996</v>
-      </c>
-      <c r="E203" s="5" t="s">
-        <v>997</v>
-      </c>
-      <c r="F203" s="5" t="s">
-        <v>998</v>
-      </c>
-      <c r="G203" s="6" t="s">
-        <v>996</v>
-      </c>
-      <c r="H203" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" ht="27.6">
-      <c r="A204" t="s">
-        <v>992</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="F204" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G204" s="3" t="s">
-        <v>997</v>
-      </c>
-      <c r="H204" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" ht="27.6">
-      <c r="A205" t="s">
-        <v>992</v>
-      </c>
-      <c r="B205" s="4" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C205" s="5" t="s">
-        <v>997</v>
-      </c>
-      <c r="D205" s="5" t="s">
-        <v>998</v>
-      </c>
-      <c r="E205" s="5" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F205" s="5" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G205" s="6" t="s">
-        <v>998</v>
-      </c>
-      <c r="H205" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" ht="27.6">
-      <c r="A206" t="s">
-        <v>992</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>1003</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G206" s="3" t="s">
-        <v>1001</v>
-      </c>
-      <c r="H206" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" ht="27.6">
-      <c r="A207" t="s">
-        <v>992</v>
-      </c>
-      <c r="B207" s="4" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D207" s="5" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E207" s="5" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F207" s="5" t="s">
-        <v>998</v>
-      </c>
-      <c r="G207" s="6" t="s">
-        <v>1003</v>
-      </c>
-      <c r="H207" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" ht="27.6">
-      <c r="A208" t="s">
-        <v>992</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="G208" s="3" t="s">
-        <v>1005</v>
-      </c>
-      <c r="H208" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" ht="27.6">
-      <c r="A209" t="s">
-        <v>992</v>
-      </c>
-      <c r="B209" s="4" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C209" s="5" t="s">
-        <v>998</v>
-      </c>
-      <c r="D209" s="5" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E209" s="5" t="s">
-        <v>1003</v>
-      </c>
-      <c r="F209" s="5" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G209" s="6" t="s">
-        <v>1005</v>
-      </c>
-      <c r="H209" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8">
-      <c r="A210" t="s">
-        <v>992</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G210" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="H210" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8">
-      <c r="A211" t="s">
-        <v>992</v>
-      </c>
-      <c r="B211" s="4" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C211" s="5" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D211" s="5" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E211" s="5" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F211" s="5" t="s">
-        <v>1014</v>
-      </c>
-      <c r="G211" s="6" t="s">
-        <v>1011</v>
-      </c>
-      <c r="H211" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" ht="27.6">
-      <c r="A212" t="s">
-        <v>992</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G212" s="3" t="s">
-        <v>1017</v>
-      </c>
-      <c r="H212" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" ht="27.6">
-      <c r="A213" t="s">
-        <v>992</v>
-      </c>
-      <c r="B213" s="4" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C213" s="5" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D213" s="5" t="s">
-        <v>1022</v>
-      </c>
-      <c r="E213" s="5" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F213" s="5" t="s">
-        <v>1024</v>
-      </c>
-      <c r="G213" s="6" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H213" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8">
-      <c r="A214" t="s">
-        <v>992</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G214" s="3" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H214" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" ht="27.6">
-      <c r="A215" t="s">
-        <v>992</v>
-      </c>
-      <c r="B215" s="4" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C215" s="5" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D215" s="5" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E215" s="5" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F215" s="5" t="s">
-        <v>1034</v>
-      </c>
-      <c r="G215" s="6" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H215" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" ht="27.6">
-      <c r="A216" t="s">
-        <v>992</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>1036</v>
-      </c>
-      <c r="F216" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="G216" s="3" t="s">
-        <v>1034</v>
-      </c>
-      <c r="H216" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" ht="27.6">
-      <c r="A217" t="s">
-        <v>992</v>
-      </c>
-      <c r="B217" s="4" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C217" s="5" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D217" s="5" t="s">
-        <v>1019</v>
-      </c>
-      <c r="E217" s="5" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F217" s="5" t="s">
-        <v>1041</v>
-      </c>
-      <c r="G217" s="6" t="s">
-        <v>1040</v>
-      </c>
-      <c r="H217" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" ht="27.6">
-      <c r="A218" t="s">
-        <v>992</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>1019</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="G218" s="3" t="s">
-        <v>1019</v>
-      </c>
-      <c r="H218" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" ht="27.6">
-      <c r="A219" t="s">
-        <v>992</v>
-      </c>
-      <c r="B219" s="4" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D219" s="5" t="s">
-        <v>1039</v>
-      </c>
-      <c r="E219" s="5" t="s">
-        <v>1019</v>
-      </c>
-      <c r="F219" s="5" t="s">
-        <v>1040</v>
-      </c>
-      <c r="G219" s="6" t="s">
-        <v>1039</v>
-      </c>
-      <c r="H219" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8">
-      <c r="A220" t="s">
-        <v>992</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>1047</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="G220" s="3" t="s">
-        <v>1045</v>
-      </c>
-      <c r="H220" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8">
-      <c r="A221" t="s">
-        <v>992</v>
-      </c>
-      <c r="B221" s="4" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C221" s="5" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D221" s="5" t="s">
-        <v>1051</v>
-      </c>
-      <c r="E221" s="5" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F221" s="5" t="s">
-        <v>1053</v>
-      </c>
-      <c r="G221" s="6" t="s">
-        <v>1051</v>
-      </c>
-      <c r="H221" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" ht="27.6">
-      <c r="A222" t="s">
-        <v>992</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G222" s="3" t="s">
-        <v>1056</v>
-      </c>
-      <c r="H222" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" ht="27.6">
-      <c r="A223" t="s">
-        <v>992</v>
-      </c>
-      <c r="B223" s="4" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>1058</v>
-      </c>
-      <c r="D223" s="5" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E223" s="5" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F223" s="5" t="s">
-        <v>1061</v>
-      </c>
-      <c r="G223" s="6" t="s">
-        <v>1058</v>
-      </c>
-      <c r="H223" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8">
-      <c r="A224" t="s">
-        <v>992</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="G224" s="3" t="s">
-        <v>1063</v>
-      </c>
-      <c r="H224" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" ht="27.6">
-      <c r="A225" t="s">
-        <v>992</v>
-      </c>
-      <c r="B225" s="4" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>1068</v>
-      </c>
-      <c r="D225" s="5" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E225" s="5" t="s">
-        <v>1070</v>
-      </c>
-      <c r="F225" s="5" t="s">
-        <v>1071</v>
-      </c>
-      <c r="G225" s="6" t="s">
-        <v>1068</v>
-      </c>
-      <c r="H225" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" ht="27.6">
-      <c r="A226" t="s">
-        <v>992</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G226" s="3" t="s">
-        <v>1074</v>
-      </c>
-      <c r="H226" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" ht="27.6">
-      <c r="A227" t="s">
-        <v>992</v>
-      </c>
-      <c r="B227" s="4" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C227" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D227" s="5" t="s">
-        <v>1079</v>
-      </c>
-      <c r="E227" s="5" t="s">
-        <v>1080</v>
-      </c>
-      <c r="F227" s="5" t="s">
-        <v>1081</v>
-      </c>
-      <c r="G227" s="6" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" ht="27.6">
-      <c r="A228" t="s">
-        <v>992</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="G228" s="3" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8">
-      <c r="A229" t="s">
-        <v>992</v>
-      </c>
-      <c r="B229" s="4" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D229" s="5" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E229" s="5" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F229" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="G229" s="6" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8">
-      <c r="A230" t="s">
-        <v>992</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>1094</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="G230" s="3" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" ht="27.6">
-      <c r="A231" t="s">
-        <v>992</v>
-      </c>
-      <c r="B231" s="4" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D231" s="5" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E231" s="5" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F231" s="5" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G231" s="6" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8" ht="27.6">
-      <c r="A232" t="s">
-        <v>992</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>1106</v>
-      </c>
-      <c r="G232" s="3" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8" ht="27.6">
-      <c r="A233" t="s">
-        <v>992</v>
-      </c>
-      <c r="B233" s="4" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D233" s="5" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E233" s="5" t="s">
-        <v>1110</v>
-      </c>
-      <c r="F233" s="5" t="s">
-        <v>1111</v>
-      </c>
-      <c r="G233" s="6" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8">
-      <c r="A234" t="s">
-        <v>992</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="G234" s="3" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8">
-      <c r="A235" t="s">
-        <v>992</v>
-      </c>
-      <c r="B235" s="4" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D235" s="5" t="s">
-        <v>1073</v>
-      </c>
-      <c r="E235" s="5" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F235" s="5" t="s">
-        <v>1117</v>
-      </c>
-      <c r="G235" s="6" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8">
-      <c r="A236" t="s">
-        <v>992</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D236" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="G236" s="3" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8" ht="27.6">
-      <c r="A237" t="s">
-        <v>992</v>
-      </c>
-      <c r="B237" s="4" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C237" s="5" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D237" s="5" t="s">
-        <v>1125</v>
-      </c>
-      <c r="E237" s="5" t="s">
-        <v>1126</v>
-      </c>
-      <c r="F237" s="5" t="s">
-        <v>1127</v>
-      </c>
-      <c r="G237" s="6" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" ht="27.6">
-      <c r="A238" t="s">
-        <v>992</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>1129</v>
-      </c>
-      <c r="D238" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="G238" s="3" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" ht="27.6">
-      <c r="A239" t="s">
-        <v>992</v>
-      </c>
-      <c r="B239" s="4" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C239" s="5" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D239" s="5" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E239" s="5" t="s">
-        <v>1135</v>
-      </c>
-      <c r="F239" s="5" t="s">
-        <v>1136</v>
-      </c>
-      <c r="G239" s="6" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8">
-      <c r="A240" t="s">
-        <v>992</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>1140</v>
-      </c>
-      <c r="G240" s="3" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7">
-      <c r="A241" t="s">
-        <v>992</v>
-      </c>
-      <c r="B241" s="4" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>1142</v>
-      </c>
-      <c r="D241" s="5" t="s">
-        <v>1143</v>
-      </c>
-      <c r="E241" s="5" t="s">
-        <v>1144</v>
-      </c>
-      <c r="F241" s="5" t="s">
-        <v>1145</v>
-      </c>
-      <c r="G241" s="6" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7">
-      <c r="A242" t="s">
-        <v>992</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D242" s="2" t="s">
-        <v>1148</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>1149</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>994</v>
-      </c>
-      <c r="G242" s="3" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" ht="27.6">
-      <c r="A243" t="s">
-        <v>992</v>
-      </c>
-      <c r="B243" s="4" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>1151</v>
-      </c>
-      <c r="D243" s="5" t="s">
-        <v>1152</v>
-      </c>
-      <c r="E243" s="5" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F243" s="5" t="s">
-        <v>1154</v>
-      </c>
-      <c r="G243" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7">
-      <c r="A244" t="s">
-        <v>992</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>1156</v>
-      </c>
-      <c r="D244" s="2" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F244" s="2" t="s">
-        <v>1158</v>
-      </c>
-      <c r="G244" s="3" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7">
-      <c r="A245" t="s">
-        <v>992</v>
-      </c>
-      <c r="B245" s="4" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>1160</v>
-      </c>
-      <c r="D245" s="5" t="s">
-        <v>1161</v>
-      </c>
-      <c r="E245" s="5" t="s">
-        <v>1162</v>
-      </c>
-      <c r="F245" s="5" t="s">
-        <v>1163</v>
-      </c>
-      <c r="G245" s="6" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" ht="27.6">
-      <c r="A246" t="s">
-        <v>992</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>1165</v>
-      </c>
-      <c r="G246" s="3" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7">
-      <c r="A247" t="s">
-        <v>992</v>
-      </c>
-      <c r="B247" s="4" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C247" s="5" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D247" s="5" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E247" s="5" t="s">
-        <v>1167</v>
-      </c>
-      <c r="F247" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="G247" s="6" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7">
-      <c r="A248" t="s">
-        <v>992</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>1171</v>
-      </c>
-      <c r="F248" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="G248" s="3" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7">
-      <c r="A249" t="s">
-        <v>992</v>
-      </c>
-      <c r="B249" s="4" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>1174</v>
-      </c>
-      <c r="D249" s="5" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E249" s="5" t="s">
-        <v>1176</v>
-      </c>
-      <c r="F249" s="5" t="s">
-        <v>1177</v>
-      </c>
-      <c r="G249" s="6" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" ht="27.6">
-      <c r="A250" t="s">
-        <v>992</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D250" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>1165</v>
-      </c>
-      <c r="G250" s="3" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" ht="27.6">
-      <c r="A251" t="s">
-        <v>992</v>
-      </c>
-      <c r="B251" s="4" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D251" s="5" t="s">
-        <v>1182</v>
-      </c>
-      <c r="E251" s="5" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F251" s="5" t="s">
-        <v>1125</v>
-      </c>
-      <c r="G251" s="6" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" ht="27.6">
-      <c r="A252" t="s">
-        <v>992</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>1185</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>1186</v>
-      </c>
-      <c r="F252" s="2" t="s">
-        <v>1187</v>
-      </c>
-      <c r="G252" s="3" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7">
-      <c r="A253" t="s">
-        <v>992</v>
-      </c>
-      <c r="B253" s="4" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>1189</v>
-      </c>
-      <c r="D253" s="5" t="s">
-        <v>1190</v>
-      </c>
-      <c r="E253" s="5" t="s">
-        <v>1191</v>
-      </c>
-      <c r="F253" s="5" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G253" s="6" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7">
-      <c r="A254" t="s">
-        <v>992</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>1195</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>1196</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>1197</v>
-      </c>
-      <c r="G254" s="3" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7">
-      <c r="A255" t="s">
-        <v>992</v>
-      </c>
-      <c r="B255" s="4" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>1199</v>
-      </c>
-      <c r="D255" s="5" t="s">
-        <v>1194</v>
-      </c>
-      <c r="E255" s="5" t="s">
-        <v>1200</v>
-      </c>
-      <c r="F255" s="5" t="s">
-        <v>1201</v>
-      </c>
-      <c r="G255" s="6" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" ht="27.6">
-      <c r="A256" t="s">
-        <v>992</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>1185</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F256" s="2" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G256" s="3" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7">
-      <c r="A257" t="s">
-        <v>992</v>
-      </c>
-      <c r="B257" s="4" t="s">
-        <v>1206</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>1195</v>
-      </c>
-      <c r="D257" s="5" t="s">
-        <v>1207</v>
-      </c>
-      <c r="E257" s="5" t="s">
-        <v>1208</v>
-      </c>
-      <c r="F257" s="5" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G257" s="6" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" ht="27.6">
-      <c r="A258" t="s">
-        <v>992</v>
-      </c>
-      <c r="B258" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>1211</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>1212</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G258" s="3" t="s">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
-      <c r="A259" t="s">
-        <v>992</v>
-      </c>
-      <c r="B259" s="4" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C259" s="5" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D259" s="5" t="s">
-        <v>1216</v>
-      </c>
-      <c r="E259" s="5" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F259" s="5" t="s">
-        <v>1135</v>
-      </c>
-      <c r="G259" s="6" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" ht="27.6">
-      <c r="A260" t="s">
-        <v>992</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D260" s="2" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>1220</v>
-      </c>
-      <c r="F260" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="G260" s="3" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7">
-      <c r="A261" t="s">
-        <v>992</v>
-      </c>
-      <c r="B261" s="4" t="s">
-        <v>1222</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>1223</v>
-      </c>
-      <c r="D261" s="5" t="s">
-        <v>1224</v>
-      </c>
-      <c r="E261" s="5" t="s">
-        <v>1225</v>
-      </c>
-      <c r="F261" s="5" t="s">
-        <v>1226</v>
-      </c>
-      <c r="G261" s="6" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7">
-      <c r="A262" t="s">
-        <v>992</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>1227</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>1228</v>
-      </c>
-      <c r="D262" s="2" t="s">
-        <v>1229</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>1230</v>
-      </c>
-      <c r="F262" s="2" t="s">
-        <v>1231</v>
-      </c>
-      <c r="G262" s="3" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" ht="27.6">
-      <c r="A263" t="s">
-        <v>992</v>
-      </c>
-      <c r="B263" s="4" t="s">
-        <v>1232</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>1233</v>
-      </c>
-      <c r="D263" s="5" t="s">
-        <v>1234</v>
-      </c>
-      <c r="E263" s="5" t="s">
-        <v>1235</v>
-      </c>
-      <c r="F263" s="5" t="s">
-        <v>1236</v>
-      </c>
-      <c r="G263" s="6" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7">
-      <c r="A264" t="s">
-        <v>992</v>
-      </c>
-      <c r="B264" s="1" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>1239</v>
-      </c>
-      <c r="E264" s="2" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F264" s="2" t="s">
-        <v>1241</v>
-      </c>
-      <c r="G264" s="3" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7">
-      <c r="A265" t="s">
-        <v>992</v>
-      </c>
-      <c r="B265" s="4" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C265" s="5" t="s">
-        <v>1243</v>
-      </c>
-      <c r="D265" s="5" t="s">
-        <v>1244</v>
-      </c>
-      <c r="E265" s="5" t="s">
-        <v>1245</v>
-      </c>
-      <c r="F265" s="5" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G265" s="6" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
-      <c r="A266" t="s">
-        <v>992</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>1246</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>1212</v>
-      </c>
-      <c r="E266" s="2" t="s">
-        <v>1248</v>
-      </c>
-      <c r="F266" s="2" t="s">
-        <v>1249</v>
-      </c>
-      <c r="G266" s="3" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7">
-      <c r="A267" t="s">
-        <v>992</v>
-      </c>
-      <c r="B267" s="4" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C267" s="5" t="s">
-        <v>1251</v>
-      </c>
-      <c r="D267" s="5" t="s">
-        <v>1212</v>
-      </c>
-      <c r="E267" s="5" t="s">
-        <v>1252</v>
-      </c>
-      <c r="F267" s="5" t="s">
-        <v>1253</v>
-      </c>
-      <c r="G267" s="6" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" ht="27.6">
-      <c r="A268" t="s">
-        <v>992</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>1255</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>1248</v>
-      </c>
-      <c r="E268" s="2" t="s">
-        <v>1212</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G268" s="3" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" ht="27.6">
-      <c r="A269" t="s">
-        <v>992</v>
-      </c>
-      <c r="B269" s="4" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C269" s="5" t="s">
-        <v>1258</v>
-      </c>
-      <c r="D269" s="5" t="s">
-        <v>1259</v>
-      </c>
-      <c r="E269" s="5" t="s">
-        <v>1260</v>
-      </c>
-      <c r="F269" s="5" t="s">
-        <v>1261</v>
-      </c>
-      <c r="G269" s="6" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" ht="27.6">
-      <c r="A270" t="s">
-        <v>992</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>1264</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>1265</v>
-      </c>
-      <c r="F270" s="2" t="s">
-        <v>1266</v>
-      </c>
-      <c r="G270" s="3" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7">
-      <c r="A271" t="s">
-        <v>992</v>
-      </c>
-      <c r="B271" s="4" t="s">
-        <v>1267</v>
-      </c>
-      <c r="C271" s="5" t="s">
-        <v>1268</v>
-      </c>
-      <c r="D271" s="5" t="s">
-        <v>1269</v>
-      </c>
-      <c r="E271" s="5" t="s">
-        <v>1270</v>
-      </c>
-      <c r="F271" s="5" t="s">
-        <v>1271</v>
-      </c>
-      <c r="G271" s="6" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7">
-      <c r="A272" t="s">
-        <v>992</v>
-      </c>
-      <c r="B272" s="1" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D272" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="E272" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F272" s="2" t="s">
-        <v>1165</v>
-      </c>
-      <c r="G272" s="3" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" ht="27.6">
-      <c r="A273" t="s">
-        <v>992</v>
-      </c>
-      <c r="B273" s="4" t="s">
-        <v>1273</v>
-      </c>
-      <c r="C273" s="5" t="s">
-        <v>1274</v>
-      </c>
-      <c r="D273" s="5" t="s">
-        <v>1275</v>
-      </c>
-      <c r="E273" s="5" t="s">
-        <v>1276</v>
-      </c>
-      <c r="F273" s="5" t="s">
-        <v>1277</v>
-      </c>
-      <c r="G273" s="6" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7">
-      <c r="A274" t="s">
-        <v>992</v>
-      </c>
-      <c r="B274" s="1" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>1279</v>
-      </c>
-      <c r="D274" s="2" t="s">
-        <v>1280</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F274" s="2" t="s">
-        <v>1281</v>
-      </c>
-      <c r="G274" s="3" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" ht="27.6">
-      <c r="A275" t="s">
-        <v>992</v>
-      </c>
-      <c r="B275" s="4" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C275" s="5" t="s">
-        <v>1283</v>
-      </c>
-      <c r="D275" s="5" t="s">
-        <v>1125</v>
-      </c>
-      <c r="E275" s="5" t="s">
-        <v>1284</v>
-      </c>
-      <c r="F275" s="5" t="s">
-        <v>1285</v>
-      </c>
-      <c r="G275" s="6" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7">
-      <c r="A276" t="s">
-        <v>992</v>
-      </c>
-      <c r="B276" s="1" t="s">
-        <v>1286</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>1287</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E276" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F276" s="2" t="s">
-        <v>1288</v>
-      </c>
-      <c r="G276" s="3" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="27.6">
-      <c r="A277" t="s">
-        <v>992</v>
-      </c>
-      <c r="B277" s="4" t="s">
-        <v>1289</v>
-      </c>
-      <c r="C277" s="5" t="s">
-        <v>1290</v>
-      </c>
-      <c r="D277" s="5" t="s">
-        <v>1291</v>
-      </c>
-      <c r="E277" s="5" t="s">
-        <v>1292</v>
-      </c>
-      <c r="F277" s="5" t="s">
-        <v>1293</v>
-      </c>
-      <c r="G277" s="6" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7">
-      <c r="A278" t="s">
-        <v>992</v>
-      </c>
-      <c r="B278" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>1295</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>1296</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>1297</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>1298</v>
-      </c>
-      <c r="G278" s="3" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" ht="27.6">
-      <c r="A279" t="s">
-        <v>992</v>
-      </c>
-      <c r="B279" s="4" t="s">
-        <v>1299</v>
-      </c>
-      <c r="C279" s="5" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D279" s="5" t="s">
-        <v>1301</v>
-      </c>
-      <c r="E279" s="5" t="s">
-        <v>1302</v>
-      </c>
-      <c r="F279" s="5" t="s">
-        <v>1303</v>
-      </c>
-      <c r="G279" s="6" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7">
-      <c r="A280" t="s">
-        <v>992</v>
-      </c>
-      <c r="B280" s="1" t="s">
-        <v>1304</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>1305</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>1306</v>
-      </c>
-      <c r="E280" s="2" t="s">
-        <v>1307</v>
-      </c>
-      <c r="F280" s="2" t="s">
-        <v>1308</v>
-      </c>
-      <c r="G280" s="3" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
-      <c r="A281" t="s">
-        <v>992</v>
-      </c>
-      <c r="B281" s="4" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C281" s="5" t="s">
-        <v>1310</v>
-      </c>
-      <c r="D281" s="5" t="s">
-        <v>1311</v>
-      </c>
-      <c r="E281" s="5" t="s">
-        <v>1297</v>
-      </c>
-      <c r="F281" s="5" t="s">
-        <v>1312</v>
-      </c>
-      <c r="G281" s="6" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7">
-      <c r="A282" t="s">
-        <v>992</v>
-      </c>
-      <c r="B282" s="1" t="s">
-        <v>1313</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>1314</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>1315</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>1316</v>
-      </c>
-      <c r="F282" s="2" t="s">
-        <v>1317</v>
-      </c>
-      <c r="G282" s="3" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7">
-      <c r="A283" t="s">
-        <v>992</v>
-      </c>
-      <c r="B283" s="4" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C283" s="5" t="s">
-        <v>1319</v>
-      </c>
-      <c r="D283" s="5" t="s">
-        <v>1320</v>
-      </c>
-      <c r="E283" s="5" t="s">
-        <v>1321</v>
-      </c>
-      <c r="F283" s="5" t="s">
-        <v>1322</v>
-      </c>
-      <c r="G283" s="6" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7">
-      <c r="A284" t="s">
-        <v>992</v>
-      </c>
-      <c r="B284" s="1" t="s">
-        <v>1323</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>1324</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>1325</v>
-      </c>
-      <c r="E284" s="2" t="s">
-        <v>1326</v>
-      </c>
-      <c r="F284" s="2" t="s">
-        <v>1327</v>
-      </c>
-      <c r="G284" s="3" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7">
-      <c r="A285" t="s">
-        <v>992</v>
-      </c>
-      <c r="B285" s="4" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C285" s="5" t="s">
-        <v>1329</v>
-      </c>
-      <c r="D285" s="5" t="s">
-        <v>1330</v>
-      </c>
-      <c r="E285" s="5" t="s">
-        <v>1331</v>
-      </c>
-      <c r="F285" s="5" t="s">
-        <v>1332</v>
-      </c>
-      <c r="G285" s="6" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
-      <c r="A286" t="s">
-        <v>992</v>
-      </c>
-      <c r="B286" s="1" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>1334</v>
-      </c>
-      <c r="D286" s="2" t="s">
-        <v>1335</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>1336</v>
-      </c>
-      <c r="F286" s="2" t="s">
-        <v>1337</v>
-      </c>
-      <c r="G286" s="3" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7">
-      <c r="A287" t="s">
-        <v>992</v>
-      </c>
-      <c r="B287" s="4" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C287" s="5" t="s">
-        <v>1339</v>
-      </c>
-      <c r="D287" s="5" t="s">
-        <v>1340</v>
-      </c>
-      <c r="E287" s="5" t="s">
-        <v>1341</v>
-      </c>
-      <c r="F287" s="5" t="s">
-        <v>1342</v>
-      </c>
-      <c r="G287" s="6" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7">
-      <c r="A288" t="s">
-        <v>992</v>
-      </c>
-      <c r="B288" s="1" t="s">
-        <v>1343</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>1344</v>
-      </c>
-      <c r="D288" s="2" t="s">
-        <v>1345</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F288" s="2" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G288" s="3" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" ht="27.6">
-      <c r="A289" t="s">
-        <v>992</v>
-      </c>
-      <c r="B289" s="4" t="s">
-        <v>1347</v>
-      </c>
-      <c r="C289" s="5" t="s">
-        <v>1348</v>
-      </c>
-      <c r="D289" s="5" t="s">
-        <v>1349</v>
-      </c>
-      <c r="E289" s="5" t="s">
-        <v>1350</v>
-      </c>
-      <c r="F289" s="5" t="s">
-        <v>1351</v>
-      </c>
-      <c r="G289" s="6" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" ht="27.6">
-      <c r="A290" t="s">
-        <v>992</v>
-      </c>
-      <c r="B290" s="1" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>1353</v>
-      </c>
-      <c r="D290" s="2" t="s">
-        <v>1354</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>1355</v>
-      </c>
-      <c r="G290" s="3" t="s">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" ht="27.6">
-      <c r="A291" t="s">
-        <v>992</v>
-      </c>
-      <c r="B291" s="4" t="s">
-        <v>1356</v>
-      </c>
-      <c r="C291" s="5" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D291" s="5" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E291" s="5" t="s">
-        <v>1357</v>
-      </c>
-      <c r="F291" s="5" t="s">
-        <v>1358</v>
-      </c>
-      <c r="G291" s="6" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7">
-      <c r="A292" t="s">
-        <v>992</v>
-      </c>
-      <c r="B292" s="1" t="s">
-        <v>1359</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>1360</v>
-      </c>
-      <c r="D292" s="2" t="s">
-        <v>1361</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>1162</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>1362</v>
-      </c>
-      <c r="G292" s="3" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="27.6">
-      <c r="A293" t="s">
-        <v>992</v>
-      </c>
-      <c r="B293" s="4" t="s">
-        <v>1363</v>
-      </c>
-      <c r="C293" s="5" t="s">
-        <v>1364</v>
-      </c>
-      <c r="D293" s="5" t="s">
-        <v>1365</v>
-      </c>
-      <c r="E293" s="5" t="s">
-        <v>1366</v>
-      </c>
-      <c r="F293" s="5" t="s">
-        <v>1367</v>
-      </c>
-      <c r="G293" s="6" t="s">
-        <v>1364</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" ht="27.6">
-      <c r="A294" t="s">
-        <v>992</v>
-      </c>
-      <c r="B294" s="1" t="s">
-        <v>1368</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>1369</v>
-      </c>
-      <c r="D294" s="2" t="s">
-        <v>1370</v>
-      </c>
-      <c r="E294" s="2" t="s">
-        <v>1371</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>1372</v>
-      </c>
-      <c r="G294" s="3" t="s">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7">
-      <c r="A295" t="s">
-        <v>992</v>
-      </c>
-      <c r="B295" s="4" t="s">
-        <v>1373</v>
-      </c>
-      <c r="C295" s="5" t="s">
-        <v>1374</v>
-      </c>
-      <c r="D295" s="5" t="s">
-        <v>1375</v>
-      </c>
-      <c r="E295" s="5" t="s">
-        <v>1136</v>
-      </c>
-      <c r="F295" s="5" t="s">
-        <v>1120</v>
-      </c>
-      <c r="G295" s="6" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7">
-      <c r="A296" t="s">
-        <v>992</v>
-      </c>
-      <c r="B296" s="1" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>1377</v>
-      </c>
-      <c r="D296" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="E296" s="2" t="s">
-        <v>1379</v>
-      </c>
-      <c r="F296" s="2" t="s">
-        <v>1380</v>
-      </c>
-      <c r="G296" s="3" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7">
-      <c r="A297" t="s">
-        <v>992</v>
-      </c>
-      <c r="B297" s="4" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C297" s="5" t="s">
-        <v>1382</v>
-      </c>
-      <c r="D297" s="5" t="s">
-        <v>1383</v>
-      </c>
-      <c r="E297" s="5" t="s">
-        <v>1384</v>
-      </c>
-      <c r="F297" s="5" t="s">
-        <v>1385</v>
-      </c>
-      <c r="G297" s="6" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7">
-      <c r="A298" t="s">
-        <v>992</v>
-      </c>
-      <c r="B298" s="1" t="s">
-        <v>1386</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>1387</v>
-      </c>
-      <c r="D298" s="2" t="s">
-        <v>1388</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>1389</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>1390</v>
-      </c>
-      <c r="G298" s="3" t="s">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" ht="27.6">
-      <c r="A299" t="s">
-        <v>992</v>
-      </c>
-      <c r="B299" s="4" t="s">
-        <v>1391</v>
-      </c>
-      <c r="C299" s="5" t="s">
-        <v>1392</v>
-      </c>
-      <c r="D299" s="5" t="s">
-        <v>1393</v>
-      </c>
-      <c r="E299" s="5" t="s">
-        <v>1394</v>
-      </c>
-      <c r="F299" s="5" t="s">
-        <v>1395</v>
-      </c>
-      <c r="G299" s="6" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7">
-      <c r="A300" t="s">
-        <v>992</v>
-      </c>
-      <c r="B300" s="1" t="s">
-        <v>1396</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>1397</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>1398</v>
-      </c>
-      <c r="E300" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="F300" s="2" t="s">
-        <v>1399</v>
-      </c>
-      <c r="G300" s="3" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" ht="27.6">
-      <c r="A301" t="s">
-        <v>992</v>
-      </c>
-      <c r="B301" s="4" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C301" s="5" t="s">
-        <v>1401</v>
-      </c>
-      <c r="D301" s="5" t="s">
-        <v>1402</v>
-      </c>
-      <c r="E301" s="5" t="s">
-        <v>1403</v>
-      </c>
-      <c r="F301" s="5" t="s">
-        <v>1404</v>
-      </c>
-      <c r="G301" s="6" t="s">
-        <v>1401</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7">
-      <c r="A302" t="s">
-        <v>992</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>1405</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>1406</v>
-      </c>
-      <c r="D302" s="2" t="s">
-        <v>1399</v>
-      </c>
-      <c r="E302" s="2" t="s">
-        <v>1397</v>
-      </c>
-      <c r="F302" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="G302" s="3" t="s">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7">
-      <c r="A303" t="s">
-        <v>992</v>
-      </c>
-      <c r="B303" s="4" t="s">
-        <v>1407</v>
-      </c>
-      <c r="C303" s="5" t="s">
-        <v>1408</v>
-      </c>
-      <c r="D303" s="5" t="s">
-        <v>1409</v>
-      </c>
-      <c r="E303" s="5" t="s">
-        <v>1410</v>
-      </c>
-      <c r="F303" s="5" t="s">
-        <v>1411</v>
-      </c>
-      <c r="G303" s="6" t="s">
-        <v>1408</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7" ht="27.6">
-      <c r="A304" t="s">
-        <v>992</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>1412</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D304" s="2" t="s">
-        <v>1209</v>
-      </c>
-      <c r="E304" s="2" t="s">
-        <v>1414</v>
-      </c>
-      <c r="F304" s="2" t="s">
-        <v>1415</v>
-      </c>
-      <c r="G304" s="3" t="s">
-        <v>1413</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7">
-      <c r="A305" t="s">
-        <v>992</v>
-      </c>
-      <c r="B305" s="4" t="s">
-        <v>1416</v>
-      </c>
-      <c r="C305" s="5" t="s">
-        <v>1417</v>
-      </c>
-      <c r="D305" s="5" t="s">
-        <v>1418</v>
-      </c>
-      <c r="E305" s="5" t="s">
-        <v>1419</v>
-      </c>
-      <c r="F305" s="5" t="s">
-        <v>1420</v>
-      </c>
-      <c r="G305" s="6" t="s">
-        <v>1417</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7" ht="27.6">
-      <c r="A306" t="s">
-        <v>992</v>
-      </c>
-      <c r="B306" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>1422</v>
-      </c>
-      <c r="D306" s="2" t="s">
-        <v>1423</v>
-      </c>
-      <c r="E306" s="2" t="s">
-        <v>1424</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>1425</v>
-      </c>
-      <c r="G306" s="3" t="s">
-        <v>1422</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7">
-      <c r="A307" t="s">
-        <v>992</v>
-      </c>
-      <c r="B307" s="4" t="s">
-        <v>1426</v>
-      </c>
-      <c r="C307" s="5" t="s">
-        <v>1427</v>
-      </c>
-      <c r="D307" s="5" t="s">
-        <v>1428</v>
-      </c>
-      <c r="E307" s="5" t="s">
-        <v>1429</v>
-      </c>
-      <c r="F307" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="G307" s="6" t="s">
-        <v>1427</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" ht="27.6">
-      <c r="A308" t="s">
-        <v>992</v>
-      </c>
-      <c r="B308" s="1" t="s">
-        <v>1430</v>
-      </c>
-      <c r="C308" s="2" t="s">
-        <v>1431</v>
-      </c>
-      <c r="D308" s="2" t="s">
-        <v>1432</v>
-      </c>
-      <c r="E308" s="2" t="s">
-        <v>1433</v>
-      </c>
-      <c r="F308" s="2" t="s">
-        <v>1434</v>
-      </c>
-      <c r="G308" s="3" t="s">
-        <v>1431</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7" ht="27.6">
-      <c r="A309" t="s">
-        <v>992</v>
-      </c>
-      <c r="B309" s="4" t="s">
-        <v>1435</v>
-      </c>
-      <c r="C309" s="5" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D309" s="5" t="s">
-        <v>1436</v>
-      </c>
-      <c r="E309" s="5" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F309" s="5" t="s">
-        <v>1081</v>
-      </c>
-      <c r="G309" s="6" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="310" spans="1:7">
-      <c r="A310" t="s">
-        <v>992</v>
-      </c>
-      <c r="B310" s="1" t="s">
-        <v>1437</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>1438</v>
-      </c>
-      <c r="D310" s="2" t="s">
-        <v>1439</v>
-      </c>
-      <c r="E310" s="2" t="s">
-        <v>1440</v>
-      </c>
-      <c r="F310" s="2" t="s">
-        <v>1441</v>
-      </c>
-      <c r="G310" s="3" t="s">
-        <v>1438</v>
-      </c>
-    </row>
-    <row r="311" spans="1:7">
-      <c r="A311" t="s">
-        <v>992</v>
-      </c>
-      <c r="B311" s="4" t="s">
-        <v>1442</v>
-      </c>
-      <c r="C311" s="5" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D311" s="5" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E311" s="5" t="s">
-        <v>1357</v>
-      </c>
-      <c r="F311" s="5" t="s">
-        <v>1443</v>
-      </c>
-      <c r="G311" s="6" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7">
-      <c r="A312" t="s">
-        <v>992</v>
-      </c>
-      <c r="B312" s="1" t="s">
-        <v>1444</v>
-      </c>
-      <c r="C312" s="2" t="s">
-        <v>1445</v>
-      </c>
-      <c r="D312" s="2" t="s">
-        <v>1446</v>
-      </c>
-      <c r="E312" s="2" t="s">
-        <v>1447</v>
-      </c>
-      <c r="F312" s="2" t="s">
-        <v>1448</v>
-      </c>
-      <c r="G312" s="3" t="s">
-        <v>1445</v>
-      </c>
-    </row>
-    <row r="313" spans="1:7">
-      <c r="A313" t="s">
-        <v>992</v>
-      </c>
-      <c r="B313" s="4" t="s">
-        <v>1449</v>
-      </c>
-      <c r="C313" s="5" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D313" s="5" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E313" s="5" t="s">
-        <v>1450</v>
-      </c>
-      <c r="F313" s="5" t="s">
-        <v>1451</v>
-      </c>
-      <c r="G313" s="6" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="314" spans="1:7">
-      <c r="A314" t="s">
-        <v>992</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>1452</v>
-      </c>
-      <c r="C314" s="2" t="s">
-        <v>1453</v>
-      </c>
-      <c r="D314" s="2" t="s">
-        <v>1454</v>
-      </c>
-      <c r="E314" s="2" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>1456</v>
-      </c>
-      <c r="G314" s="3" t="s">
-        <v>1453</v>
-      </c>
-    </row>
-    <row r="315" spans="1:7">
-      <c r="A315" t="s">
-        <v>992</v>
-      </c>
-      <c r="B315" s="4" t="s">
-        <v>1457</v>
-      </c>
-      <c r="C315" s="5" t="s">
-        <v>1454</v>
-      </c>
-      <c r="D315" s="5" t="s">
-        <v>1453</v>
-      </c>
-      <c r="E315" s="5" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F315" s="5" t="s">
-        <v>1458</v>
-      </c>
-      <c r="G315" s="6" t="s">
-        <v>1454</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7">
-      <c r="A316" t="s">
-        <v>992</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>1459</v>
-      </c>
-      <c r="C316" s="2" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D316" s="2" t="s">
-        <v>1461</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F316" s="2" t="s">
-        <v>1462</v>
-      </c>
-      <c r="G316" s="3" t="s">
-        <v>1460</v>
-      </c>
-    </row>
-    <row r="317" spans="1:7">
-      <c r="A317" t="s">
-        <v>992</v>
-      </c>
-      <c r="B317" s="4" t="s">
-        <v>1463</v>
-      </c>
-      <c r="C317" s="5" t="s">
-        <v>1464</v>
-      </c>
-      <c r="D317" s="5" t="s">
-        <v>1465</v>
-      </c>
-      <c r="E317" s="5" t="s">
-        <v>1162</v>
-      </c>
-      <c r="F317" s="5" t="s">
-        <v>1249</v>
-      </c>
-      <c r="G317" s="6" t="s">
-        <v>1464</v>
-      </c>
-    </row>
-    <row r="318" spans="1:7" ht="27.6">
-      <c r="A318" t="s">
-        <v>992</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>1466</v>
-      </c>
-      <c r="C318" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D318" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>1467</v>
-      </c>
-      <c r="F318" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="G318" s="3" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="319" spans="1:7" ht="27.6">
-      <c r="A319" t="s">
-        <v>992</v>
-      </c>
-      <c r="B319" s="4" t="s">
-        <v>1468</v>
-      </c>
-      <c r="C319" s="5" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D319" s="5" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E319" s="5" t="s">
-        <v>1469</v>
-      </c>
-      <c r="F319" s="5" t="s">
-        <v>994</v>
-      </c>
-      <c r="G319" s="6" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="320" spans="1:7" ht="27.6">
-      <c r="A320" t="s">
-        <v>992</v>
-      </c>
-      <c r="B320" s="1" t="s">
-        <v>1470</v>
-      </c>
-      <c r="C320" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D320" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E320" s="2" t="s">
-        <v>1471</v>
-      </c>
-      <c r="F320" s="2" t="s">
-        <v>993</v>
-      </c>
-      <c r="G320" s="3" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="321" spans="1:7">
-      <c r="A321" t="s">
-        <v>992</v>
-      </c>
-      <c r="B321" s="4" t="s">
-        <v>1472</v>
-      </c>
-      <c r="C321" s="5" t="s">
-        <v>1473</v>
-      </c>
-      <c r="D321" s="5" t="s">
-        <v>1474</v>
-      </c>
-      <c r="E321" s="5" t="s">
-        <v>1162</v>
-      </c>
-      <c r="F321" s="5" t="s">
-        <v>1475</v>
-      </c>
-      <c r="G321" s="6" t="s">
-        <v>1473</v>
-      </c>
-    </row>
-    <row r="322" spans="1:7">
-      <c r="A322" t="s">
-        <v>992</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>1476</v>
-      </c>
-      <c r="C322" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D322" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E322" s="2" t="s">
-        <v>1357</v>
-      </c>
-      <c r="F322" s="2" t="s">
-        <v>1477</v>
-      </c>
-      <c r="G322" s="3" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="323" spans="1:7">
-      <c r="A323" t="s">
-        <v>992</v>
-      </c>
-      <c r="B323" s="4" t="s">
-        <v>1478</v>
-      </c>
-      <c r="C323" s="5" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D323" s="5" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E323" s="5" t="s">
-        <v>1479</v>
-      </c>
-      <c r="F323" s="5" t="s">
-        <v>1480</v>
-      </c>
-      <c r="G323" s="6" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="324" spans="1:7">
-      <c r="A324" t="s">
-        <v>992</v>
-      </c>
-      <c r="B324" s="1" t="s">
-        <v>1481</v>
-      </c>
-      <c r="C324" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D324" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E324" s="2" t="s">
-        <v>1482</v>
-      </c>
-      <c r="F324" s="2" t="s">
-        <v>1483</v>
-      </c>
-      <c r="G324" s="3" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="325" spans="1:7">
-      <c r="A325" t="s">
-        <v>992</v>
-      </c>
-      <c r="B325" s="4" t="s">
-        <v>1484</v>
-      </c>
-      <c r="C325" s="5" t="s">
-        <v>1485</v>
-      </c>
-      <c r="D325" s="5" t="s">
-        <v>1486</v>
-      </c>
-      <c r="E325" s="5" t="s">
-        <v>1487</v>
-      </c>
-      <c r="F325" s="5" t="s">
-        <v>1488</v>
-      </c>
-      <c r="G325" s="6" t="s">
-        <v>1485</v>
-      </c>
-    </row>
-    <row r="326" spans="1:7">
-      <c r="A326" t="s">
-        <v>992</v>
-      </c>
-      <c r="B326" s="1" t="s">
-        <v>1489</v>
-      </c>
-      <c r="C326" s="2" t="s">
-        <v>1490</v>
-      </c>
-      <c r="D326" s="2" t="s">
-        <v>1491</v>
-      </c>
-      <c r="E326" s="2" t="s">
-        <v>1492</v>
-      </c>
-      <c r="F326" s="2" t="s">
-        <v>1493</v>
-      </c>
-      <c r="G326" s="3" t="s">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="327" spans="1:7">
-      <c r="A327" t="s">
-        <v>992</v>
-      </c>
-      <c r="B327" s="4" t="s">
-        <v>1494</v>
-      </c>
-      <c r="C327" s="5" t="s">
-        <v>1495</v>
-      </c>
-      <c r="D327" s="5" t="s">
-        <v>1496</v>
-      </c>
-      <c r="E327" s="5" t="s">
-        <v>1497</v>
-      </c>
-      <c r="F327" s="5" t="s">
-        <v>1498</v>
-      </c>
-      <c r="G327" s="6" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="328" spans="1:7" ht="27.6">
-      <c r="A328" t="s">
-        <v>992</v>
-      </c>
-      <c r="B328" s="1" t="s">
-        <v>1499</v>
-      </c>
-      <c r="C328" s="2" t="s">
-        <v>1500</v>
-      </c>
-      <c r="D328" s="2" t="s">
-        <v>1501</v>
-      </c>
-      <c r="E328" s="2" t="s">
-        <v>1106</v>
-      </c>
-      <c r="F328" s="2" t="s">
-        <v>1502</v>
-      </c>
-      <c r="G328" s="3" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="329" spans="1:7">
-      <c r="A329" t="s">
-        <v>992</v>
-      </c>
-      <c r="B329" s="4" t="s">
-        <v>1503</v>
-      </c>
-      <c r="C329" s="5" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D329" s="5" t="s">
-        <v>1505</v>
-      </c>
-      <c r="E329" s="5" t="s">
-        <v>1506</v>
-      </c>
-      <c r="F329" s="5" t="s">
-        <v>1507</v>
-      </c>
-      <c r="G329" s="6" t="s">
-        <v>1504</v>
-      </c>
-    </row>
-    <row r="330" spans="1:7">
-      <c r="A330" t="s">
-        <v>992</v>
-      </c>
-      <c r="B330" s="1" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C330" s="2" t="s">
-        <v>1509</v>
-      </c>
-      <c r="D330" s="2" t="s">
-        <v>1510</v>
-      </c>
-      <c r="E330" s="2" t="s">
-        <v>1441</v>
-      </c>
-      <c r="F330" s="2" t="s">
-        <v>1511</v>
-      </c>
-      <c r="G330" s="3" t="s">
-        <v>1509</v>
-      </c>
-    </row>
-    <row r="331" spans="1:7">
-      <c r="A331" t="s">
-        <v>992</v>
-      </c>
-      <c r="B331" s="4" t="s">
-        <v>1512</v>
-      </c>
-      <c r="C331" s="5" t="s">
-        <v>1510</v>
-      </c>
-      <c r="D331" s="5" t="s">
-        <v>1509</v>
-      </c>
-      <c r="E331" s="5" t="s">
-        <v>1513</v>
-      </c>
-      <c r="F331" s="5" t="s">
-        <v>1440</v>
-      </c>
-      <c r="G331" s="6" t="s">
-        <v>1510</v>
-      </c>
-    </row>
-    <row r="333" spans="1:7">
-      <c r="A333" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="334" spans="1:7">
-      <c r="A334" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="335" spans="1:7">
-      <c r="A335" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="336" spans="1:7">
-      <c r="A336" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="337" spans="1:1">
-      <c r="A337" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="338" spans="1:1">
-      <c r="A338" t="s">
-        <v>992</v>
-      </c>
+      <c r="B202" s="1"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
+      <c r="E202" s="2"/>
+      <c r="F202" s="2"/>
+      <c r="G202" s="3"/>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="B203" s="4"/>
+      <c r="C203" s="5"/>
+      <c r="D203" s="5"/>
+      <c r="E203" s="5"/>
+      <c r="F203" s="5"/>
+      <c r="G203" s="6"/>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="B204" s="1"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
+      <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
+      <c r="G204" s="3"/>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="B205" s="4"/>
+      <c r="C205" s="5"/>
+      <c r="D205" s="5"/>
+      <c r="E205" s="5"/>
+      <c r="F205" s="5"/>
+      <c r="G205" s="6"/>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="B206" s="1"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
+      <c r="E206" s="2"/>
+      <c r="F206" s="2"/>
+      <c r="G206" s="3"/>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="B207" s="4"/>
+      <c r="C207" s="5"/>
+      <c r="D207" s="5"/>
+      <c r="E207" s="5"/>
+      <c r="F207" s="5"/>
+      <c r="G207" s="6"/>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="B208" s="1"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="2"/>
+      <c r="E208" s="2"/>
+      <c r="F208" s="2"/>
+      <c r="G208" s="3"/>
+    </row>
+    <row r="209" spans="2:7">
+      <c r="B209" s="4"/>
+      <c r="C209" s="5"/>
+      <c r="D209" s="5"/>
+      <c r="E209" s="5"/>
+      <c r="F209" s="5"/>
+      <c r="G209" s="6"/>
+    </row>
+    <row r="210" spans="2:7">
+      <c r="B210" s="1"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
+      <c r="E210" s="2"/>
+      <c r="F210" s="2"/>
+      <c r="G210" s="3"/>
+    </row>
+    <row r="211" spans="2:7">
+      <c r="B211" s="4"/>
+      <c r="C211" s="5"/>
+      <c r="D211" s="5"/>
+      <c r="E211" s="5"/>
+      <c r="F211" s="5"/>
+      <c r="G211" s="6"/>
+    </row>
+    <row r="212" spans="2:7">
+      <c r="B212" s="1"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
+      <c r="E212" s="2"/>
+      <c r="F212" s="2"/>
+      <c r="G212" s="3"/>
+    </row>
+    <row r="213" spans="2:7">
+      <c r="B213" s="4"/>
+      <c r="C213" s="5"/>
+      <c r="D213" s="5"/>
+      <c r="E213" s="5"/>
+      <c r="F213" s="5"/>
+      <c r="G213" s="6"/>
+    </row>
+    <row r="214" spans="2:7">
+      <c r="B214" s="1"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
+      <c r="E214" s="2"/>
+      <c r="F214" s="2"/>
+      <c r="G214" s="3"/>
+    </row>
+    <row r="215" spans="2:7">
+      <c r="B215" s="4"/>
+      <c r="C215" s="5"/>
+      <c r="D215" s="5"/>
+      <c r="E215" s="5"/>
+      <c r="F215" s="5"/>
+      <c r="G215" s="6"/>
+    </row>
+    <row r="216" spans="2:7">
+      <c r="B216" s="1"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
+      <c r="E216" s="2"/>
+      <c r="F216" s="2"/>
+      <c r="G216" s="3"/>
+    </row>
+    <row r="217" spans="2:7">
+      <c r="B217" s="4"/>
+      <c r="C217" s="5"/>
+      <c r="D217" s="5"/>
+      <c r="E217" s="5"/>
+      <c r="F217" s="5"/>
+      <c r="G217" s="6"/>
+    </row>
+    <row r="218" spans="2:7">
+      <c r="B218" s="1"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
+      <c r="E218" s="2"/>
+      <c r="F218" s="2"/>
+      <c r="G218" s="3"/>
+    </row>
+    <row r="219" spans="2:7">
+      <c r="B219" s="4"/>
+      <c r="C219" s="5"/>
+      <c r="D219" s="5"/>
+      <c r="E219" s="5"/>
+      <c r="F219" s="5"/>
+      <c r="G219" s="6"/>
+    </row>
+    <row r="220" spans="2:7">
+      <c r="B220" s="1"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="3"/>
+    </row>
+    <row r="221" spans="2:7">
+      <c r="B221" s="4"/>
+      <c r="C221" s="5"/>
+      <c r="D221" s="5"/>
+      <c r="E221" s="5"/>
+      <c r="F221" s="5"/>
+      <c r="G221" s="6"/>
+    </row>
+    <row r="222" spans="2:7">
+      <c r="B222" s="1"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="3"/>
+    </row>
+    <row r="223" spans="2:7">
+      <c r="B223" s="4"/>
+      <c r="C223" s="5"/>
+      <c r="D223" s="5"/>
+      <c r="E223" s="5"/>
+      <c r="F223" s="5"/>
+      <c r="G223" s="6"/>
+    </row>
+    <row r="224" spans="2:7">
+      <c r="B224" s="1"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
+      <c r="E224" s="2"/>
+      <c r="F224" s="2"/>
+      <c r="G224" s="3"/>
+    </row>
+    <row r="225" spans="2:7">
+      <c r="B225" s="4"/>
+      <c r="C225" s="5"/>
+      <c r="D225" s="5"/>
+      <c r="E225" s="5"/>
+      <c r="F225" s="5"/>
+      <c r="G225" s="6"/>
+    </row>
+    <row r="226" spans="2:7">
+      <c r="B226" s="1"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
+      <c r="E226" s="2"/>
+      <c r="F226" s="2"/>
+      <c r="G226" s="3"/>
+    </row>
+    <row r="227" spans="2:7">
+      <c r="B227" s="4"/>
+      <c r="C227" s="5"/>
+      <c r="D227" s="5"/>
+      <c r="E227" s="5"/>
+      <c r="F227" s="5"/>
+      <c r="G227" s="6"/>
+    </row>
+    <row r="228" spans="2:7">
+      <c r="B228" s="1"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2"/>
+      <c r="E228" s="2"/>
+      <c r="F228" s="2"/>
+      <c r="G228" s="3"/>
+    </row>
+    <row r="229" spans="2:7">
+      <c r="B229" s="4"/>
+      <c r="C229" s="5"/>
+      <c r="D229" s="5"/>
+      <c r="E229" s="5"/>
+      <c r="F229" s="5"/>
+      <c r="G229" s="6"/>
+    </row>
+    <row r="230" spans="2:7">
+      <c r="B230" s="1"/>
+      <c r="C230" s="2"/>
+      <c r="D230" s="2"/>
+      <c r="E230" s="2"/>
+      <c r="F230" s="2"/>
+      <c r="G230" s="3"/>
+    </row>
+    <row r="231" spans="2:7">
+      <c r="B231" s="4"/>
+      <c r="C231" s="5"/>
+      <c r="D231" s="5"/>
+      <c r="E231" s="5"/>
+      <c r="F231" s="5"/>
+      <c r="G231" s="6"/>
+    </row>
+    <row r="232" spans="2:7">
+      <c r="B232" s="1"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="2"/>
+      <c r="E232" s="2"/>
+      <c r="F232" s="2"/>
+      <c r="G232" s="3"/>
+    </row>
+    <row r="233" spans="2:7">
+      <c r="B233" s="4"/>
+      <c r="C233" s="5"/>
+      <c r="D233" s="5"/>
+      <c r="E233" s="5"/>
+      <c r="F233" s="5"/>
+      <c r="G233" s="6"/>
+    </row>
+    <row r="234" spans="2:7">
+      <c r="B234" s="1"/>
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
+      <c r="E234" s="2"/>
+      <c r="F234" s="2"/>
+      <c r="G234" s="3"/>
+    </row>
+    <row r="235" spans="2:7">
+      <c r="B235" s="4"/>
+      <c r="C235" s="5"/>
+      <c r="D235" s="5"/>
+      <c r="E235" s="5"/>
+      <c r="F235" s="5"/>
+      <c r="G235" s="6"/>
+    </row>
+    <row r="236" spans="2:7">
+      <c r="B236" s="1"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
+      <c r="E236" s="2"/>
+      <c r="F236" s="2"/>
+      <c r="G236" s="3"/>
+    </row>
+    <row r="237" spans="2:7">
+      <c r="B237" s="4"/>
+      <c r="C237" s="5"/>
+      <c r="D237" s="5"/>
+      <c r="E237" s="5"/>
+      <c r="F237" s="5"/>
+      <c r="G237" s="6"/>
+    </row>
+    <row r="238" spans="2:7">
+      <c r="B238" s="1"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
+      <c r="E238" s="2"/>
+      <c r="F238" s="2"/>
+      <c r="G238" s="3"/>
+    </row>
+    <row r="239" spans="2:7">
+      <c r="B239" s="4"/>
+      <c r="C239" s="5"/>
+      <c r="D239" s="5"/>
+      <c r="E239" s="5"/>
+      <c r="F239" s="5"/>
+      <c r="G239" s="6"/>
+    </row>
+    <row r="240" spans="2:7">
+      <c r="B240" s="1"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+      <c r="F240" s="2"/>
+      <c r="G240" s="3"/>
+    </row>
+    <row r="241" spans="2:7">
+      <c r="B241" s="4"/>
+      <c r="C241" s="5"/>
+      <c r="D241" s="5"/>
+      <c r="E241" s="5"/>
+      <c r="F241" s="5"/>
+      <c r="G241" s="6"/>
+    </row>
+    <row r="242" spans="2:7">
+      <c r="B242" s="1"/>
+      <c r="C242" s="2"/>
+      <c r="D242" s="2"/>
+      <c r="E242" s="2"/>
+      <c r="F242" s="2"/>
+      <c r="G242" s="3"/>
+    </row>
+    <row r="243" spans="2:7">
+      <c r="B243" s="4"/>
+      <c r="C243" s="5"/>
+      <c r="D243" s="5"/>
+      <c r="E243" s="5"/>
+      <c r="F243" s="5"/>
+      <c r="G243" s="6"/>
+    </row>
+    <row r="244" spans="2:7">
+      <c r="B244" s="1"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
+      <c r="E244" s="2"/>
+      <c r="F244" s="2"/>
+      <c r="G244" s="3"/>
+    </row>
+    <row r="245" spans="2:7">
+      <c r="B245" s="4"/>
+      <c r="C245" s="5"/>
+      <c r="D245" s="5"/>
+      <c r="E245" s="5"/>
+      <c r="F245" s="5"/>
+      <c r="G245" s="6"/>
+    </row>
+    <row r="246" spans="2:7">
+      <c r="B246" s="1"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
+      <c r="E246" s="2"/>
+      <c r="F246" s="2"/>
+      <c r="G246" s="3"/>
+    </row>
+    <row r="247" spans="2:7">
+      <c r="B247" s="4"/>
+      <c r="C247" s="5"/>
+      <c r="D247" s="5"/>
+      <c r="E247" s="5"/>
+      <c r="F247" s="5"/>
+      <c r="G247" s="6"/>
+    </row>
+    <row r="248" spans="2:7">
+      <c r="B248" s="1"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="3"/>
+    </row>
+    <row r="249" spans="2:7">
+      <c r="B249" s="4"/>
+      <c r="C249" s="5"/>
+      <c r="D249" s="5"/>
+      <c r="E249" s="5"/>
+      <c r="F249" s="5"/>
+      <c r="G249" s="6"/>
+    </row>
+    <row r="250" spans="2:7">
+      <c r="B250" s="1"/>
+      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
+      <c r="E250" s="2"/>
+      <c r="F250" s="2"/>
+      <c r="G250" s="3"/>
+    </row>
+    <row r="251" spans="2:7">
+      <c r="B251" s="4"/>
+      <c r="C251" s="5"/>
+      <c r="D251" s="5"/>
+      <c r="E251" s="5"/>
+      <c r="F251" s="5"/>
+      <c r="G251" s="6"/>
+    </row>
+    <row r="252" spans="2:7">
+      <c r="B252" s="1"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
+      <c r="E252" s="2"/>
+      <c r="F252" s="2"/>
+      <c r="G252" s="3"/>
+    </row>
+    <row r="253" spans="2:7">
+      <c r="B253" s="4"/>
+      <c r="C253" s="5"/>
+      <c r="D253" s="5"/>
+      <c r="E253" s="5"/>
+      <c r="F253" s="5"/>
+      <c r="G253" s="6"/>
+    </row>
+    <row r="254" spans="2:7">
+      <c r="B254" s="1"/>
+      <c r="C254" s="2"/>
+      <c r="D254" s="2"/>
+      <c r="E254" s="2"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="3"/>
+    </row>
+    <row r="255" spans="2:7">
+      <c r="B255" s="4"/>
+      <c r="C255" s="5"/>
+      <c r="D255" s="5"/>
+      <c r="E255" s="5"/>
+      <c r="F255" s="5"/>
+      <c r="G255" s="6"/>
+    </row>
+    <row r="256" spans="2:7">
+      <c r="B256" s="1"/>
+      <c r="C256" s="2"/>
+      <c r="D256" s="2"/>
+      <c r="E256" s="2"/>
+      <c r="F256" s="2"/>
+      <c r="G256" s="3"/>
+    </row>
+    <row r="257" spans="2:7">
+      <c r="B257" s="4"/>
+      <c r="C257" s="5"/>
+      <c r="D257" s="5"/>
+      <c r="E257" s="5"/>
+      <c r="F257" s="5"/>
+      <c r="G257" s="6"/>
+    </row>
+    <row r="258" spans="2:7">
+      <c r="B258" s="1"/>
+      <c r="C258" s="2"/>
+      <c r="D258" s="2"/>
+      <c r="E258" s="2"/>
+      <c r="F258" s="2"/>
+      <c r="G258" s="3"/>
+    </row>
+    <row r="259" spans="2:7">
+      <c r="B259" s="4"/>
+      <c r="C259" s="5"/>
+      <c r="D259" s="5"/>
+      <c r="E259" s="5"/>
+      <c r="F259" s="5"/>
+      <c r="G259" s="6"/>
+    </row>
+    <row r="260" spans="2:7">
+      <c r="B260" s="1"/>
+      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
+      <c r="E260" s="2"/>
+      <c r="F260" s="2"/>
+      <c r="G260" s="3"/>
+    </row>
+    <row r="261" spans="2:7">
+      <c r="B261" s="4"/>
+      <c r="C261" s="5"/>
+      <c r="D261" s="5"/>
+      <c r="E261" s="5"/>
+      <c r="F261" s="5"/>
+      <c r="G261" s="6"/>
+    </row>
+    <row r="262" spans="2:7">
+      <c r="B262" s="1"/>
+      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
+      <c r="E262" s="2"/>
+      <c r="F262" s="2"/>
+      <c r="G262" s="3"/>
+    </row>
+    <row r="263" spans="2:7">
+      <c r="B263" s="4"/>
+      <c r="C263" s="5"/>
+      <c r="D263" s="5"/>
+      <c r="E263" s="5"/>
+      <c r="F263" s="5"/>
+      <c r="G263" s="6"/>
+    </row>
+    <row r="264" spans="2:7">
+      <c r="B264" s="1"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="2"/>
+      <c r="E264" s="2"/>
+      <c r="F264" s="2"/>
+      <c r="G264" s="3"/>
+    </row>
+    <row r="265" spans="2:7">
+      <c r="B265" s="4"/>
+      <c r="C265" s="5"/>
+      <c r="D265" s="5"/>
+      <c r="E265" s="5"/>
+      <c r="F265" s="5"/>
+      <c r="G265" s="6"/>
+    </row>
+    <row r="266" spans="2:7">
+      <c r="B266" s="1"/>
+      <c r="C266" s="2"/>
+      <c r="D266" s="2"/>
+      <c r="E266" s="2"/>
+      <c r="F266" s="2"/>
+      <c r="G266" s="3"/>
+    </row>
+    <row r="267" spans="2:7">
+      <c r="B267" s="4"/>
+      <c r="C267" s="5"/>
+      <c r="D267" s="5"/>
+      <c r="E267" s="5"/>
+      <c r="F267" s="5"/>
+      <c r="G267" s="6"/>
+    </row>
+    <row r="268" spans="2:7">
+      <c r="B268" s="1"/>
+      <c r="C268" s="2"/>
+      <c r="D268" s="2"/>
+      <c r="E268" s="2"/>
+      <c r="F268" s="2"/>
+      <c r="G268" s="3"/>
+    </row>
+    <row r="269" spans="2:7">
+      <c r="B269" s="4"/>
+      <c r="C269" s="5"/>
+      <c r="D269" s="5"/>
+      <c r="E269" s="5"/>
+      <c r="F269" s="5"/>
+      <c r="G269" s="6"/>
+    </row>
+    <row r="270" spans="2:7">
+      <c r="B270" s="1"/>
+      <c r="C270" s="2"/>
+      <c r="D270" s="2"/>
+      <c r="E270" s="2"/>
+      <c r="F270" s="2"/>
+      <c r="G270" s="3"/>
+    </row>
+    <row r="271" spans="2:7">
+      <c r="B271" s="4"/>
+      <c r="C271" s="5"/>
+      <c r="D271" s="5"/>
+      <c r="E271" s="5"/>
+      <c r="F271" s="5"/>
+      <c r="G271" s="6"/>
+    </row>
+    <row r="272" spans="2:7">
+      <c r="B272" s="1"/>
+      <c r="C272" s="2"/>
+      <c r="D272" s="2"/>
+      <c r="E272" s="2"/>
+      <c r="F272" s="2"/>
+      <c r="G272" s="3"/>
+    </row>
+    <row r="273" spans="2:7">
+      <c r="B273" s="4"/>
+      <c r="C273" s="5"/>
+      <c r="D273" s="5"/>
+      <c r="E273" s="5"/>
+      <c r="F273" s="5"/>
+      <c r="G273" s="6"/>
+    </row>
+    <row r="274" spans="2:7">
+      <c r="B274" s="1"/>
+      <c r="C274" s="2"/>
+      <c r="D274" s="2"/>
+      <c r="E274" s="2"/>
+      <c r="F274" s="2"/>
+      <c r="G274" s="3"/>
+    </row>
+    <row r="275" spans="2:7">
+      <c r="B275" s="4"/>
+      <c r="C275" s="5"/>
+      <c r="D275" s="5"/>
+      <c r="E275" s="5"/>
+      <c r="F275" s="5"/>
+      <c r="G275" s="6"/>
+    </row>
+    <row r="276" spans="2:7">
+      <c r="B276" s="1"/>
+      <c r="C276" s="2"/>
+      <c r="D276" s="2"/>
+      <c r="E276" s="2"/>
+      <c r="F276" s="2"/>
+      <c r="G276" s="3"/>
+    </row>
+    <row r="277" spans="2:7">
+      <c r="B277" s="4"/>
+      <c r="C277" s="5"/>
+      <c r="D277" s="5"/>
+      <c r="E277" s="5"/>
+      <c r="F277" s="5"/>
+      <c r="G277" s="6"/>
+    </row>
+    <row r="278" spans="2:7">
+      <c r="B278" s="1"/>
+      <c r="C278" s="2"/>
+      <c r="D278" s="2"/>
+      <c r="E278" s="2"/>
+      <c r="F278" s="2"/>
+      <c r="G278" s="3"/>
+    </row>
+    <row r="279" spans="2:7">
+      <c r="B279" s="4"/>
+      <c r="C279" s="5"/>
+      <c r="D279" s="5"/>
+      <c r="E279" s="5"/>
+      <c r="F279" s="5"/>
+      <c r="G279" s="6"/>
+    </row>
+    <row r="280" spans="2:7">
+      <c r="B280" s="1"/>
+      <c r="C280" s="2"/>
+      <c r="D280" s="2"/>
+      <c r="E280" s="2"/>
+      <c r="F280" s="2"/>
+      <c r="G280" s="3"/>
+    </row>
+    <row r="281" spans="2:7">
+      <c r="B281" s="4"/>
+      <c r="C281" s="5"/>
+      <c r="D281" s="5"/>
+      <c r="E281" s="5"/>
+      <c r="F281" s="5"/>
+      <c r="G281" s="6"/>
+    </row>
+    <row r="282" spans="2:7">
+      <c r="B282" s="1"/>
+      <c r="C282" s="2"/>
+      <c r="D282" s="2"/>
+      <c r="E282" s="2"/>
+      <c r="F282" s="2"/>
+      <c r="G282" s="3"/>
+    </row>
+    <row r="283" spans="2:7">
+      <c r="B283" s="4"/>
+      <c r="C283" s="5"/>
+      <c r="D283" s="5"/>
+      <c r="E283" s="5"/>
+      <c r="F283" s="5"/>
+      <c r="G283" s="6"/>
+    </row>
+    <row r="284" spans="2:7">
+      <c r="B284" s="1"/>
+      <c r="C284" s="2"/>
+      <c r="D284" s="2"/>
+      <c r="E284" s="2"/>
+      <c r="F284" s="2"/>
+      <c r="G284" s="3"/>
+    </row>
+    <row r="285" spans="2:7">
+      <c r="B285" s="4"/>
+      <c r="C285" s="5"/>
+      <c r="D285" s="5"/>
+      <c r="E285" s="5"/>
+      <c r="F285" s="5"/>
+      <c r="G285" s="6"/>
+    </row>
+    <row r="286" spans="2:7">
+      <c r="B286" s="1"/>
+      <c r="C286" s="2"/>
+      <c r="D286" s="2"/>
+      <c r="E286" s="2"/>
+      <c r="F286" s="2"/>
+      <c r="G286" s="3"/>
+    </row>
+    <row r="287" spans="2:7">
+      <c r="B287" s="4"/>
+      <c r="C287" s="5"/>
+      <c r="D287" s="5"/>
+      <c r="E287" s="5"/>
+      <c r="F287" s="5"/>
+      <c r="G287" s="6"/>
+    </row>
+    <row r="288" spans="2:7">
+      <c r="B288" s="1"/>
+      <c r="C288" s="2"/>
+      <c r="D288" s="2"/>
+      <c r="E288" s="2"/>
+      <c r="F288" s="2"/>
+      <c r="G288" s="3"/>
+    </row>
+    <row r="289" spans="2:7">
+      <c r="B289" s="4"/>
+      <c r="C289" s="5"/>
+      <c r="D289" s="5"/>
+      <c r="E289" s="5"/>
+      <c r="F289" s="5"/>
+      <c r="G289" s="6"/>
+    </row>
+    <row r="290" spans="2:7">
+      <c r="B290" s="1"/>
+      <c r="C290" s="2"/>
+      <c r="D290" s="2"/>
+      <c r="E290" s="2"/>
+      <c r="F290" s="2"/>
+      <c r="G290" s="3"/>
+    </row>
+    <row r="291" spans="2:7">
+      <c r="B291" s="4"/>
+      <c r="C291" s="5"/>
+      <c r="D291" s="5"/>
+      <c r="E291" s="5"/>
+      <c r="F291" s="5"/>
+      <c r="G291" s="6"/>
+    </row>
+    <row r="292" spans="2:7">
+      <c r="B292" s="1"/>
+      <c r="C292" s="2"/>
+      <c r="D292" s="2"/>
+      <c r="E292" s="2"/>
+      <c r="F292" s="2"/>
+      <c r="G292" s="3"/>
+    </row>
+    <row r="293" spans="2:7">
+      <c r="B293" s="4"/>
+      <c r="C293" s="5"/>
+      <c r="D293" s="5"/>
+      <c r="E293" s="5"/>
+      <c r="F293" s="5"/>
+      <c r="G293" s="6"/>
+    </row>
+    <row r="294" spans="2:7">
+      <c r="B294" s="1"/>
+      <c r="C294" s="2"/>
+      <c r="D294" s="2"/>
+      <c r="E294" s="2"/>
+      <c r="F294" s="2"/>
+      <c r="G294" s="3"/>
+    </row>
+    <row r="295" spans="2:7">
+      <c r="B295" s="4"/>
+      <c r="C295" s="5"/>
+      <c r="D295" s="5"/>
+      <c r="E295" s="5"/>
+      <c r="F295" s="5"/>
+      <c r="G295" s="6"/>
+    </row>
+    <row r="296" spans="2:7">
+      <c r="B296" s="1"/>
+      <c r="C296" s="2"/>
+      <c r="D296" s="2"/>
+      <c r="E296" s="2"/>
+      <c r="F296" s="2"/>
+      <c r="G296" s="3"/>
+    </row>
+    <row r="297" spans="2:7">
+      <c r="B297" s="4"/>
+      <c r="C297" s="5"/>
+      <c r="D297" s="5"/>
+      <c r="E297" s="5"/>
+      <c r="F297" s="5"/>
+      <c r="G297" s="6"/>
+    </row>
+    <row r="298" spans="2:7">
+      <c r="B298" s="1"/>
+      <c r="C298" s="2"/>
+      <c r="D298" s="2"/>
+      <c r="E298" s="2"/>
+      <c r="F298" s="2"/>
+      <c r="G298" s="3"/>
+    </row>
+    <row r="299" spans="2:7">
+      <c r="B299" s="4"/>
+      <c r="C299" s="5"/>
+      <c r="D299" s="5"/>
+      <c r="E299" s="5"/>
+      <c r="F299" s="5"/>
+      <c r="G299" s="6"/>
+    </row>
+    <row r="300" spans="2:7">
+      <c r="B300" s="1"/>
+      <c r="C300" s="2"/>
+      <c r="D300" s="2"/>
+      <c r="E300" s="2"/>
+      <c r="F300" s="2"/>
+      <c r="G300" s="3"/>
+    </row>
+    <row r="301" spans="2:7">
+      <c r="B301" s="4"/>
+      <c r="C301" s="5"/>
+      <c r="D301" s="5"/>
+      <c r="E301" s="5"/>
+      <c r="F301" s="5"/>
+      <c r="G301" s="6"/>
+    </row>
+    <row r="302" spans="2:7">
+      <c r="B302" s="1"/>
+      <c r="C302" s="2"/>
+      <c r="D302" s="2"/>
+      <c r="E302" s="2"/>
+      <c r="F302" s="2"/>
+      <c r="G302" s="3"/>
+    </row>
+    <row r="303" spans="2:7">
+      <c r="B303" s="4"/>
+      <c r="C303" s="5"/>
+      <c r="D303" s="5"/>
+      <c r="E303" s="5"/>
+      <c r="F303" s="5"/>
+      <c r="G303" s="6"/>
+    </row>
+    <row r="304" spans="2:7">
+      <c r="B304" s="1"/>
+      <c r="C304" s="2"/>
+      <c r="D304" s="2"/>
+      <c r="E304" s="2"/>
+      <c r="F304" s="2"/>
+      <c r="G304" s="3"/>
+    </row>
+    <row r="305" spans="2:7">
+      <c r="B305" s="4"/>
+      <c r="C305" s="5"/>
+      <c r="D305" s="5"/>
+      <c r="E305" s="5"/>
+      <c r="F305" s="5"/>
+      <c r="G305" s="6"/>
+    </row>
+    <row r="306" spans="2:7">
+      <c r="B306" s="1"/>
+      <c r="C306" s="2"/>
+      <c r="D306" s="2"/>
+      <c r="E306" s="2"/>
+      <c r="F306" s="2"/>
+      <c r="G306" s="3"/>
+    </row>
+    <row r="307" spans="2:7">
+      <c r="B307" s="4"/>
+      <c r="C307" s="5"/>
+      <c r="D307" s="5"/>
+      <c r="E307" s="5"/>
+      <c r="F307" s="5"/>
+      <c r="G307" s="6"/>
+    </row>
+    <row r="308" spans="2:7">
+      <c r="B308" s="1"/>
+      <c r="C308" s="2"/>
+      <c r="D308" s="2"/>
+      <c r="E308" s="2"/>
+      <c r="F308" s="2"/>
+      <c r="G308" s="3"/>
+    </row>
+    <row r="309" spans="2:7">
+      <c r="B309" s="4"/>
+      <c r="C309" s="5"/>
+      <c r="D309" s="5"/>
+      <c r="E309" s="5"/>
+      <c r="F309" s="5"/>
+      <c r="G309" s="6"/>
+    </row>
+    <row r="310" spans="2:7">
+      <c r="B310" s="1"/>
+      <c r="C310" s="2"/>
+      <c r="D310" s="2"/>
+      <c r="E310" s="2"/>
+      <c r="F310" s="2"/>
+      <c r="G310" s="3"/>
+    </row>
+    <row r="311" spans="2:7">
+      <c r="B311" s="4"/>
+      <c r="C311" s="5"/>
+      <c r="D311" s="5"/>
+      <c r="E311" s="5"/>
+      <c r="F311" s="5"/>
+      <c r="G311" s="6"/>
+    </row>
+    <row r="312" spans="2:7">
+      <c r="B312" s="1"/>
+      <c r="C312" s="2"/>
+      <c r="D312" s="2"/>
+      <c r="E312" s="2"/>
+      <c r="F312" s="2"/>
+      <c r="G312" s="3"/>
+    </row>
+    <row r="313" spans="2:7">
+      <c r="B313" s="4"/>
+      <c r="C313" s="5"/>
+      <c r="D313" s="5"/>
+      <c r="E313" s="5"/>
+      <c r="F313" s="5"/>
+      <c r="G313" s="6"/>
+    </row>
+    <row r="314" spans="2:7">
+      <c r="B314" s="1"/>
+      <c r="C314" s="2"/>
+      <c r="D314" s="2"/>
+      <c r="E314" s="2"/>
+      <c r="F314" s="2"/>
+      <c r="G314" s="3"/>
+    </row>
+    <row r="315" spans="2:7">
+      <c r="B315" s="4"/>
+      <c r="C315" s="5"/>
+      <c r="D315" s="5"/>
+      <c r="E315" s="5"/>
+      <c r="F315" s="5"/>
+      <c r="G315" s="6"/>
+    </row>
+    <row r="316" spans="2:7">
+      <c r="B316" s="1"/>
+      <c r="C316" s="2"/>
+      <c r="D316" s="2"/>
+      <c r="E316" s="2"/>
+      <c r="F316" s="2"/>
+      <c r="G316" s="3"/>
+    </row>
+    <row r="317" spans="2:7">
+      <c r="B317" s="4"/>
+      <c r="C317" s="5"/>
+      <c r="D317" s="5"/>
+      <c r="E317" s="5"/>
+      <c r="F317" s="5"/>
+      <c r="G317" s="6"/>
+    </row>
+    <row r="318" spans="2:7">
+      <c r="B318" s="1"/>
+      <c r="C318" s="2"/>
+      <c r="D318" s="2"/>
+      <c r="E318" s="2"/>
+      <c r="F318" s="2"/>
+      <c r="G318" s="3"/>
+    </row>
+    <row r="319" spans="2:7">
+      <c r="B319" s="4"/>
+      <c r="C319" s="5"/>
+      <c r="D319" s="5"/>
+      <c r="E319" s="5"/>
+      <c r="F319" s="5"/>
+      <c r="G319" s="6"/>
+    </row>
+    <row r="320" spans="2:7">
+      <c r="B320" s="1"/>
+      <c r="C320" s="2"/>
+      <c r="D320" s="2"/>
+      <c r="E320" s="2"/>
+      <c r="F320" s="2"/>
+      <c r="G320" s="3"/>
+    </row>
+    <row r="321" spans="2:7">
+      <c r="B321" s="4"/>
+      <c r="C321" s="5"/>
+      <c r="D321" s="5"/>
+      <c r="E321" s="5"/>
+      <c r="F321" s="5"/>
+      <c r="G321" s="6"/>
+    </row>
+    <row r="322" spans="2:7">
+      <c r="B322" s="1"/>
+      <c r="C322" s="2"/>
+      <c r="D322" s="2"/>
+      <c r="E322" s="2"/>
+      <c r="F322" s="2"/>
+      <c r="G322" s="3"/>
+    </row>
+    <row r="323" spans="2:7">
+      <c r="B323" s="4"/>
+      <c r="C323" s="5"/>
+      <c r="D323" s="5"/>
+      <c r="E323" s="5"/>
+      <c r="F323" s="5"/>
+      <c r="G323" s="6"/>
+    </row>
+    <row r="324" spans="2:7">
+      <c r="B324" s="1"/>
+      <c r="C324" s="2"/>
+      <c r="D324" s="2"/>
+      <c r="E324" s="2"/>
+      <c r="F324" s="2"/>
+      <c r="G324" s="3"/>
+    </row>
+    <row r="325" spans="2:7">
+      <c r="B325" s="4"/>
+      <c r="C325" s="5"/>
+      <c r="D325" s="5"/>
+      <c r="E325" s="5"/>
+      <c r="F325" s="5"/>
+      <c r="G325" s="6"/>
+    </row>
+    <row r="326" spans="2:7">
+      <c r="B326" s="1"/>
+      <c r="C326" s="2"/>
+      <c r="D326" s="2"/>
+      <c r="E326" s="2"/>
+      <c r="F326" s="2"/>
+      <c r="G326" s="3"/>
+    </row>
+    <row r="327" spans="2:7">
+      <c r="B327" s="4"/>
+      <c r="C327" s="5"/>
+      <c r="D327" s="5"/>
+      <c r="E327" s="5"/>
+      <c r="F327" s="5"/>
+      <c r="G327" s="6"/>
+    </row>
+    <row r="328" spans="2:7">
+      <c r="B328" s="1"/>
+      <c r="C328" s="2"/>
+      <c r="D328" s="2"/>
+      <c r="E328" s="2"/>
+      <c r="F328" s="2"/>
+      <c r="G328" s="3"/>
+    </row>
+    <row r="329" spans="2:7">
+      <c r="B329" s="4"/>
+      <c r="C329" s="5"/>
+      <c r="D329" s="5"/>
+      <c r="E329" s="5"/>
+      <c r="F329" s="5"/>
+      <c r="G329" s="6"/>
+    </row>
+    <row r="330" spans="2:7">
+      <c r="B330" s="1"/>
+      <c r="C330" s="2"/>
+      <c r="D330" s="2"/>
+      <c r="E330" s="2"/>
+      <c r="F330" s="2"/>
+      <c r="G330" s="3"/>
+    </row>
+    <row r="331" spans="2:7">
+      <c r="B331" s="4"/>
+      <c r="C331" s="5"/>
+      <c r="D331" s="5"/>
+      <c r="E331" s="5"/>
+      <c r="F331" s="5"/>
+      <c r="G331" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
